--- a/전공의_파견_모니터링.xlsx
+++ b/전공의_파견_모니터링.xlsx
@@ -1,37 +1,36 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="사용안내" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="입력_기본자료" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="입력_인턴근무계획" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="입력_파견수련계획" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="입력_구리근무자명단" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="입력_전공의명단" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="출력_서울급여" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="출력_구리근무자" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="출력_요약" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="출력_인턴현황" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="설정_코드표" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사용안내" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="입력_기본자료" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="입력_인턴근무계획" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="입력_구리근무자명단" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="입력_전공의명단" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="출력_서울급여" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="출력_구리근무자" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="출력_요약" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="출력_인턴현황" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="설정_코드표" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="급여기준월">'설정_코드표'!$P$9</definedName>
     <definedName name="판정기준일">'설정_코드표'!$P$10</definedName>
-    <definedName name="임박기준일">'설정_코드표'!$P$11</definedName>
     <definedName name="병원목록">병원표[병원]</definedName>
     <definedName name="진료과목록">진료과표[근무과]</definedName>
-    <definedName name="근거목록">근거표[파견근거]</definedName>
     <definedName name="병원표기목록">병원약칭표[표기]</definedName>
     <definedName name="과약칭목록">과약칭표[약칭]</definedName>
     <definedName name="구리_키">'출력_구리근무자'!$K$6:$K$20005</definedName>
     <definedName name="구리_이름">'출력_구리근무자'!$D$6:$D$20005</definedName>
     <definedName name="구리_근무일">'출력_구리근무자'!$H$6:$H$20005</definedName>
     <definedName name="구리_독자">'출력_구리근무자'!$J$6:$J$20005</definedName>
+    <definedName name="구리_시작">'출력_구리근무자'!$F$6:$F$20005</definedName>
+    <definedName name="구리_종료">'출력_구리근무자'!$G$6:$G$20005</definedName>
     <definedName name="인턴위치_이번">'출력_인턴현황'!$G$3</definedName>
     <definedName name="인턴위치_다음">'출력_인턴현황'!$I$3</definedName>
     <definedName name="인턴위치_기준월">'출력_인턴현황'!$K$2</definedName>
@@ -183,7 +182,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -202,8 +201,6 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="3" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -212,6 +209,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -246,7 +244,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="12">
+  <dxfs count="9">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -289,27 +287,6 @@
       <fill>
         <patternFill patternType="solid">
           <bgColor rgb="00FFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="00F8CBAD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="00C6E0B4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="00BDD7EE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -442,16 +419,6 @@
 </table>
 </file>
 
-<file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="병원약칭표" displayName="병원약칭표" ref="L1:M19" headerRowCount="1">
-  <tableColumns count="2">
-    <tableColumn id="1" name="표기"/>
-    <tableColumn id="2" name="정식 병원"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
-</table>
-</file>
-
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="인턴계획표" displayName="인턴계획표" ref="B2:T5" headerRowCount="1">
   <tableColumns count="19">
@@ -498,82 +465,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="파견표" displayName="파견표" ref="A3:AF10" headerRowCount="1">
-  <tableColumns count="32">
-    <tableColumn id="1" name="연번"/>
-    <tableColumn id="2" name="모병원명"/>
-    <tableColumn id="3" name="수련종별(I/R)"/>
-    <tableColumn id="4" name="수련과목"/>
-    <tableColumn id="5" name="연차"/>
-    <tableColumn id="6" name="성명"/>
-    <tableColumn id="7" name="전공의등록번호"/>
-    <tableColumn id="8" name="파견시작일"/>
-    <tableColumn id="9" name="파견종료일"/>
-    <tableColumn id="10" name="파견일수"/>
-    <tableColumn id="11" name="파견병원"/>
-    <tableColumn id="12" name="파견과목"/>
-    <tableColumn id="13" name="파견근거(모자/통합수련)"/>
-    <tableColumn id="14" name="비고"/>
-    <tableColumn id="15" name="추가메모"/>
-    <tableColumn id="16" name="키">
-      <calculatedColumnFormula>IF(TRIM(파견표[[#This Row],[전공의등록번호]]&amp;"")="","","R|"&amp;TRIM(파견표[[#This Row],[전공의등록번호]]&amp;""))</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="17" name="시작일(계산)">
-      <calculatedColumnFormula>_xlfn.LET(_xlpm.v_x,파견표[[#This Row],[파견시작일]],IF(ISNUMBER(_xlpm.v_x),_xlpm.v_x,IF(TRIM(_xlpm.v_x&amp;"")="","",IFERROR(DATE(VALUE(LEFT(_xlpm.v_x,4)),VALUE(MID(_xlpm.v_x,6,2)),VALUE(MID(_xlpm.v_x,9,2))),"⚠"&amp;_xlpm.v_x))))</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="18" name="종료일(계산)">
-      <calculatedColumnFormula>_xlfn.LET(_xlpm.v_x,파견표[[#This Row],[파견종료일]],IF(ISNUMBER(_xlpm.v_x),_xlpm.v_x,IF(TRIM(_xlpm.v_x&amp;"")="","",IFERROR(DATE(VALUE(LEFT(_xlpm.v_x,4)),VALUE(MID(_xlpm.v_x,6,2)),VALUE(MID(_xlpm.v_x,9,2))),"⚠"&amp;_xlpm.v_x))))</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="19" name="모병원(정규화)">
-      <calculatedColumnFormula>_xlfn.LET(_xlpm.v_x,TRIM(파견표[[#This Row],[모병원명]]&amp;""),IF(_xlpm.v_x="","",_xlfn.XLOOKUP(_xlpm.v_x,병원약칭표[표기],병원약칭표[정식 병원],"⚠"&amp;_xlpm.v_x)))</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="20" name="파견병원(정규화)">
-      <calculatedColumnFormula>_xlfn.LET(_xlpm.v_x,TRIM(파견표[[#This Row],[파견병원]]&amp;""),IF(_xlpm.v_x="","",_xlfn.XLOOKUP(_xlpm.v_x,병원약칭표[표기],병원약칭표[정식 병원],"⚠"&amp;_xlpm.v_x)))</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="21" name="파견근거(정규화)">
-      <calculatedColumnFormula>_xlfn.LET(_xlpm.v_x,TRIM(파견표[[#This Row],[파견근거(모자/통합수련)]]&amp;""),IF(_xlpm.v_x="","",_xlfn.XLOOKUP(_xlpm.v_x,근거표[파견근거],근거표[파견근거],"⚠"&amp;_xlpm.v_x)))</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="22" name="파견과목(정규화)">
-      <calculatedColumnFormula>_xlfn.LET(_xlpm.v_x,TRIM(파견표[[#This Row],[파견과목]]&amp;""),IF(_xlpm.v_x="","",_xlfn.XLOOKUP(_xlpm.v_x,과약칭표[약칭],과약칭표[정식 명칭],"⚠"&amp;_xlpm.v_x)))</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="23" name="파견일수(계산)">
-      <calculatedColumnFormula>IF(AND(ISNUMBER(파견표[[#This Row],[시작일(계산)]]),ISNUMBER(파견표[[#This Row],[종료일(계산)]])),파견표[[#This Row],[종료일(계산)]]-파견표[[#This Row],[시작일(계산)]]+1,"")</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="24" name="기준월 겹침일수">
-      <calculatedColumnFormula>IF(ISNUMBER(파견표[[#This Row],[시작일(계산)]]),MAX(0,MIN(IF(ISNUMBER(파견표[[#This Row],[종료일(계산)]]),파견표[[#This Row],[종료일(계산)]],EOMONTH(급여기준월,0)),EOMONTH(급여기준월,0))-MAX(파견표[[#This Row],[시작일(계산)]],급여기준월)+1),0)</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="25" name="상태">
-      <calculatedColumnFormula>IF(OR(NOT(ISNUMBER(파견표[[#This Row],[시작일(계산)]])),파견표[[#This Row],[키]]=""),"",IF(TODAY()&lt;파견표[[#This Row],[시작일(계산)]],"파견예정",IF(AND(ISNUMBER(파견표[[#This Row],[종료일(계산)]]),TODAY()&gt;파견표[[#This Row],[종료일(계산)]]),"파견종료","파견중")))</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="26" name="키|상태">
-      <calculatedColumnFormula>IF(OR(파견표[[#This Row],[키]]="",파견표[[#This Row],[상태]]=""),"",파견표[[#This Row],[키]]&amp;"|"&amp;파견표[[#This Row],[상태]])</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="27" name="키|월">
-      <calculatedColumnFormula>IF(AND(파견표[[#This Row],[키]]&lt;&gt;"",파견표[[#This Row],[기준월 겹침일수]]&gt;0),파견표[[#This Row],[키]]&amp;"|월","")</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="28" name="다기관 시작">
-      <calculatedColumnFormula>_xlfn.LET(_xlpm.v_n,TRIM(파견표[[#This Row],[비고]]&amp;" "&amp;파견표[[#This Row],[추가메모]]),IF(ISNUMBER(SEARCH("다기관",_xlpm.v_n)),IFERROR(DATE(VALUE(MID(_xlpm.v_n,1,4)),VALUE(MID(_xlpm.v_n,6,2)),VALUE(MID(_xlpm.v_n,9,2))),IF(ISNUMBER(파견표[[#This Row],[시작일(계산)]]),파견표[[#This Row],[시작일(계산)]],"")),""))</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="29" name="다기관 종료">
-      <calculatedColumnFormula>_xlfn.LET(_xlpm.v_n,TRIM(파견표[[#This Row],[비고]]&amp;" "&amp;파견표[[#This Row],[추가메모]]),IF(ISNUMBER(SEARCH("다기관",_xlpm.v_n)),IFERROR(DATE(VALUE(MID(_xlpm.v_n,12,4)),VALUE(MID(_xlpm.v_n,17,2)),VALUE(MID(_xlpm.v_n,20,2))),IF(ISNUMBER(파견표[[#This Row],[종료일(계산)]]),파견표[[#This Row],[종료일(계산)]],"")),""))</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="30" name="다기관 겹침일수">
-      <calculatedColumnFormula>IF(AND(ISNUMBER(파견표[[#This Row],[다기관 시작]]),ISNUMBER(파견표[[#This Row],[다기관 종료]])),MAX(0,MIN(파견표[[#This Row],[다기관 종료]],EOMONTH(급여기준월,0))-MAX(파견표[[#This Row],[다기관 시작]],급여기준월)+1),0)</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="31" name="키|다기관">
-      <calculatedColumnFormula>IF(AND(파견표[[#This Row],[키]]&lt;&gt;"",ISNUMBER(파견표[[#This Row],[다기관 시작]])),파견표[[#This Row],[키]]&amp;"|다기관","")</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="32" name="입력오류">
-      <calculatedColumnFormula>IF(COUNTA(파견표[[#This Row],[모병원명]:[파견종료일]],파견표[[#This Row],[파견병원]:[비고]])=0,"",IF(파견표[[#This Row],[키]]="","등록번호 없음",IF(LEFT(파견표[[#This Row],[모병원(정규화)]],1)="⚠","모병원명 미등록",IF(파견표[[#This Row],[파견병원(정규화)]]="","파견병원 입력",IF(LEFT(파견표[[#This Row],[파견병원(정규화)]],1)="⚠","파견병원명 미등록",IF(LEFT(파견표[[#This Row],[파견과목(정규화)]],1)="⚠","파견과목 미등록",IF(OR(파견표[[#This Row],[파견근거(정규화)]]="",LEFT(파견표[[#This Row],[파견근거(정규화)]],1)="⚠"),"파견근거 확인",IF(NOT(AND(ISNUMBER(파견표[[#This Row],[시작일(계산)]]),ISNUMBER(파견표[[#This Row],[종료일(계산)]]))),"날짜 형식/누락",IF(파견표[[#This Row],[종료일(계산)]]&lt;파견표[[#This Row],[시작일(계산)]],"종료일&lt;시작일","")))))))))</calculatedColumnFormula>
-    </tableColumn>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight9" showRowStripes="1"/>
-</table>
-</file>
-
-<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="명단표" displayName="명단표" ref="A1:AS9" headerRowCount="1">
-  <tableColumns count="45">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="명단표" displayName="명단표" ref="A1:AH9" headerRowCount="1">
+  <tableColumns count="34">
     <tableColumn id="1" name="번호">
       <calculatedColumnFormula>ROW()-ROW(명단표[#Headers])</calculatedColumnFormula>
     </tableColumn>
@@ -610,106 +503,73 @@
     </tableColumn>
     <tableColumn id="13" name="입사장소"/>
     <tableColumn id="14" name="현재 근무병원">
-      <calculatedColumnFormula>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(AND(명단표[[#This Row],[파견상태]]="파견중",명단표[[#This Row],[파견병원]]&lt;&gt;""),명단표[[#This Row],[파견병원]],IF(AND(명단표[[#This Row],[인턴 이번달]]&lt;&gt;"",LEFT(명단표[[#This Row],[인턴 이번달]],1)&lt;&gt;"⚠"),LEFT(명단표[[#This Row],[인턴 이번달]],FIND(" ",명단표[[#This Row],[인턴 이번달]])-1),IF(명단표[[#This Row],[근무지]]="","",_xlfn.XLOOKUP(TRIM(명단표[[#This Row],[근무지]]&amp;""),병원약칭표[표기],병원약칭표[정식 병원],명단표[[#This Row],[근무지]]&amp;"")))))</calculatedColumnFormula>
+      <calculatedColumnFormula>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(AND(명단표[[#This Row],[인턴 이번달]]&lt;&gt;"",LEFT(명단표[[#This Row],[인턴 이번달]],1)&lt;&gt;"⚠"),LEFT(명단표[[#This Row],[인턴 이번달]],FIND(" ",명단표[[#This Row],[인턴 이번달]])-1),IF(명단표[[#This Row],[구리 근무 중]]="Y","구리병원",IF(명단표[[#This Row],[근무지]]="","",_xlfn.XLOOKUP(TRIM(명단표[[#This Row],[근무지]]&amp;""),병원약칭표[표기],병원약칭표[정식 병원],명단표[[#This Row],[근무지]]&amp;"")))))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="15" name="현재 진료과">
-      <calculatedColumnFormula>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(AND(명단표[[#This Row],[파견상태]]="파견중",명단표[[#This Row],[파견병원]]&lt;&gt;""),IF(명단표[[#This Row],[파견진료과]]&lt;&gt;"",명단표[[#This Row],[파견진료과]],"파견과 미입력"),IF(AND(명단표[[#This Row],[인턴 이번달]]&lt;&gt;"",LEFT(명단표[[#This Row],[인턴 이번달]],1)&lt;&gt;"⚠"),MID(명단표[[#This Row],[인턴 이번달]],FIND(" ",명단표[[#This Row],[인턴 이번달]])+1,60),IF(명단표[[#This Row],[수련과목]]="","",IF(명단표[[#This Row],[수련과목]]="인턴","수련교육부(인턴)",명단표[[#This Row],[수련과목]])))))</calculatedColumnFormula>
+      <calculatedColumnFormula>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(AND(명단표[[#This Row],[인턴 이번달]]&lt;&gt;"",LEFT(명단표[[#This Row],[인턴 이번달]],1)&lt;&gt;"⚠"),MID(명단표[[#This Row],[인턴 이번달]],FIND(" ",명단표[[#This Row],[인턴 이번달]])+1,60),IF(명단표[[#This Row],[수련과목]]="","",IF(명단표[[#This Row],[수련과목]]="인턴","수련교육부(인턴)",명단표[[#This Row],[수련과목]]))))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" name="파견근거">
-      <calculatedColumnFormula>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(명단표[[#This Row],[다기관 기록행]]&lt;&gt;"",IF(AND(TODAY()&gt;=INDEX(파견표[다기관 시작],명단표[[#This Row],[다기관 기록행]]),OR(NOT(ISNUMBER(INDEX(파견표[다기관 종료],명단표[[#This Row],[다기관 기록행]]))),TODAY()&lt;=INDEX(파견표[다기관 종료],명단표[[#This Row],[다기관 기록행]]))),"다기관",IF(명단표[[#This Row],[파견기록행]]="","",INDEX(파견표[파견근거(정규화)],명단표[[#This Row],[파견기록행]]))),IF(명단표[[#This Row],[파견기록행]]="","",INDEX(파견표[파견근거(정규화)],명단표[[#This Row],[파견기록행]]))))</calculatedColumnFormula>
+    <tableColumn id="16" name="구리 근무 시작일(기준월)">
+      <calculatedColumnFormula>IF(명단표[[#This Row],[구리행]]="","",INDEX(구리_시작,명단표[[#This Row],[구리행]]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" name="파견병원">
-      <calculatedColumnFormula>IF(명단표[[#This Row],[파견기록행]]="","",INDEX(파견표[파견병원(정규화)],명단표[[#This Row],[파견기록행]]))</calculatedColumnFormula>
+    <tableColumn id="17" name="구리 근무 종료일(기준월)">
+      <calculatedColumnFormula>IF(명단표[[#This Row],[구리행]]="","",INDEX(구리_종료,명단표[[#This Row],[구리행]]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="18" name="파견진료과">
-      <calculatedColumnFormula>IF(명단표[[#This Row],[파견기록행]]="","",INDEX(파견표[파견과목(정규화)],명단표[[#This Row],[파견기록행]]))</calculatedColumnFormula>
+    <tableColumn id="18" name="구리독자">
+      <calculatedColumnFormula>IF(명단표[[#This Row],[구리행]]="","",INDEX(구리_독자,명단표[[#This Row],[구리행]]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" name="파견시작일">
-      <calculatedColumnFormula>IF(명단표[[#This Row],[파견기록행]]="","",INDEX(파견표[시작일(계산)],명단표[[#This Row],[파견기록행]]))</calculatedColumnFormula>
+    <tableColumn id="19" name="서울 근무일(기준월)">
+      <calculatedColumnFormula>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(명단표[[#This Row],[구리행]]&lt;&gt;"",MAX(0,DAY(EOMONTH(급여기준월,0))-N(명단표[[#This Row],[구리명단 근무일]])),IF(명단표[[#This Row],[기준월 근무병원]]="서울병원",DAY(EOMONTH(급여기준월,0)),0)))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" name="파견종료일">
-      <calculatedColumnFormula>IF(명단표[[#This Row],[파견기록행]]="","",INDEX(파견표[종료일(계산)],명단표[[#This Row],[파견기록행]]))</calculatedColumnFormula>
+    <tableColumn id="20" name="구리 근무일(기준월)">
+      <calculatedColumnFormula>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(명단표[[#This Row],[구리행]]&lt;&gt;"",N(명단표[[#This Row],[구리명단 근무일]]),IF(명단표[[#This Row],[기준월 근무병원]]="구리병원",DAY(EOMONTH(급여기준월,0)),0)))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" name="파견상태">
-      <calculatedColumnFormula>IF(명단표[[#This Row],[파견기록행]]="","",INDEX(파견표[상태],명단표[[#This Row],[파견기록행]]))</calculatedColumnFormula>
+    <tableColumn id="21" name="급여지급병원(기준월)">
+      <calculatedColumnFormula>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(명단표[[#This Row],[기준월 근무병원]]="","",IF(명단표[[#This Row],[구리행]]="",명단표[[#This Row],[기준월 근무병원]],IF(AND(명단표[[#This Row],[서울 근무일(기준월)]]&gt;=판정기준일,명단표[[#This Row],[구리 근무일(기준월)]]&lt;판정기준일),"서울병원",IF(AND(명단표[[#This Row],[구리 근무일(기준월)]]&gt;=판정기준일,명단표[[#This Row],[서울 근무일(기준월)]]&lt;판정기준일),"구리병원","⚠15일 판정불가(서울 "&amp;명단표[[#This Row],[서울 근무일(기준월)]]&amp;"일/구리 "&amp;명단표[[#This Row],[구리 근무일(기준월)]]&amp;"일)")))))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" name="파견기간(일)">
-      <calculatedColumnFormula>IF(명단표[[#This Row],[파견기록행]]="","",INDEX(파견표[파견일수(계산)],명단표[[#This Row],[파견기록행]]))</calculatedColumnFormula>
+    <tableColumn id="22" name="급여 판정 근거">
+      <calculatedColumnFormula>IF(OR(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),명단표[[#This Row],[급여지급병원(기준월)]]=""),"",IF(명단표[[#This Row],[구리행]]&lt;&gt;"","서울 "&amp;명단표[[#This Row],[서울 근무일(기준월)]]&amp;"일 / 구리 "&amp;명단표[[#This Row],[구리 근무일(기준월)]]&amp;"일 (구리 근무자명단) → 15일 이상 근무 병원 지급",IF(AND(명단표[[#This Row],[인턴 기준월]]&lt;&gt;"",LEFT(명단표[[#This Row],[인턴 기준월]],1)&lt;&gt;"⚠"),"인턴 근무계획 → 그 달 근무병원 지급","구리 근무자명단에 없음 → 소속병원 지급")))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="23" name="종료까지(일)">
-      <calculatedColumnFormula>IF(AND(명단표[[#This Row],[파견상태]]="파견중",ISNUMBER(명단표[[#This Row],[파견종료일]])),명단표[[#This Row],[파견종료일]]-TODAY(),"")</calculatedColumnFormula>
+    <tableColumn id="23" name="점검">
+      <calculatedColumnFormula>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(명단표[[#This Row],[기본자료행]]="","기본자료에 없는 사번",IF(COUNTIF(명단표[사번],명단표[[#This Row],[사번]])&gt;1,"중복 사번",IF(명단표[[#This Row],[소속병원]]="","소속(입사장소) 입력",IF(LEFT(명단표[[#This Row],[급여지급병원(기준월)]],1)="⚠","서울·구리 15일 판정 불가(양쪽 모두 이상/미만)",IF(IF(명단표[[#This Row],[인턴계획행]]="",0,N(INDEX(인턴계획표[입력오류],명단표[[#This Row],[인턴계획행]])))&gt;0,"인턴계획 입력오류 확인",IF(AND(명단표[[#This Row],[구리행]]="",COUNTIF(구리_이름,명단표[[#This Row],[이름]])&gt;0),"구리 근무자명단 연결 확인(동명이인·과 불일치)","정상")))))))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="24" name="급여기준월 파견일수">
-      <calculatedColumnFormula>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(명단표[[#This Row],[키]]="",0,SUMIFS(파견표[기준월 겹침일수],파견표[키],명단표[[#This Row],[키]])))</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="25" name="서울 근무일(기준월)">
-      <calculatedColumnFormula>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(명단표[[#This Row],[구리행]]&lt;&gt;"",MAX(0,DAY(EOMONTH(급여기준월,0))-N(명단표[[#This Row],[구리명단 근무일]])),IF(명단표[[#This Row],[키]]="",0,SUMIFS(파견표[기준월 겹침일수],파견표[키],명단표[[#This Row],[키]],파견표[파견병원(정규화)],"서울병원"))+IF(명단표[[#This Row],[기준월 근무병원]]="서울병원",MAX(0,DAY(EOMONTH(급여기준월,0))-N(명단표[[#This Row],[급여기준월 파견일수]])),0)))</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="26" name="구리 근무일(기준월)">
-      <calculatedColumnFormula>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(명단표[[#This Row],[구리행]]&lt;&gt;"",N(명단표[[#This Row],[구리명단 근무일]]),IF(명단표[[#This Row],[키]]="",0,SUMIFS(파견표[기준월 겹침일수],파견표[키],명단표[[#This Row],[키]],파견표[파견병원(정규화)],"구리병원"))+IF(명단표[[#This Row],[기준월 근무병원]]="구리병원",MAX(0,DAY(EOMONTH(급여기준월,0))-N(명단표[[#This Row],[급여기준월 파견일수]])),0)))</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="27" name="급여지급병원(기준월)">
-      <calculatedColumnFormula>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(명단표[[#This Row],[기준월 근무병원]]="","",IF(명단표[[#This Row],[다기관 겹침일수]]&gt;0,명단표[[#This Row],[소속병원]],IF(AND(N(명단표[[#This Row],[급여기준월 파견일수]])&lt;=0,명단표[[#This Row],[구리행]]=""),명단표[[#This Row],[기준월 근무병원]],IF(명단표[[#This Row],[서울 근무일(기준월)]]+명단표[[#This Row],[구리 근무일(기준월)]]=DAY(EOMONTH(급여기준월,0)),IF(AND(명단표[[#This Row],[서울 근무일(기준월)]]&gt;=판정기준일,명단표[[#This Row],[구리 근무일(기준월)]]&lt;판정기준일),"서울병원",IF(AND(명단표[[#This Row],[구리 근무일(기준월)]]&gt;=판정기준일,명단표[[#This Row],[서울 근무일(기준월)]]&lt;판정기준일),"구리병원","⚠15일 판정불가(서울 "&amp;명단표[[#This Row],[서울 근무일(기준월)]]&amp;"일/구리 "&amp;명단표[[#This Row],[구리 근무일(기준월)]]&amp;"일)")),IF(명단표[[#This Row],[기준월 대표파견행]]="",명단표[[#This Row],[소속병원]],IF(INDEX(파견표[파견근거(정규화)],명단표[[#This Row],[기준월 대표파견행]])="통합수련",INDEX(파견표[파견병원(정규화)],명단표[[#This Row],[기준월 대표파견행]]),명단표[[#This Row],[소속병원]])))))))</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="28" name="급여 판정 근거">
-      <calculatedColumnFormula>IF(OR(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),명단표[[#This Row],[급여지급병원(기준월)]]=""),"",IF(명단표[[#This Row],[다기관 겹침일수]]&gt;0,"다기관 기간 → 소속병원 지급",IF(AND(N(명단표[[#This Row],[급여기준월 파견일수]])&lt;=0,명단표[[#This Row],[구리행]]=""),"파견 없음 → 그 달 근무병원 지급",IF(명단표[[#This Row],[서울 근무일(기준월)]]+명단표[[#This Row],[구리 근무일(기준월)]]=DAY(EOMONTH(급여기준월,0)),"서울 "&amp;명단표[[#This Row],[서울 근무일(기준월)]]&amp;"일 / 구리 "&amp;명단표[[#This Row],[구리 근무일(기준월)]]&amp;"일"&amp;IF(명단표[[#This Row],[구리행]]&lt;&gt;""," (구리 근무자명단 반영)","")&amp;" → 15일 이상 근무 병원 지급","타 병원 포함 → "&amp;IF(명단표[[#This Row],[기준월 대표파견행]]="","소속",INDEX(파견표[파견근거(정규화)],명단표[[#This Row],[기준월 대표파견행]]))&amp;" 규칙"))))</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="29" name="점검">
-      <calculatedColumnFormula>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(명단표[[#This Row],[기본자료행]]="","기본자료에 없는 사번",IF(COUNTIF(명단표[사번],명단표[[#This Row],[사번]])&gt;1,"중복 사번",IF(명단표[[#This Row],[소속병원]]="","소속(입사장소) 입력",IF(IF(명단표[[#This Row],[키]]="",0,COUNTIFS(파견표[키],명단표[[#This Row],[키]],파견표[입력오류],"?*"))&gt;0,"파견수련계획 입력오류 확인",IF(LEFT(명단표[[#This Row],[급여지급병원(기준월)]],1)="⚠","서울·구리 15일 판정 불가(양쪽 모두 이상/미만)",IF(IF(명단표[[#This Row],[인턴계획행]]="",0,N(INDEX(인턴계획표[입력오류],명단표[[#This Row],[인턴계획행]])))&gt;0,"인턴계획 입력오류 확인",IF(AND(명단표[[#This Row],[구리행]]&lt;&gt;"",명단표[[#This Row],[기준월 근무병원]]&lt;&gt;"구리병원",IF(명단표[[#This Row],[키]]="",0,SUMIFS(파견표[기준월 겹침일수],파견표[키],명단표[[#This Row],[키]],파견표[파견병원(정규화)],"구리병원"))=0),"구리 근무자명단에만 있음(파견수련계획 확인)",IF(AND(명단표[[#This Row],[인턴계획행]]&lt;&gt;"",명단표[[#This Row],[파견상태]]&lt;&gt;"파견중",명단표[[#This Row],[현재 근무병원]]&lt;&gt;명단표[[#This Row],[소속병원]]),"인턴 타지역 근무: 파견 여부 확인","정상")))))))))</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="30" name="다기관(비고 기재 기간)">
-      <calculatedColumnFormula>IF(명단표[[#This Row],[다기관 기록행]]="","","다기관 "&amp;TEXT(INDEX(파견표[다기관 시작],명단표[[#This Row],[다기관 기록행]]),"yyyy-mm-dd")&amp;"~"&amp;IF(ISNUMBER(INDEX(파견표[다기관 종료],명단표[[#This Row],[다기관 기록행]])),TEXT(INDEX(파견표[다기관 종료],명단표[[#This Row],[다기관 기록행]]),"yyyy-mm-dd"),""))</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="31" name="비고"/>
-    <tableColumn id="32" name="기본자료행">
+    <tableColumn id="24" name="비고"/>
+    <tableColumn id="25" name="기본자료행">
       <calculatedColumnFormula>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IFERROR(_xlfn.XMATCH("S|"&amp;TRIM(명단표[[#This Row],[사번]]&amp;""),기본자료표[사번키]),""))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="33" name="키">
-      <calculatedColumnFormula>IF(TRIM(명단표[[#This Row],[전공의등록번호]]&amp;"")="","","R|"&amp;TRIM(명단표[[#This Row],[전공의등록번호]]&amp;""))</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="34" name="이름|과">
+    <tableColumn id="26" name="이름|과">
       <calculatedColumnFormula>IF(명단표[[#This Row],[이름]]="","",명단표[[#This Row],[이름]]&amp;"|"&amp;명단표[[#This Row],[수련과목]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="35" name="인턴계획행">
+    <tableColumn id="27" name="인턴계획행">
       <calculatedColumnFormula>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IFERROR(_xlfn.XMATCH("S|"&amp;TRIM(명단표[[#This Row],[사번]]&amp;""),인턴계획표[사번키]),""))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="36" name="인턴 이번달">
+    <tableColumn id="28" name="인턴 이번달">
       <calculatedColumnFormula>IF(OR(명단표[[#This Row],[인턴계획행]]="",인턴위치_이번=""),"",INDEX(인턴계획표[[정규화1]:[정규화6]],명단표[[#This Row],[인턴계획행]],인턴위치_이번)&amp;"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="37" name="인턴 기준월">
+    <tableColumn id="29" name="인턴 기준월">
       <calculatedColumnFormula>IF(OR(명단표[[#This Row],[인턴계획행]]="",인턴위치_기준월=""),"",INDEX(인턴계획표[[정규화1]:[정규화6]],명단표[[#This Row],[인턴계획행]],인턴위치_기준월)&amp;"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="38" name="소속병원">
-      <calculatedColumnFormula>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(명단표[[#This Row],[입사장소]]&lt;&gt;"",명단표[[#This Row],[입사장소]],IF(IF(명단표[[#This Row],[구리행]]="",FALSE,INDEX(구리_독자,명단표[[#This Row],[구리행]])="구리독자"),"구리병원",IF(명단표[[#This Row],[파견기록행]]&lt;&gt;"",_xlfn.LET(_xlpm.v_m,INDEX(파견표[모병원(정규화)],명단표[[#This Row],[파견기록행]]),IF(AND(_xlpm.v_m&lt;&gt;"",LEFT(_xlpm.v_m,1)&lt;&gt;"⚠"),_xlpm.v_m,IF(명단표[[#This Row],[근무지]]="","",_xlfn.XLOOKUP(TRIM(명단표[[#This Row],[근무지]]&amp;""),병원약칭표[표기],병원약칭표[정식 병원],명단표[[#This Row],[근무지]]&amp;"")))),IF(명단표[[#This Row],[근무지]]="","",_xlfn.XLOOKUP(TRIM(명단표[[#This Row],[근무지]]&amp;""),병원약칭표[표기],병원약칭표[정식 병원],명단표[[#This Row],[근무지]]&amp;""))))))</calculatedColumnFormula>
+    <tableColumn id="30" name="소속병원">
+      <calculatedColumnFormula>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(명단표[[#This Row],[입사장소]]&lt;&gt;"",명단표[[#This Row],[입사장소]],IF(명단표[[#This Row],[구리독자]]="구리독자","구리병원",IF(명단표[[#This Row],[근무지]]="","",_xlfn.XLOOKUP(TRIM(명단표[[#This Row],[근무지]]&amp;""),병원약칭표[표기],병원약칭표[정식 병원],명단표[[#This Row],[근무지]]&amp;"")))))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="39" name="기준월 근무병원">
+    <tableColumn id="31" name="기준월 근무병원">
       <calculatedColumnFormula>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(AND(명단표[[#This Row],[인턴 기준월]]&lt;&gt;"",LEFT(명단표[[#This Row],[인턴 기준월]],1)&lt;&gt;"⚠"),LEFT(명단표[[#This Row],[인턴 기준월]],FIND(" ",명단표[[#This Row],[인턴 기준월]])-1),명단표[[#This Row],[소속병원]]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="40" name="파견기록행">
-      <calculatedColumnFormula>IF(명단표[[#This Row],[키]]="","",IFERROR(_xlfn.XMATCH(명단표[[#This Row],[키]]&amp;"|파견중",파견표[키|상태]),IFERROR(_xlfn.XMATCH(명단표[[#This Row],[키]]&amp;"|파견예정",파견표[키|상태]),IFERROR(_xlfn.XMATCH(명단표[[#This Row],[키]]&amp;"|파견종료",파견표[키|상태]),""))))</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="41" name="기준월 대표파견행">
-      <calculatedColumnFormula>IF(명단표[[#This Row],[키]]="","",IFERROR(_xlfn.XMATCH(명단표[[#This Row],[키]]&amp;"|월",파견표[키|월]),""))</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="42" name="다기관 기록행">
-      <calculatedColumnFormula>IF(명단표[[#This Row],[키]]="","",IFERROR(_xlfn.XMATCH(명단표[[#This Row],[키]]&amp;"|다기관",파견표[키|다기관]),""))</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="43" name="다기관 겹침일수">
-      <calculatedColumnFormula>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),0,IF(명단표[[#This Row],[키]]="",0,SUMIFS(파견표[다기관 겹침일수],파견표[키],명단표[[#This Row],[키]])))</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="44" name="구리행">
+    <tableColumn id="32" name="구리행">
       <calculatedColumnFormula>IF(명단표[[#This Row],[이름]]="","",_xlfn.LET(_xlpm.v_a,_xlfn.XMATCH(명단표[[#This Row],[이름|과]],구리_키),IF(ISNUMBER(_xlpm.v_a),_xlpm.v_a,IF(AND(COUNTIF(구리_이름,명단표[[#This Row],[이름]])=1,COUNTIF(명단표[이름],명단표[[#This Row],[이름]])=1),_xlfn.XMATCH(명단표[[#This Row],[이름]],구리_이름),""))))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="45" name="구리명단 근무일">
+    <tableColumn id="33" name="구리명단 근무일">
       <calculatedColumnFormula>IF(명단표[[#This Row],[구리행]]="","",INDEX(구리_근무일,명단표[[#This Row],[구리행]]))</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="34" name="구리 근무 중">
+      <calculatedColumnFormula>IF(명단표[[#This Row],[구리행]]="","",_xlfn.LET(_xlpm.v_s,IFERROR(DATEVALUE(명단표[[#This Row],[구리 근무 시작일(기준월)]]),""),_xlpm.v_e,IFERROR(DATEVALUE(명단표[[#This Row],[구리 근무 종료일(기준월)]]),""),IF(AND(ISNUMBER(_xlpm.v_s),ISNUMBER(_xlpm.v_e)),IF(AND(TODAY()&gt;=_xlpm.v_s,TODAY()&lt;=_xlpm.v_e),"Y",""),"")))</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showRowStripes="1"/>
 </table>
 </file>
 
-<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="병원표" displayName="병원표" ref="A1:A7" headerRowCount="1">
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="병원표" displayName="병원표" ref="A1:A7" headerRowCount="1">
   <tableColumns count="1">
     <tableColumn id="1" name="병원"/>
   </tableColumns>
@@ -717,8 +577,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="진료과표" displayName="진료과표" ref="C1:C25" headerRowCount="1">
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="진료과표" displayName="진료과표" ref="C1:C25" headerRowCount="1">
   <tableColumns count="1">
     <tableColumn id="1" name="근무과"/>
   </tableColumns>
@@ -726,17 +586,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="근거표" displayName="근거표" ref="E1:E4" headerRowCount="1">
-  <tableColumns count="1">
-    <tableColumn id="1" name="파견근거"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
-</table>
-</file>
-
-<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="인턴구분표" displayName="인턴구분표" ref="G1:G5" headerRowCount="1">
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="인턴구분표" displayName="인턴구분표" ref="E1:E5" headerRowCount="1">
   <tableColumns count="1">
     <tableColumn id="1" name="인턴 구분"/>
   </tableColumns>
@@ -744,11 +595,21 @@
 </table>
 </file>
 
-<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="과약칭표" displayName="과약칭표" ref="I1:J65" headerRowCount="1">
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="과약칭표" displayName="과약칭표" ref="I1:J65" headerRowCount="1">
   <tableColumns count="2">
     <tableColumn id="1" name="약칭"/>
     <tableColumn id="2" name="정식 명칭"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="병원약칭표" displayName="병원약칭표" ref="L1:M19" headerRowCount="1">
+  <tableColumns count="2">
+    <tableColumn id="1" name="표기"/>
+    <tableColumn id="2" name="정식 병원"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
 </table>
@@ -1069,7 +930,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>• 입력_기본자료 / 입력_인턴근무계획 / 입력_파견수련계획 / 입력_전공의명단: 엑셀 '표'. 표 바로 아래(또는 첫 자료 행)에 붙여넣으면 표가 자동으로 늘어나고 초록 머리글 계산 열도 자동으로 채워집니다.</t>
+          <t>• 입력_기본자료 / 입력_인턴근무계획 / 입력_전공의명단: 엑셀 '표'. 표 바로 아래(또는 첫 자료 행)에 붙여넣으면 표가 자동으로 늘어나고 초록 머리글 계산 열도 자동으로 채워집니다.</t>
         </is>
       </c>
     </row>
@@ -1090,7 +951,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>• 설정_코드표: 병원·진료과·파견근거·인턴구분·약칭 목록(표)과 설정값(급여 기준월·15일 기준·종료 임박 기준).</t>
+          <t>• 설정_코드표: 병원·진료과·인턴구분·약칭 목록(표)과 설정값(급여 기준월·15일 기준).</t>
         </is>
       </c>
     </row>
@@ -1121,7 +982,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>• 파견수련계획: 원본 양식의 4행부터 자료 행을 A4에 (연번~비고, 추가 메모는 O열). 날짜는 날짜 또는 'YYYY.MM.DD' 글자 모두 됩니다.</t>
+          <t>• 구리 근무자명단: 구리병원 파일의 시트를 A1에 양식 그대로(1~2행 제목, 3행 머리글, 4행부터 자료). 날짜는 'YYYY.MM.DD' 글자도 됩니다.</t>
         </is>
       </c>
     </row>
@@ -1190,7 +1051,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>• 근무일: 구리 근무자명단에 있으면 그 날짜가 구리 근무일, 나머지 날은 모두 서울. 없으면 파견수련계획의 파견 기간은 파견병원, 나머지는 그 달 근무병원(소속 또는 인턴 근무계획 병원).</t>
+          <t>• 근무일: 구리 근무자명단에 있으면 그 날짜가 구리 근무일, 그 달의 나머지 날은 모두 서울 근무일입니다.</t>
         </is>
       </c>
     </row>
@@ -1204,14 +1065,14 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>• 다기관 기간(파견근거=다기관 또는 비고에 '다기관')이 걸리면 소속병원 지급. 서울·구리 외 병원이 섞이면 통합수련=파견병원, 모자=소속병원(가정).</t>
+          <t>• 구리 근무자명단에 없는 사람은 그 달 근무병원(인턴은 인턴근무계획의 병원, 그 외는 소속병원)이 지급합니다.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>• 파견이 없는 달은 그 달 근무병원이 지급합니다.</t>
+          <t>• 소속병원 = 입사장소 → (비어 있으면) 구리 근무자명단 비고 '구리독자'면 구리병원 → 기본자료 근무지 순서로 정합니다.</t>
         </is>
       </c>
     </row>
@@ -1245,335 +1106,6 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00548235"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:X6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="17" customWidth="1" min="6" max="6"/>
-    <col width="17" customWidth="1" min="7" max="7"/>
-    <col width="17" customWidth="1" min="8" max="8"/>
-    <col width="17" customWidth="1" min="9" max="9"/>
-    <col width="17" customWidth="1" min="10" max="10"/>
-    <col width="17" customWidth="1" min="11" max="11"/>
-    <col width="17" customWidth="1" min="12" max="12"/>
-    <col width="17" customWidth="1" min="13" max="13"/>
-    <col width="17" customWidth="1" min="14" max="14"/>
-    <col width="17" customWidth="1" min="15" max="15"/>
-    <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="3" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="10" customWidth="1" min="19" max="19"/>
-    <col width="10" customWidth="1" min="20" max="20"/>
-    <col width="10" customWidth="1" min="21" max="21"/>
-    <col width="10" customWidth="1" min="22" max="22"/>
-    <col width="10" customWidth="1" min="23" max="23"/>
-    <col width="10" customWidth="1" min="24" max="24"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>인턴 근무 현황</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>기준일</t>
-        </is>
-      </c>
-      <c r="B2" s="27">
-        <f>TODAY()</f>
-        <v/>
-      </c>
-      <c r="J2" s="12" t="inlineStr">
-        <is>
-          <t>급여 기준월 위치→</t>
-        </is>
-      </c>
-      <c r="K2" s="28">
-        <f>IFERROR(MATCH(MONTH(급여기준월),$J$3:$O$3,0),"")</f>
-        <v/>
-      </c>
-      <c r="R2" s="3" t="inlineStr">
-        <is>
-          <t>월별 병원별 인턴 인원</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="12" t="inlineStr">
-        <is>
-          <t>계획 월 번호(자동)</t>
-        </is>
-      </c>
-      <c r="F3" s="12" t="inlineStr">
-        <is>
-          <t>이번/다음 달 위치→</t>
-        </is>
-      </c>
-      <c r="G3" s="28">
-        <f>IFERROR(MATCH(MONTH(TODAY()),$J$3:$O$3,0),"")</f>
-        <v/>
-      </c>
-      <c r="I3" s="28">
-        <f>IFERROR(MATCH(MONTH(EDATE(TODAY(),1)),$J$3:$O$3,0),"")</f>
-        <v/>
-      </c>
-      <c r="J3" s="28">
-        <f>IFERROR(VALUE(SUBSTITUTE(TRIM(J5),"월","")),"")</f>
-        <v/>
-      </c>
-      <c r="K3" s="28">
-        <f>IFERROR(VALUE(SUBSTITUTE(TRIM(K5),"월","")),"")</f>
-        <v/>
-      </c>
-      <c r="L3" s="28">
-        <f>IFERROR(VALUE(SUBSTITUTE(TRIM(L5),"월","")),"")</f>
-        <v/>
-      </c>
-      <c r="M3" s="28">
-        <f>IFERROR(VALUE(SUBSTITUTE(TRIM(M5),"월","")),"")</f>
-        <v/>
-      </c>
-      <c r="N3" s="28">
-        <f>IFERROR(VALUE(SUBSTITUTE(TRIM(N5),"월","")),"")</f>
-        <v/>
-      </c>
-      <c r="O3" s="28">
-        <f>IFERROR(VALUE(SUBSTITUTE(TRIM(O5),"월","")),"")</f>
-        <v/>
-      </c>
-      <c r="R3" s="4" t="inlineStr">
-        <is>
-          <t>병원</t>
-        </is>
-      </c>
-      <c r="S3" s="4">
-        <f>J5</f>
-        <v/>
-      </c>
-      <c r="T3" s="4">
-        <f>K5</f>
-        <v/>
-      </c>
-      <c r="U3" s="4">
-        <f>L5</f>
-        <v/>
-      </c>
-      <c r="V3" s="4">
-        <f>M5</f>
-        <v/>
-      </c>
-      <c r="W3" s="4">
-        <f>N5</f>
-        <v/>
-      </c>
-      <c r="X3" s="4">
-        <f>O5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4">
-      <c r="R4" s="29" t="inlineStr">
-        <is>
-          <t>합계(배정)</t>
-        </is>
-      </c>
-      <c r="S4" s="21">
-        <f>COUNTIF(인턴계획표[정규화1],"?*")</f>
-        <v/>
-      </c>
-      <c r="T4" s="21">
-        <f>COUNTIF(인턴계획표[정규화2],"?*")</f>
-        <v/>
-      </c>
-      <c r="U4" s="21">
-        <f>COUNTIF(인턴계획표[정규화3],"?*")</f>
-        <v/>
-      </c>
-      <c r="V4" s="21">
-        <f>COUNTIF(인턴계획표[정규화4],"?*")</f>
-        <v/>
-      </c>
-      <c r="W4" s="21">
-        <f>COUNTIF(인턴계획표[정규화5],"?*")</f>
-        <v/>
-      </c>
-      <c r="X4" s="21">
-        <f>COUNTIF(인턴계획표[정규화6],"?*")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>순번</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>이름</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>사번</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>기본자료 확인</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>입사일</t>
-        </is>
-      </c>
-      <c r="F5" s="4">
-        <f>"이번 달("&amp;IF($G$3="","계획 외",MONTH(TODAY())&amp;"월")&amp;") 병원"</f>
-        <v/>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>이번 달 진료과</t>
-        </is>
-      </c>
-      <c r="H5" s="4">
-        <f>"다음 달("&amp;IF($I$3="","계획 외",MONTH(EDATE(TODAY(),1))&amp;"월")&amp;") 병원"</f>
-        <v/>
-      </c>
-      <c r="I5" s="4" t="inlineStr">
-        <is>
-          <t>다음 달 진료과</t>
-        </is>
-      </c>
-      <c r="J5" s="4">
-        <f>TRIM(INDEX(인턴계획표[#Headers],1,4)&amp;"")</f>
-        <v/>
-      </c>
-      <c r="K5" s="4">
-        <f>TRIM(INDEX(인턴계획표[#Headers],1,5)&amp;"")</f>
-        <v/>
-      </c>
-      <c r="L5" s="4">
-        <f>TRIM(INDEX(인턴계획표[#Headers],1,6)&amp;"")</f>
-        <v/>
-      </c>
-      <c r="M5" s="4">
-        <f>TRIM(INDEX(인턴계획표[#Headers],1,7)&amp;"")</f>
-        <v/>
-      </c>
-      <c r="N5" s="4">
-        <f>TRIM(INDEX(인턴계획표[#Headers],1,8)&amp;"")</f>
-        <v/>
-      </c>
-      <c r="O5" s="4">
-        <f>TRIM(INDEX(인턴계획표[#Headers],1,9)&amp;"")</f>
-        <v/>
-      </c>
-      <c r="P5" s="4" t="inlineStr">
-        <is>
-          <t>입력오류</t>
-        </is>
-      </c>
-      <c r="R5" s="29" t="inlineStr">
-        <is>
-          <t>⚠ 오류</t>
-        </is>
-      </c>
-      <c r="S5" s="21">
-        <f>COUNTIF(인턴계획표[정규화1],"⚠*")</f>
-        <v/>
-      </c>
-      <c r="T5" s="21">
-        <f>COUNTIF(인턴계획표[정규화2],"⚠*")</f>
-        <v/>
-      </c>
-      <c r="U5" s="21">
-        <f>COUNTIF(인턴계획표[정규화3],"⚠*")</f>
-        <v/>
-      </c>
-      <c r="V5" s="21">
-        <f>COUNTIF(인턴계획표[정규화4],"⚠*")</f>
-        <v/>
-      </c>
-      <c r="W5" s="21">
-        <f>COUNTIF(인턴계획표[정규화5],"⚠*")</f>
-        <v/>
-      </c>
-      <c r="X5" s="21">
-        <f>COUNTIF(인턴계획표[정규화6],"⚠*")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" cm="1">
-        <f t="array" ref="A6">_xlfn.LET(_xlpm.v_n,TRIM(인턴계획표[이름]&amp;""),_xlpm.v_x,_xlpm.v_n&lt;&gt;"",_xlpm.v_c,IF($G$3="","",INDEX(인턴계획표[[정규화1]:[정규화6]],0,$G$3)&amp;""),_xlpm.v_t,IF($I$3="","",INDEX(인턴계획표[[정규화1]:[정규화6]],0,$I$3)&amp;""),_xlpm.v_ok,IF(ISNUMBER(_xlfn.XMATCH(인턴계획표[사번키],기본자료표[사번키])),"확인","미등록"),_xlpm.v_in,IF(ISNUMBER(인턴계획표[입사일(비고)]),TEXT(인턴계획표[입사일(비고)],"yyyy-mm-dd"),인턴계획표[입사일(비고)]&amp;""),IF(SUM(--_xlpm.v_x)=0,"인턴 계획 없음",_xlfn._xlws.FILTER(CHOOSE({1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16},인턴계획표[순번]&amp;"",_xlpm.v_n,인턴계획표[사번]&amp;"",_xlpm.v_ok,_xlpm.v_in,IF(_xlpm.v_c="","",IF(LEFT(_xlpm.v_c,1)="⚠",_xlpm.v_c,IFERROR(LEFT(_xlpm.v_c,FIND(" ",_xlpm.v_c)-1),_xlpm.v_c))),IF(_xlpm.v_c="","",IF(LEFT(_xlpm.v_c,1)="⚠","",IFERROR(MID(_xlpm.v_c,FIND(" ",_xlpm.v_c)+1,60),""))),IF(_xlpm.v_t="","",IF(LEFT(_xlpm.v_t,1)="⚠",_xlpm.v_t,IFERROR(LEFT(_xlpm.v_t,FIND(" ",_xlpm.v_t)-1),_xlpm.v_t))),IF(_xlpm.v_t="","",IF(LEFT(_xlpm.v_t,1)="⚠","",IFERROR(MID(_xlpm.v_t,FIND(" ",_xlpm.v_t)+1,60),""))),인턴계획표[정규화1],인턴계획표[정규화2],인턴계획표[정규화3],인턴계획표[정규화4],인턴계획표[정규화5],인턴계획표[정규화6],인턴계획표[입력오류]),_xlpm.v_x)))</f>
-        <v/>
-      </c>
-      <c r="R6" cm="1">
-        <f t="array" ref="R6">병원표[병원]</f>
-        <v/>
-      </c>
-      <c r="S6" cm="1">
-        <f t="array" ref="S6">COUNTIF(인턴계획표[정규화1],병원표[병원]&amp;" *")</f>
-        <v/>
-      </c>
-      <c r="T6" cm="1">
-        <f t="array" ref="T6">COUNTIF(인턴계획표[정규화2],병원표[병원]&amp;" *")</f>
-        <v/>
-      </c>
-      <c r="U6" cm="1">
-        <f t="array" ref="U6">COUNTIF(인턴계획표[정규화3],병원표[병원]&amp;" *")</f>
-        <v/>
-      </c>
-      <c r="V6" cm="1">
-        <f t="array" ref="V6">COUNTIF(인턴계획표[정규화4],병원표[병원]&amp;" *")</f>
-        <v/>
-      </c>
-      <c r="W6" cm="1">
-        <f t="array" ref="W6">COUNTIF(인턴계획표[정규화5],병원표[병원]&amp;" *")</f>
-        <v/>
-      </c>
-      <c r="X6" cm="1">
-        <f t="array" ref="X6">COUNTIF(인턴계획표[정규화6],병원표[병원]&amp;" *")</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="D6:D20005">
-    <cfRule type="expression" priority="1" dxfId="0">
-      <formula>$D6="미등록"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J6:O20005">
-    <cfRule type="expression" priority="2" dxfId="11">
-      <formula>LEFT(J6,1)="⚠"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J5:O20005">
-    <cfRule type="expression" priority="3" dxfId="9">
-      <formula>J$3=MONTH(TODAY())</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="007F7F7F"/>
@@ -1589,7 +1121,7 @@
     <col width="3" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="3" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="3" customWidth="1" min="7" max="7"/>
     <col width="3" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
@@ -1614,11 +1146,6 @@
       </c>
       <c r="E1" s="4" t="inlineStr">
         <is>
-          <t>파견근거</t>
-        </is>
-      </c>
-      <c r="G1" s="4" t="inlineStr">
-        <is>
           <t>인턴 구분</t>
         </is>
       </c>
@@ -1661,11 +1188,6 @@
       </c>
       <c r="E2" s="6" t="inlineStr">
         <is>
-          <t>모자</t>
-        </is>
-      </c>
-      <c r="G2" s="6" t="inlineStr">
-        <is>
           <t>통합</t>
         </is>
       </c>
@@ -1691,7 +1213,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>※ 병원약칭표(L~M): 인턴근무계획의 지역 단어, 파견수련계획의 모병원명·파견병원을 정식 병원으로 바꿉니다. 실제 기관명은 여기에 추가하세요.</t>
+          <t>※ 병원약칭표(L~M): 인턴근무계획의 지역 단어와 기본자료의 근무지를 정식 병원으로 바꿉니다. 실제 기관명은 여기에 추가하세요.</t>
         </is>
       </c>
     </row>
@@ -1708,11 +1230,6 @@
       </c>
       <c r="E3" s="6" t="inlineStr">
         <is>
-          <t>통합수련</t>
-        </is>
-      </c>
-      <c r="G3" s="6" t="inlineStr">
-        <is>
           <t>핵/방</t>
         </is>
       </c>
@@ -1738,7 +1255,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>※ 과약칭표(I~J): 인턴근무계획 월 칸의 마지막 단어, 파견수련계획의 파견과목을 정식 명칭으로 바꿉니다.</t>
+          <t>※ 과약칭표(I~J): 인턴근무계획 월 칸의 마지막 단어(진료과 약칭)를 정식 명칭으로 바꿉니다.</t>
         </is>
       </c>
     </row>
@@ -1755,11 +1272,6 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>다기관</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
           <t>직/피</t>
         </is>
       </c>
@@ -1785,7 +1297,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>※ 인턴구분표(G): 통합(과 미지정), 핵/방, 직/피, 정/영처럼 인턴 순환에만 쓰는 구분입니다.</t>
+          <t>※ 인턴구분표(E): 통합(과 미지정), 핵/방, 직/피, 정/영처럼 인턴 순환에만 쓰는 구분입니다.</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1312,7 @@
           <t>정신건강의학과</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>정/영</t>
         </is>
@@ -1953,12 +1465,12 @@
           <t>인천병원</t>
         </is>
       </c>
-      <c r="O9" s="29" t="inlineStr">
+      <c r="O9" s="28" t="inlineStr">
         <is>
           <t>급여 기준월(1일)</t>
         </is>
       </c>
-      <c r="P9" s="30">
+      <c r="P9" s="29">
         <f>DATE(YEAR(TODAY()),MONTH(TODAY()),1)</f>
         <v/>
       </c>
@@ -1989,12 +1501,12 @@
           <t>구리병원</t>
         </is>
       </c>
-      <c r="O10" s="29" t="inlineStr">
+      <c r="O10" s="28" t="inlineStr">
         <is>
           <t>서울·구리 15일 기준(일)</t>
         </is>
       </c>
-      <c r="P10" s="31" t="n">
+      <c r="P10" s="30" t="n">
         <v>15</v>
       </c>
     </row>
@@ -2024,13 +1536,10 @@
           <t>창원병원</t>
         </is>
       </c>
-      <c r="O11" s="29" t="inlineStr">
-        <is>
-          <t>종료 임박 기준(일)</t>
-        </is>
-      </c>
-      <c r="P11" s="31" t="n">
-        <v>30</v>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>※ 급여 기준월: 다른 달을 보려면 그 달 1일 날짜를 입력(기본 수식 = 이번 달 1일).</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -2059,11 +1568,7 @@
           <t>제주병원</t>
         </is>
       </c>
-      <c r="O12" s="12" t="inlineStr">
-        <is>
-          <t>※ 급여 기준월: 다른 달을 보려면 그 달 1일 날짜를 입력(기본 수식 = 이번 달 1일).</t>
-        </is>
-      </c>
+      <c r="O12" s="16" t="n"/>
     </row>
     <row r="13">
       <c r="C13" s="6" t="inlineStr">
@@ -2838,13 +2343,12 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="6">
+  <tableParts count="5">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
   </tableParts>
 </worksheet>
 </file>
@@ -3806,1142 +3310,6 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="002F5597"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AF10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="7" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="13" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
-    <col width="26" customWidth="1" min="15" max="15"/>
-    <col width="11" customWidth="1" min="16" max="16"/>
-    <col width="11" customWidth="1" min="17" max="17"/>
-    <col width="11" customWidth="1" min="18" max="18"/>
-    <col width="11" customWidth="1" min="19" max="19"/>
-    <col width="11" customWidth="1" min="20" max="20"/>
-    <col width="10" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="8" customWidth="1" min="23" max="23"/>
-    <col width="9" customWidth="1" min="24" max="24"/>
-    <col width="9" customWidth="1" min="25" max="25"/>
-    <col width="16" customWidth="1" min="26" max="26"/>
-    <col width="14" customWidth="1" min="27" max="27"/>
-    <col width="11" customWidth="1" min="28" max="28"/>
-    <col width="11" customWidth="1" min="29" max="29"/>
-    <col width="9" customWidth="1" min="30" max="30"/>
-    <col width="14" customWidth="1" min="31" max="31"/>
-    <col width="18" customWidth="1" min="32" max="32"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>파견 수련계획</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="12" t="inlineStr">
-        <is>
-          <t>※ 파견수련계획 양식의 '자료 행'(4행부터)을 복사해 이 표의 첫 칸(A4)에 붙여넣으세요. 표가 자동으로 늘어납니다. 초록 머리글 열은 자동 계산이므로 비워 둡니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>연번</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>모병원명</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>수련종별(I/R)</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>수련과목</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>연차</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>성명</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>전공의등록번호</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>파견시작일</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>파견종료일</t>
-        </is>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>파견일수</t>
-        </is>
-      </c>
-      <c r="K3" s="4" t="inlineStr">
-        <is>
-          <t>파견병원</t>
-        </is>
-      </c>
-      <c r="L3" s="4" t="inlineStr">
-        <is>
-          <t>파견과목</t>
-        </is>
-      </c>
-      <c r="M3" s="4" t="inlineStr">
-        <is>
-          <t>파견근거(모자/통합수련)</t>
-        </is>
-      </c>
-      <c r="N3" s="4" t="inlineStr">
-        <is>
-          <t>비고</t>
-        </is>
-      </c>
-      <c r="O3" s="4" t="inlineStr">
-        <is>
-          <t>추가메모</t>
-        </is>
-      </c>
-      <c r="P3" s="5" t="inlineStr">
-        <is>
-          <t>키</t>
-        </is>
-      </c>
-      <c r="Q3" s="5" t="inlineStr">
-        <is>
-          <t>시작일(계산)</t>
-        </is>
-      </c>
-      <c r="R3" s="5" t="inlineStr">
-        <is>
-          <t>종료일(계산)</t>
-        </is>
-      </c>
-      <c r="S3" s="5" t="inlineStr">
-        <is>
-          <t>모병원(정규화)</t>
-        </is>
-      </c>
-      <c r="T3" s="5" t="inlineStr">
-        <is>
-          <t>파견병원(정규화)</t>
-        </is>
-      </c>
-      <c r="U3" s="5" t="inlineStr">
-        <is>
-          <t>파견근거(정규화)</t>
-        </is>
-      </c>
-      <c r="V3" s="5" t="inlineStr">
-        <is>
-          <t>파견과목(정규화)</t>
-        </is>
-      </c>
-      <c r="W3" s="5" t="inlineStr">
-        <is>
-          <t>파견일수(계산)</t>
-        </is>
-      </c>
-      <c r="X3" s="5" t="inlineStr">
-        <is>
-          <t>기준월 겹침일수</t>
-        </is>
-      </c>
-      <c r="Y3" s="5" t="inlineStr">
-        <is>
-          <t>상태</t>
-        </is>
-      </c>
-      <c r="Z3" s="5" t="inlineStr">
-        <is>
-          <t>키|상태</t>
-        </is>
-      </c>
-      <c r="AA3" s="5" t="inlineStr">
-        <is>
-          <t>키|월</t>
-        </is>
-      </c>
-      <c r="AB3" s="5" t="inlineStr">
-        <is>
-          <t>다기관 시작</t>
-        </is>
-      </c>
-      <c r="AC3" s="5" t="inlineStr">
-        <is>
-          <t>다기관 종료</t>
-        </is>
-      </c>
-      <c r="AD3" s="5" t="inlineStr">
-        <is>
-          <t>다기관 겹침일수</t>
-        </is>
-      </c>
-      <c r="AE3" s="5" t="inlineStr">
-        <is>
-          <t>키|다기관</t>
-        </is>
-      </c>
-      <c r="AF3" s="5" t="inlineStr">
-        <is>
-          <t>입력오류</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>한양대학교병원</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>내과</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>박ㅇㅇ</t>
-        </is>
-      </c>
-      <c r="G4" s="7" t="inlineStr">
-        <is>
-          <t>21-1111</t>
-        </is>
-      </c>
-      <c r="H4" s="13" t="n">
-        <v>46144</v>
-      </c>
-      <c r="I4" s="13" t="n">
-        <v>46265</v>
-      </c>
-      <c r="J4" s="6" t="n"/>
-      <c r="K4" s="6" t="inlineStr">
-        <is>
-          <t>한양대구리병원</t>
-        </is>
-      </c>
-      <c r="L4" s="6" t="inlineStr">
-        <is>
-          <t>내과</t>
-        </is>
-      </c>
-      <c r="M4" s="6" t="inlineStr">
-        <is>
-          <t>모자</t>
-        </is>
-      </c>
-      <c r="N4" s="6" t="n"/>
-      <c r="O4" s="6" t="inlineStr">
-        <is>
-          <t>2026.09.01-2026.09.30 다기관 파견</t>
-        </is>
-      </c>
-      <c r="P4" s="8">
-        <f>IF(TRIM(파견표[[#This Row],[전공의등록번호]]&amp;"")="","","R|"&amp;TRIM(파견표[[#This Row],[전공의등록번호]]&amp;""))</f>
-        <v/>
-      </c>
-      <c r="Q4" s="10">
-        <f>_xlfn.LET(_xlpm.v_x,파견표[[#This Row],[파견시작일]],IF(ISNUMBER(_xlpm.v_x),_xlpm.v_x,IF(TRIM(_xlpm.v_x&amp;"")="","",IFERROR(DATE(VALUE(LEFT(_xlpm.v_x,4)),VALUE(MID(_xlpm.v_x,6,2)),VALUE(MID(_xlpm.v_x,9,2))),"⚠"&amp;_xlpm.v_x))))</f>
-        <v/>
-      </c>
-      <c r="R4" s="10">
-        <f>_xlfn.LET(_xlpm.v_x,파견표[[#This Row],[파견종료일]],IF(ISNUMBER(_xlpm.v_x),_xlpm.v_x,IF(TRIM(_xlpm.v_x&amp;"")="","",IFERROR(DATE(VALUE(LEFT(_xlpm.v_x,4)),VALUE(MID(_xlpm.v_x,6,2)),VALUE(MID(_xlpm.v_x,9,2))),"⚠"&amp;_xlpm.v_x))))</f>
-        <v/>
-      </c>
-      <c r="S4" s="8">
-        <f>_xlfn.LET(_xlpm.v_x,TRIM(파견표[[#This Row],[모병원명]]&amp;""),IF(_xlpm.v_x="","",_xlfn.XLOOKUP(_xlpm.v_x,병원약칭표[표기],병원약칭표[정식 병원],"⚠"&amp;_xlpm.v_x)))</f>
-        <v/>
-      </c>
-      <c r="T4" s="8">
-        <f>_xlfn.LET(_xlpm.v_x,TRIM(파견표[[#This Row],[파견병원]]&amp;""),IF(_xlpm.v_x="","",_xlfn.XLOOKUP(_xlpm.v_x,병원약칭표[표기],병원약칭표[정식 병원],"⚠"&amp;_xlpm.v_x)))</f>
-        <v/>
-      </c>
-      <c r="U4" s="8">
-        <f>_xlfn.LET(_xlpm.v_x,TRIM(파견표[[#This Row],[파견근거(모자/통합수련)]]&amp;""),IF(_xlpm.v_x="","",_xlfn.XLOOKUP(_xlpm.v_x,근거표[파견근거],근거표[파견근거],"⚠"&amp;_xlpm.v_x)))</f>
-        <v/>
-      </c>
-      <c r="V4" s="8">
-        <f>_xlfn.LET(_xlpm.v_x,TRIM(파견표[[#This Row],[파견과목]]&amp;""),IF(_xlpm.v_x="","",_xlfn.XLOOKUP(_xlpm.v_x,과약칭표[약칭],과약칭표[정식 명칭],"⚠"&amp;_xlpm.v_x)))</f>
-        <v/>
-      </c>
-      <c r="W4" s="11">
-        <f>IF(AND(ISNUMBER(파견표[[#This Row],[시작일(계산)]]),ISNUMBER(파견표[[#This Row],[종료일(계산)]])),파견표[[#This Row],[종료일(계산)]]-파견표[[#This Row],[시작일(계산)]]+1,"")</f>
-        <v/>
-      </c>
-      <c r="X4" s="11">
-        <f>IF(ISNUMBER(파견표[[#This Row],[시작일(계산)]]),MAX(0,MIN(IF(ISNUMBER(파견표[[#This Row],[종료일(계산)]]),파견표[[#This Row],[종료일(계산)]],EOMONTH(급여기준월,0)),EOMONTH(급여기준월,0))-MAX(파견표[[#This Row],[시작일(계산)]],급여기준월)+1),0)</f>
-        <v/>
-      </c>
-      <c r="Y4" s="8">
-        <f>IF(OR(NOT(ISNUMBER(파견표[[#This Row],[시작일(계산)]])),파견표[[#This Row],[키]]=""),"",IF(TODAY()&lt;파견표[[#This Row],[시작일(계산)]],"파견예정",IF(AND(ISNUMBER(파견표[[#This Row],[종료일(계산)]]),TODAY()&gt;파견표[[#This Row],[종료일(계산)]]),"파견종료","파견중")))</f>
-        <v/>
-      </c>
-      <c r="Z4" s="8">
-        <f>IF(OR(파견표[[#This Row],[키]]="",파견표[[#This Row],[상태]]=""),"",파견표[[#This Row],[키]]&amp;"|"&amp;파견표[[#This Row],[상태]])</f>
-        <v/>
-      </c>
-      <c r="AA4" s="8">
-        <f>IF(AND(파견표[[#This Row],[키]]&lt;&gt;"",파견표[[#This Row],[기준월 겹침일수]]&gt;0),파견표[[#This Row],[키]]&amp;"|월","")</f>
-        <v/>
-      </c>
-      <c r="AB4" s="10">
-        <f>_xlfn.LET(_xlpm.v_n,TRIM(파견표[[#This Row],[비고]]&amp;" "&amp;파견표[[#This Row],[추가메모]]),IF(ISNUMBER(SEARCH("다기관",_xlpm.v_n)),IFERROR(DATE(VALUE(MID(_xlpm.v_n,1,4)),VALUE(MID(_xlpm.v_n,6,2)),VALUE(MID(_xlpm.v_n,9,2))),IF(ISNUMBER(파견표[[#This Row],[시작일(계산)]]),파견표[[#This Row],[시작일(계산)]],"")),""))</f>
-        <v/>
-      </c>
-      <c r="AC4" s="10">
-        <f>_xlfn.LET(_xlpm.v_n,TRIM(파견표[[#This Row],[비고]]&amp;" "&amp;파견표[[#This Row],[추가메모]]),IF(ISNUMBER(SEARCH("다기관",_xlpm.v_n)),IFERROR(DATE(VALUE(MID(_xlpm.v_n,12,4)),VALUE(MID(_xlpm.v_n,17,2)),VALUE(MID(_xlpm.v_n,20,2))),IF(ISNUMBER(파견표[[#This Row],[종료일(계산)]]),파견표[[#This Row],[종료일(계산)]],"")),""))</f>
-        <v/>
-      </c>
-      <c r="AD4" s="11">
-        <f>IF(AND(ISNUMBER(파견표[[#This Row],[다기관 시작]]),ISNUMBER(파견표[[#This Row],[다기관 종료]])),MAX(0,MIN(파견표[[#This Row],[다기관 종료]],EOMONTH(급여기준월,0))-MAX(파견표[[#This Row],[다기관 시작]],급여기준월)+1),0)</f>
-        <v/>
-      </c>
-      <c r="AE4" s="8">
-        <f>IF(AND(파견표[[#This Row],[키]]&lt;&gt;"",ISNUMBER(파견표[[#This Row],[다기관 시작]])),파견표[[#This Row],[키]]&amp;"|다기관","")</f>
-        <v/>
-      </c>
-      <c r="AF4" s="8">
-        <f>IF(COUNTA(파견표[[#This Row],[모병원명]:[파견종료일]],파견표[[#This Row],[파견병원]:[비고]])=0,"",IF(파견표[[#This Row],[키]]="","등록번호 없음",IF(LEFT(파견표[[#This Row],[모병원(정규화)]],1)="⚠","모병원명 미등록",IF(파견표[[#This Row],[파견병원(정규화)]]="","파견병원 입력",IF(LEFT(파견표[[#This Row],[파견병원(정규화)]],1)="⚠","파견병원명 미등록",IF(LEFT(파견표[[#This Row],[파견과목(정규화)]],1)="⚠","파견과목 미등록",IF(OR(파견표[[#This Row],[파견근거(정규화)]]="",LEFT(파견표[[#This Row],[파견근거(정규화)]],1)="⚠"),"파견근거 확인",IF(NOT(AND(ISNUMBER(파견표[[#This Row],[시작일(계산)]]),ISNUMBER(파견표[[#This Row],[종료일(계산)]]))),"날짜 형식/누락",IF(파견표[[#This Row],[종료일(계산)]]&lt;파견표[[#This Row],[시작일(계산)]],"종료일&lt;시작일","")))))))))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>한양대학교병원</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>내과</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>박ㅇㅇ</t>
-        </is>
-      </c>
-      <c r="G5" s="7" t="inlineStr">
-        <is>
-          <t>21-1111</t>
-        </is>
-      </c>
-      <c r="H5" s="13" t="n">
-        <v>46296</v>
-      </c>
-      <c r="I5" s="13" t="n">
-        <v>46326</v>
-      </c>
-      <c r="J5" s="6" t="n"/>
-      <c r="K5" s="6" t="inlineStr">
-        <is>
-          <t>한양대구리병원</t>
-        </is>
-      </c>
-      <c r="L5" s="6" t="inlineStr">
-        <is>
-          <t>내과</t>
-        </is>
-      </c>
-      <c r="M5" s="6" t="inlineStr">
-        <is>
-          <t>모자</t>
-        </is>
-      </c>
-      <c r="N5" s="6" t="n"/>
-      <c r="O5" s="6" t="n"/>
-      <c r="P5" s="8">
-        <f>IF(TRIM(파견표[[#This Row],[전공의등록번호]]&amp;"")="","","R|"&amp;TRIM(파견표[[#This Row],[전공의등록번호]]&amp;""))</f>
-        <v/>
-      </c>
-      <c r="Q5" s="10">
-        <f>_xlfn.LET(_xlpm.v_x,파견표[[#This Row],[파견시작일]],IF(ISNUMBER(_xlpm.v_x),_xlpm.v_x,IF(TRIM(_xlpm.v_x&amp;"")="","",IFERROR(DATE(VALUE(LEFT(_xlpm.v_x,4)),VALUE(MID(_xlpm.v_x,6,2)),VALUE(MID(_xlpm.v_x,9,2))),"⚠"&amp;_xlpm.v_x))))</f>
-        <v/>
-      </c>
-      <c r="R5" s="10">
-        <f>_xlfn.LET(_xlpm.v_x,파견표[[#This Row],[파견종료일]],IF(ISNUMBER(_xlpm.v_x),_xlpm.v_x,IF(TRIM(_xlpm.v_x&amp;"")="","",IFERROR(DATE(VALUE(LEFT(_xlpm.v_x,4)),VALUE(MID(_xlpm.v_x,6,2)),VALUE(MID(_xlpm.v_x,9,2))),"⚠"&amp;_xlpm.v_x))))</f>
-        <v/>
-      </c>
-      <c r="S5" s="8">
-        <f>_xlfn.LET(_xlpm.v_x,TRIM(파견표[[#This Row],[모병원명]]&amp;""),IF(_xlpm.v_x="","",_xlfn.XLOOKUP(_xlpm.v_x,병원약칭표[표기],병원약칭표[정식 병원],"⚠"&amp;_xlpm.v_x)))</f>
-        <v/>
-      </c>
-      <c r="T5" s="8">
-        <f>_xlfn.LET(_xlpm.v_x,TRIM(파견표[[#This Row],[파견병원]]&amp;""),IF(_xlpm.v_x="","",_xlfn.XLOOKUP(_xlpm.v_x,병원약칭표[표기],병원약칭표[정식 병원],"⚠"&amp;_xlpm.v_x)))</f>
-        <v/>
-      </c>
-      <c r="U5" s="8">
-        <f>_xlfn.LET(_xlpm.v_x,TRIM(파견표[[#This Row],[파견근거(모자/통합수련)]]&amp;""),IF(_xlpm.v_x="","",_xlfn.XLOOKUP(_xlpm.v_x,근거표[파견근거],근거표[파견근거],"⚠"&amp;_xlpm.v_x)))</f>
-        <v/>
-      </c>
-      <c r="V5" s="8">
-        <f>_xlfn.LET(_xlpm.v_x,TRIM(파견표[[#This Row],[파견과목]]&amp;""),IF(_xlpm.v_x="","",_xlfn.XLOOKUP(_xlpm.v_x,과약칭표[약칭],과약칭표[정식 명칭],"⚠"&amp;_xlpm.v_x)))</f>
-        <v/>
-      </c>
-      <c r="W5" s="11">
-        <f>IF(AND(ISNUMBER(파견표[[#This Row],[시작일(계산)]]),ISNUMBER(파견표[[#This Row],[종료일(계산)]])),파견표[[#This Row],[종료일(계산)]]-파견표[[#This Row],[시작일(계산)]]+1,"")</f>
-        <v/>
-      </c>
-      <c r="X5" s="11">
-        <f>IF(ISNUMBER(파견표[[#This Row],[시작일(계산)]]),MAX(0,MIN(IF(ISNUMBER(파견표[[#This Row],[종료일(계산)]]),파견표[[#This Row],[종료일(계산)]],EOMONTH(급여기준월,0)),EOMONTH(급여기준월,0))-MAX(파견표[[#This Row],[시작일(계산)]],급여기준월)+1),0)</f>
-        <v/>
-      </c>
-      <c r="Y5" s="8">
-        <f>IF(OR(NOT(ISNUMBER(파견표[[#This Row],[시작일(계산)]])),파견표[[#This Row],[키]]=""),"",IF(TODAY()&lt;파견표[[#This Row],[시작일(계산)]],"파견예정",IF(AND(ISNUMBER(파견표[[#This Row],[종료일(계산)]]),TODAY()&gt;파견표[[#This Row],[종료일(계산)]]),"파견종료","파견중")))</f>
-        <v/>
-      </c>
-      <c r="Z5" s="8">
-        <f>IF(OR(파견표[[#This Row],[키]]="",파견표[[#This Row],[상태]]=""),"",파견표[[#This Row],[키]]&amp;"|"&amp;파견표[[#This Row],[상태]])</f>
-        <v/>
-      </c>
-      <c r="AA5" s="8">
-        <f>IF(AND(파견표[[#This Row],[키]]&lt;&gt;"",파견표[[#This Row],[기준월 겹침일수]]&gt;0),파견표[[#This Row],[키]]&amp;"|월","")</f>
-        <v/>
-      </c>
-      <c r="AB5" s="10">
-        <f>_xlfn.LET(_xlpm.v_n,TRIM(파견표[[#This Row],[비고]]&amp;" "&amp;파견표[[#This Row],[추가메모]]),IF(ISNUMBER(SEARCH("다기관",_xlpm.v_n)),IFERROR(DATE(VALUE(MID(_xlpm.v_n,1,4)),VALUE(MID(_xlpm.v_n,6,2)),VALUE(MID(_xlpm.v_n,9,2))),IF(ISNUMBER(파견표[[#This Row],[시작일(계산)]]),파견표[[#This Row],[시작일(계산)]],"")),""))</f>
-        <v/>
-      </c>
-      <c r="AC5" s="10">
-        <f>_xlfn.LET(_xlpm.v_n,TRIM(파견표[[#This Row],[비고]]&amp;" "&amp;파견표[[#This Row],[추가메모]]),IF(ISNUMBER(SEARCH("다기관",_xlpm.v_n)),IFERROR(DATE(VALUE(MID(_xlpm.v_n,12,4)),VALUE(MID(_xlpm.v_n,17,2)),VALUE(MID(_xlpm.v_n,20,2))),IF(ISNUMBER(파견표[[#This Row],[종료일(계산)]]),파견표[[#This Row],[종료일(계산)]],"")),""))</f>
-        <v/>
-      </c>
-      <c r="AD5" s="11">
-        <f>IF(AND(ISNUMBER(파견표[[#This Row],[다기관 시작]]),ISNUMBER(파견표[[#This Row],[다기관 종료]])),MAX(0,MIN(파견표[[#This Row],[다기관 종료]],EOMONTH(급여기준월,0))-MAX(파견표[[#This Row],[다기관 시작]],급여기준월)+1),0)</f>
-        <v/>
-      </c>
-      <c r="AE5" s="8">
-        <f>IF(AND(파견표[[#This Row],[키]]&lt;&gt;"",ISNUMBER(파견표[[#This Row],[다기관 시작]])),파견표[[#This Row],[키]]&amp;"|다기관","")</f>
-        <v/>
-      </c>
-      <c r="AF5" s="8">
-        <f>IF(COUNTA(파견표[[#This Row],[모병원명]:[파견종료일]],파견표[[#This Row],[파견병원]:[비고]])=0,"",IF(파견표[[#This Row],[키]]="","등록번호 없음",IF(LEFT(파견표[[#This Row],[모병원(정규화)]],1)="⚠","모병원명 미등록",IF(파견표[[#This Row],[파견병원(정규화)]]="","파견병원 입력",IF(LEFT(파견표[[#This Row],[파견병원(정규화)]],1)="⚠","파견병원명 미등록",IF(LEFT(파견표[[#This Row],[파견과목(정규화)]],1)="⚠","파견과목 미등록",IF(OR(파견표[[#This Row],[파견근거(정규화)]]="",LEFT(파견표[[#This Row],[파견근거(정규화)]],1)="⚠"),"파견근거 확인",IF(NOT(AND(ISNUMBER(파견표[[#This Row],[시작일(계산)]]),ISNUMBER(파견표[[#This Row],[종료일(계산)]]))),"날짜 형식/누락",IF(파견표[[#This Row],[종료일(계산)]]&lt;파견표[[#This Row],[시작일(계산)]],"종료일&lt;시작일","")))))))))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>한양대학교병원</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>가정의학과</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>김ㅇㅇ</t>
-        </is>
-      </c>
-      <c r="G6" s="7" t="inlineStr">
-        <is>
-          <t>11-1111</t>
-        </is>
-      </c>
-      <c r="H6" s="13" t="n">
-        <v>46316</v>
-      </c>
-      <c r="I6" s="13" t="n">
-        <v>46387</v>
-      </c>
-      <c r="J6" s="6" t="n"/>
-      <c r="K6" s="6" t="inlineStr">
-        <is>
-          <t>한양대구리병원</t>
-        </is>
-      </c>
-      <c r="L6" s="6" t="inlineStr">
-        <is>
-          <t>가정의학과</t>
-        </is>
-      </c>
-      <c r="M6" s="6" t="inlineStr">
-        <is>
-          <t>통합수련</t>
-        </is>
-      </c>
-      <c r="N6" s="6" t="n"/>
-      <c r="O6" s="6" t="n"/>
-      <c r="P6" s="8">
-        <f>IF(TRIM(파견표[[#This Row],[전공의등록번호]]&amp;"")="","","R|"&amp;TRIM(파견표[[#This Row],[전공의등록번호]]&amp;""))</f>
-        <v/>
-      </c>
-      <c r="Q6" s="10">
-        <f>_xlfn.LET(_xlpm.v_x,파견표[[#This Row],[파견시작일]],IF(ISNUMBER(_xlpm.v_x),_xlpm.v_x,IF(TRIM(_xlpm.v_x&amp;"")="","",IFERROR(DATE(VALUE(LEFT(_xlpm.v_x,4)),VALUE(MID(_xlpm.v_x,6,2)),VALUE(MID(_xlpm.v_x,9,2))),"⚠"&amp;_xlpm.v_x))))</f>
-        <v/>
-      </c>
-      <c r="R6" s="10">
-        <f>_xlfn.LET(_xlpm.v_x,파견표[[#This Row],[파견종료일]],IF(ISNUMBER(_xlpm.v_x),_xlpm.v_x,IF(TRIM(_xlpm.v_x&amp;"")="","",IFERROR(DATE(VALUE(LEFT(_xlpm.v_x,4)),VALUE(MID(_xlpm.v_x,6,2)),VALUE(MID(_xlpm.v_x,9,2))),"⚠"&amp;_xlpm.v_x))))</f>
-        <v/>
-      </c>
-      <c r="S6" s="8">
-        <f>_xlfn.LET(_xlpm.v_x,TRIM(파견표[[#This Row],[모병원명]]&amp;""),IF(_xlpm.v_x="","",_xlfn.XLOOKUP(_xlpm.v_x,병원약칭표[표기],병원약칭표[정식 병원],"⚠"&amp;_xlpm.v_x)))</f>
-        <v/>
-      </c>
-      <c r="T6" s="8">
-        <f>_xlfn.LET(_xlpm.v_x,TRIM(파견표[[#This Row],[파견병원]]&amp;""),IF(_xlpm.v_x="","",_xlfn.XLOOKUP(_xlpm.v_x,병원약칭표[표기],병원약칭표[정식 병원],"⚠"&amp;_xlpm.v_x)))</f>
-        <v/>
-      </c>
-      <c r="U6" s="8">
-        <f>_xlfn.LET(_xlpm.v_x,TRIM(파견표[[#This Row],[파견근거(모자/통합수련)]]&amp;""),IF(_xlpm.v_x="","",_xlfn.XLOOKUP(_xlpm.v_x,근거표[파견근거],근거표[파견근거],"⚠"&amp;_xlpm.v_x)))</f>
-        <v/>
-      </c>
-      <c r="V6" s="8">
-        <f>_xlfn.LET(_xlpm.v_x,TRIM(파견표[[#This Row],[파견과목]]&amp;""),IF(_xlpm.v_x="","",_xlfn.XLOOKUP(_xlpm.v_x,과약칭표[약칭],과약칭표[정식 명칭],"⚠"&amp;_xlpm.v_x)))</f>
-        <v/>
-      </c>
-      <c r="W6" s="11">
-        <f>IF(AND(ISNUMBER(파견표[[#This Row],[시작일(계산)]]),ISNUMBER(파견표[[#This Row],[종료일(계산)]])),파견표[[#This Row],[종료일(계산)]]-파견표[[#This Row],[시작일(계산)]]+1,"")</f>
-        <v/>
-      </c>
-      <c r="X6" s="11">
-        <f>IF(ISNUMBER(파견표[[#This Row],[시작일(계산)]]),MAX(0,MIN(IF(ISNUMBER(파견표[[#This Row],[종료일(계산)]]),파견표[[#This Row],[종료일(계산)]],EOMONTH(급여기준월,0)),EOMONTH(급여기준월,0))-MAX(파견표[[#This Row],[시작일(계산)]],급여기준월)+1),0)</f>
-        <v/>
-      </c>
-      <c r="Y6" s="8">
-        <f>IF(OR(NOT(ISNUMBER(파견표[[#This Row],[시작일(계산)]])),파견표[[#This Row],[키]]=""),"",IF(TODAY()&lt;파견표[[#This Row],[시작일(계산)]],"파견예정",IF(AND(ISNUMBER(파견표[[#This Row],[종료일(계산)]]),TODAY()&gt;파견표[[#This Row],[종료일(계산)]]),"파견종료","파견중")))</f>
-        <v/>
-      </c>
-      <c r="Z6" s="8">
-        <f>IF(OR(파견표[[#This Row],[키]]="",파견표[[#This Row],[상태]]=""),"",파견표[[#This Row],[키]]&amp;"|"&amp;파견표[[#This Row],[상태]])</f>
-        <v/>
-      </c>
-      <c r="AA6" s="8">
-        <f>IF(AND(파견표[[#This Row],[키]]&lt;&gt;"",파견표[[#This Row],[기준월 겹침일수]]&gt;0),파견표[[#This Row],[키]]&amp;"|월","")</f>
-        <v/>
-      </c>
-      <c r="AB6" s="10">
-        <f>_xlfn.LET(_xlpm.v_n,TRIM(파견표[[#This Row],[비고]]&amp;" "&amp;파견표[[#This Row],[추가메모]]),IF(ISNUMBER(SEARCH("다기관",_xlpm.v_n)),IFERROR(DATE(VALUE(MID(_xlpm.v_n,1,4)),VALUE(MID(_xlpm.v_n,6,2)),VALUE(MID(_xlpm.v_n,9,2))),IF(ISNUMBER(파견표[[#This Row],[시작일(계산)]]),파견표[[#This Row],[시작일(계산)]],"")),""))</f>
-        <v/>
-      </c>
-      <c r="AC6" s="10">
-        <f>_xlfn.LET(_xlpm.v_n,TRIM(파견표[[#This Row],[비고]]&amp;" "&amp;파견표[[#This Row],[추가메모]]),IF(ISNUMBER(SEARCH("다기관",_xlpm.v_n)),IFERROR(DATE(VALUE(MID(_xlpm.v_n,12,4)),VALUE(MID(_xlpm.v_n,17,2)),VALUE(MID(_xlpm.v_n,20,2))),IF(ISNUMBER(파견표[[#This Row],[종료일(계산)]]),파견표[[#This Row],[종료일(계산)]],"")),""))</f>
-        <v/>
-      </c>
-      <c r="AD6" s="11">
-        <f>IF(AND(ISNUMBER(파견표[[#This Row],[다기관 시작]]),ISNUMBER(파견표[[#This Row],[다기관 종료]])),MAX(0,MIN(파견표[[#This Row],[다기관 종료]],EOMONTH(급여기준월,0))-MAX(파견표[[#This Row],[다기관 시작]],급여기준월)+1),0)</f>
-        <v/>
-      </c>
-      <c r="AE6" s="8">
-        <f>IF(AND(파견표[[#This Row],[키]]&lt;&gt;"",ISNUMBER(파견표[[#This Row],[다기관 시작]])),파견표[[#This Row],[키]]&amp;"|다기관","")</f>
-        <v/>
-      </c>
-      <c r="AF6" s="8">
-        <f>IF(COUNTA(파견표[[#This Row],[모병원명]:[파견종료일]],파견표[[#This Row],[파견병원]:[비고]])=0,"",IF(파견표[[#This Row],[키]]="","등록번호 없음",IF(LEFT(파견표[[#This Row],[모병원(정규화)]],1)="⚠","모병원명 미등록",IF(파견표[[#This Row],[파견병원(정규화)]]="","파견병원 입력",IF(LEFT(파견표[[#This Row],[파견병원(정규화)]],1)="⚠","파견병원명 미등록",IF(LEFT(파견표[[#This Row],[파견과목(정규화)]],1)="⚠","파견과목 미등록",IF(OR(파견표[[#This Row],[파견근거(정규화)]]="",LEFT(파견표[[#This Row],[파견근거(정규화)]],1)="⚠"),"파견근거 확인",IF(NOT(AND(ISNUMBER(파견표[[#This Row],[시작일(계산)]]),ISNUMBER(파견표[[#This Row],[종료일(계산)]]))),"날짜 형식/누락",IF(파견표[[#This Row],[종료일(계산)]]&lt;파견표[[#This Row],[시작일(계산)]],"종료일&lt;시작일","")))))))))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>한양대학교병원</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>내과</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>이ㅇㅇ</t>
-        </is>
-      </c>
-      <c r="G7" s="7" t="inlineStr">
-        <is>
-          <t>11-1112</t>
-        </is>
-      </c>
-      <c r="H7" s="13" t="n">
-        <v>46300</v>
-      </c>
-      <c r="I7" s="13" t="n">
-        <v>46387</v>
-      </c>
-      <c r="J7" s="6" t="n"/>
-      <c r="K7" s="6" t="inlineStr">
-        <is>
-          <t>에스중앙병원</t>
-        </is>
-      </c>
-      <c r="L7" s="6" t="inlineStr">
-        <is>
-          <t>내과</t>
-        </is>
-      </c>
-      <c r="M7" s="6" t="inlineStr">
-        <is>
-          <t>통합수련</t>
-        </is>
-      </c>
-      <c r="N7" s="6" t="n"/>
-      <c r="O7" s="6" t="n"/>
-      <c r="P7" s="8">
-        <f>IF(TRIM(파견표[[#This Row],[전공의등록번호]]&amp;"")="","","R|"&amp;TRIM(파견표[[#This Row],[전공의등록번호]]&amp;""))</f>
-        <v/>
-      </c>
-      <c r="Q7" s="10">
-        <f>_xlfn.LET(_xlpm.v_x,파견표[[#This Row],[파견시작일]],IF(ISNUMBER(_xlpm.v_x),_xlpm.v_x,IF(TRIM(_xlpm.v_x&amp;"")="","",IFERROR(DATE(VALUE(LEFT(_xlpm.v_x,4)),VALUE(MID(_xlpm.v_x,6,2)),VALUE(MID(_xlpm.v_x,9,2))),"⚠"&amp;_xlpm.v_x))))</f>
-        <v/>
-      </c>
-      <c r="R7" s="10">
-        <f>_xlfn.LET(_xlpm.v_x,파견표[[#This Row],[파견종료일]],IF(ISNUMBER(_xlpm.v_x),_xlpm.v_x,IF(TRIM(_xlpm.v_x&amp;"")="","",IFERROR(DATE(VALUE(LEFT(_xlpm.v_x,4)),VALUE(MID(_xlpm.v_x,6,2)),VALUE(MID(_xlpm.v_x,9,2))),"⚠"&amp;_xlpm.v_x))))</f>
-        <v/>
-      </c>
-      <c r="S7" s="8">
-        <f>_xlfn.LET(_xlpm.v_x,TRIM(파견표[[#This Row],[모병원명]]&amp;""),IF(_xlpm.v_x="","",_xlfn.XLOOKUP(_xlpm.v_x,병원약칭표[표기],병원약칭표[정식 병원],"⚠"&amp;_xlpm.v_x)))</f>
-        <v/>
-      </c>
-      <c r="T7" s="8">
-        <f>_xlfn.LET(_xlpm.v_x,TRIM(파견표[[#This Row],[파견병원]]&amp;""),IF(_xlpm.v_x="","",_xlfn.XLOOKUP(_xlpm.v_x,병원약칭표[표기],병원약칭표[정식 병원],"⚠"&amp;_xlpm.v_x)))</f>
-        <v/>
-      </c>
-      <c r="U7" s="8">
-        <f>_xlfn.LET(_xlpm.v_x,TRIM(파견표[[#This Row],[파견근거(모자/통합수련)]]&amp;""),IF(_xlpm.v_x="","",_xlfn.XLOOKUP(_xlpm.v_x,근거표[파견근거],근거표[파견근거],"⚠"&amp;_xlpm.v_x)))</f>
-        <v/>
-      </c>
-      <c r="V7" s="8">
-        <f>_xlfn.LET(_xlpm.v_x,TRIM(파견표[[#This Row],[파견과목]]&amp;""),IF(_xlpm.v_x="","",_xlfn.XLOOKUP(_xlpm.v_x,과약칭표[약칭],과약칭표[정식 명칭],"⚠"&amp;_xlpm.v_x)))</f>
-        <v/>
-      </c>
-      <c r="W7" s="11">
-        <f>IF(AND(ISNUMBER(파견표[[#This Row],[시작일(계산)]]),ISNUMBER(파견표[[#This Row],[종료일(계산)]])),파견표[[#This Row],[종료일(계산)]]-파견표[[#This Row],[시작일(계산)]]+1,"")</f>
-        <v/>
-      </c>
-      <c r="X7" s="11">
-        <f>IF(ISNUMBER(파견표[[#This Row],[시작일(계산)]]),MAX(0,MIN(IF(ISNUMBER(파견표[[#This Row],[종료일(계산)]]),파견표[[#This Row],[종료일(계산)]],EOMONTH(급여기준월,0)),EOMONTH(급여기준월,0))-MAX(파견표[[#This Row],[시작일(계산)]],급여기준월)+1),0)</f>
-        <v/>
-      </c>
-      <c r="Y7" s="8">
-        <f>IF(OR(NOT(ISNUMBER(파견표[[#This Row],[시작일(계산)]])),파견표[[#This Row],[키]]=""),"",IF(TODAY()&lt;파견표[[#This Row],[시작일(계산)]],"파견예정",IF(AND(ISNUMBER(파견표[[#This Row],[종료일(계산)]]),TODAY()&gt;파견표[[#This Row],[종료일(계산)]]),"파견종료","파견중")))</f>
-        <v/>
-      </c>
-      <c r="Z7" s="8">
-        <f>IF(OR(파견표[[#This Row],[키]]="",파견표[[#This Row],[상태]]=""),"",파견표[[#This Row],[키]]&amp;"|"&amp;파견표[[#This Row],[상태]])</f>
-        <v/>
-      </c>
-      <c r="AA7" s="8">
-        <f>IF(AND(파견표[[#This Row],[키]]&lt;&gt;"",파견표[[#This Row],[기준월 겹침일수]]&gt;0),파견표[[#This Row],[키]]&amp;"|월","")</f>
-        <v/>
-      </c>
-      <c r="AB7" s="10">
-        <f>_xlfn.LET(_xlpm.v_n,TRIM(파견표[[#This Row],[비고]]&amp;" "&amp;파견표[[#This Row],[추가메모]]),IF(ISNUMBER(SEARCH("다기관",_xlpm.v_n)),IFERROR(DATE(VALUE(MID(_xlpm.v_n,1,4)),VALUE(MID(_xlpm.v_n,6,2)),VALUE(MID(_xlpm.v_n,9,2))),IF(ISNUMBER(파견표[[#This Row],[시작일(계산)]]),파견표[[#This Row],[시작일(계산)]],"")),""))</f>
-        <v/>
-      </c>
-      <c r="AC7" s="10">
-        <f>_xlfn.LET(_xlpm.v_n,TRIM(파견표[[#This Row],[비고]]&amp;" "&amp;파견표[[#This Row],[추가메모]]),IF(ISNUMBER(SEARCH("다기관",_xlpm.v_n)),IFERROR(DATE(VALUE(MID(_xlpm.v_n,12,4)),VALUE(MID(_xlpm.v_n,17,2)),VALUE(MID(_xlpm.v_n,20,2))),IF(ISNUMBER(파견표[[#This Row],[종료일(계산)]]),파견표[[#This Row],[종료일(계산)]],"")),""))</f>
-        <v/>
-      </c>
-      <c r="AD7" s="11">
-        <f>IF(AND(ISNUMBER(파견표[[#This Row],[다기관 시작]]),ISNUMBER(파견표[[#This Row],[다기관 종료]])),MAX(0,MIN(파견표[[#This Row],[다기관 종료]],EOMONTH(급여기준월,0))-MAX(파견표[[#This Row],[다기관 시작]],급여기준월)+1),0)</f>
-        <v/>
-      </c>
-      <c r="AE7" s="8">
-        <f>IF(AND(파견표[[#This Row],[키]]&lt;&gt;"",ISNUMBER(파견표[[#This Row],[다기관 시작]])),파견표[[#This Row],[키]]&amp;"|다기관","")</f>
-        <v/>
-      </c>
-      <c r="AF7" s="8">
-        <f>IF(COUNTA(파견표[[#This Row],[모병원명]:[파견종료일]],파견표[[#This Row],[파견병원]:[비고]])=0,"",IF(파견표[[#This Row],[키]]="","등록번호 없음",IF(LEFT(파견표[[#This Row],[모병원(정규화)]],1)="⚠","모병원명 미등록",IF(파견표[[#This Row],[파견병원(정규화)]]="","파견병원 입력",IF(LEFT(파견표[[#This Row],[파견병원(정규화)]],1)="⚠","파견병원명 미등록",IF(LEFT(파견표[[#This Row],[파견과목(정규화)]],1)="⚠","파견과목 미등록",IF(OR(파견표[[#This Row],[파견근거(정규화)]]="",LEFT(파견표[[#This Row],[파견근거(정규화)]],1)="⚠"),"파견근거 확인",IF(NOT(AND(ISNUMBER(파견표[[#This Row],[시작일(계산)]]),ISNUMBER(파견표[[#This Row],[종료일(계산)]]))),"날짜 형식/누락",IF(파견표[[#This Row],[종료일(계산)]]&lt;파견표[[#This Row],[시작일(계산)]],"종료일&lt;시작일","")))))))))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>한양대구리병원</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>마취통증의학과</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>정ㅇㅇ</t>
-        </is>
-      </c>
-      <c r="G8" s="7" t="inlineStr">
-        <is>
-          <t>11-1115</t>
-        </is>
-      </c>
-      <c r="H8" s="13" t="n">
-        <v>46313</v>
-      </c>
-      <c r="I8" s="13" t="n">
-        <v>46387</v>
-      </c>
-      <c r="J8" s="6" t="n"/>
-      <c r="K8" s="6" t="inlineStr">
-        <is>
-          <t>한양대학교병원</t>
-        </is>
-      </c>
-      <c r="L8" s="6" t="inlineStr">
-        <is>
-          <t>마취통증의학과</t>
-        </is>
-      </c>
-      <c r="M8" s="6" t="inlineStr">
-        <is>
-          <t>모자</t>
-        </is>
-      </c>
-      <c r="N8" s="6" t="n"/>
-      <c r="O8" s="6" t="n"/>
-      <c r="P8" s="8">
-        <f>IF(TRIM(파견표[[#This Row],[전공의등록번호]]&amp;"")="","","R|"&amp;TRIM(파견표[[#This Row],[전공의등록번호]]&amp;""))</f>
-        <v/>
-      </c>
-      <c r="Q8" s="10">
-        <f>_xlfn.LET(_xlpm.v_x,파견표[[#This Row],[파견시작일]],IF(ISNUMBER(_xlpm.v_x),_xlpm.v_x,IF(TRIM(_xlpm.v_x&amp;"")="","",IFERROR(DATE(VALUE(LEFT(_xlpm.v_x,4)),VALUE(MID(_xlpm.v_x,6,2)),VALUE(MID(_xlpm.v_x,9,2))),"⚠"&amp;_xlpm.v_x))))</f>
-        <v/>
-      </c>
-      <c r="R8" s="10">
-        <f>_xlfn.LET(_xlpm.v_x,파견표[[#This Row],[파견종료일]],IF(ISNUMBER(_xlpm.v_x),_xlpm.v_x,IF(TRIM(_xlpm.v_x&amp;"")="","",IFERROR(DATE(VALUE(LEFT(_xlpm.v_x,4)),VALUE(MID(_xlpm.v_x,6,2)),VALUE(MID(_xlpm.v_x,9,2))),"⚠"&amp;_xlpm.v_x))))</f>
-        <v/>
-      </c>
-      <c r="S8" s="8">
-        <f>_xlfn.LET(_xlpm.v_x,TRIM(파견표[[#This Row],[모병원명]]&amp;""),IF(_xlpm.v_x="","",_xlfn.XLOOKUP(_xlpm.v_x,병원약칭표[표기],병원약칭표[정식 병원],"⚠"&amp;_xlpm.v_x)))</f>
-        <v/>
-      </c>
-      <c r="T8" s="8">
-        <f>_xlfn.LET(_xlpm.v_x,TRIM(파견표[[#This Row],[파견병원]]&amp;""),IF(_xlpm.v_x="","",_xlfn.XLOOKUP(_xlpm.v_x,병원약칭표[표기],병원약칭표[정식 병원],"⚠"&amp;_xlpm.v_x)))</f>
-        <v/>
-      </c>
-      <c r="U8" s="8">
-        <f>_xlfn.LET(_xlpm.v_x,TRIM(파견표[[#This Row],[파견근거(모자/통합수련)]]&amp;""),IF(_xlpm.v_x="","",_xlfn.XLOOKUP(_xlpm.v_x,근거표[파견근거],근거표[파견근거],"⚠"&amp;_xlpm.v_x)))</f>
-        <v/>
-      </c>
-      <c r="V8" s="8">
-        <f>_xlfn.LET(_xlpm.v_x,TRIM(파견표[[#This Row],[파견과목]]&amp;""),IF(_xlpm.v_x="","",_xlfn.XLOOKUP(_xlpm.v_x,과약칭표[약칭],과약칭표[정식 명칭],"⚠"&amp;_xlpm.v_x)))</f>
-        <v/>
-      </c>
-      <c r="W8" s="11">
-        <f>IF(AND(ISNUMBER(파견표[[#This Row],[시작일(계산)]]),ISNUMBER(파견표[[#This Row],[종료일(계산)]])),파견표[[#This Row],[종료일(계산)]]-파견표[[#This Row],[시작일(계산)]]+1,"")</f>
-        <v/>
-      </c>
-      <c r="X8" s="11">
-        <f>IF(ISNUMBER(파견표[[#This Row],[시작일(계산)]]),MAX(0,MIN(IF(ISNUMBER(파견표[[#This Row],[종료일(계산)]]),파견표[[#This Row],[종료일(계산)]],EOMONTH(급여기준월,0)),EOMONTH(급여기준월,0))-MAX(파견표[[#This Row],[시작일(계산)]],급여기준월)+1),0)</f>
-        <v/>
-      </c>
-      <c r="Y8" s="8">
-        <f>IF(OR(NOT(ISNUMBER(파견표[[#This Row],[시작일(계산)]])),파견표[[#This Row],[키]]=""),"",IF(TODAY()&lt;파견표[[#This Row],[시작일(계산)]],"파견예정",IF(AND(ISNUMBER(파견표[[#This Row],[종료일(계산)]]),TODAY()&gt;파견표[[#This Row],[종료일(계산)]]),"파견종료","파견중")))</f>
-        <v/>
-      </c>
-      <c r="Z8" s="8">
-        <f>IF(OR(파견표[[#This Row],[키]]="",파견표[[#This Row],[상태]]=""),"",파견표[[#This Row],[키]]&amp;"|"&amp;파견표[[#This Row],[상태]])</f>
-        <v/>
-      </c>
-      <c r="AA8" s="8">
-        <f>IF(AND(파견표[[#This Row],[키]]&lt;&gt;"",파견표[[#This Row],[기준월 겹침일수]]&gt;0),파견표[[#This Row],[키]]&amp;"|월","")</f>
-        <v/>
-      </c>
-      <c r="AB8" s="10">
-        <f>_xlfn.LET(_xlpm.v_n,TRIM(파견표[[#This Row],[비고]]&amp;" "&amp;파견표[[#This Row],[추가메모]]),IF(ISNUMBER(SEARCH("다기관",_xlpm.v_n)),IFERROR(DATE(VALUE(MID(_xlpm.v_n,1,4)),VALUE(MID(_xlpm.v_n,6,2)),VALUE(MID(_xlpm.v_n,9,2))),IF(ISNUMBER(파견표[[#This Row],[시작일(계산)]]),파견표[[#This Row],[시작일(계산)]],"")),""))</f>
-        <v/>
-      </c>
-      <c r="AC8" s="10">
-        <f>_xlfn.LET(_xlpm.v_n,TRIM(파견표[[#This Row],[비고]]&amp;" "&amp;파견표[[#This Row],[추가메모]]),IF(ISNUMBER(SEARCH("다기관",_xlpm.v_n)),IFERROR(DATE(VALUE(MID(_xlpm.v_n,12,4)),VALUE(MID(_xlpm.v_n,17,2)),VALUE(MID(_xlpm.v_n,20,2))),IF(ISNUMBER(파견표[[#This Row],[종료일(계산)]]),파견표[[#This Row],[종료일(계산)]],"")),""))</f>
-        <v/>
-      </c>
-      <c r="AD8" s="11">
-        <f>IF(AND(ISNUMBER(파견표[[#This Row],[다기관 시작]]),ISNUMBER(파견표[[#This Row],[다기관 종료]])),MAX(0,MIN(파견표[[#This Row],[다기관 종료]],EOMONTH(급여기준월,0))-MAX(파견표[[#This Row],[다기관 시작]],급여기준월)+1),0)</f>
-        <v/>
-      </c>
-      <c r="AE8" s="8">
-        <f>IF(AND(파견표[[#This Row],[키]]&lt;&gt;"",ISNUMBER(파견표[[#This Row],[다기관 시작]])),파견표[[#This Row],[키]]&amp;"|다기관","")</f>
-        <v/>
-      </c>
-      <c r="AF8" s="8">
-        <f>IF(COUNTA(파견표[[#This Row],[모병원명]:[파견종료일]],파견표[[#This Row],[파견병원]:[비고]])=0,"",IF(파견표[[#This Row],[키]]="","등록번호 없음",IF(LEFT(파견표[[#This Row],[모병원(정규화)]],1)="⚠","모병원명 미등록",IF(파견표[[#This Row],[파견병원(정규화)]]="","파견병원 입력",IF(LEFT(파견표[[#This Row],[파견병원(정규화)]],1)="⚠","파견병원명 미등록",IF(LEFT(파견표[[#This Row],[파견과목(정규화)]],1)="⚠","파견과목 미등록",IF(OR(파견표[[#This Row],[파견근거(정규화)]]="",LEFT(파견표[[#This Row],[파견근거(정규화)]],1)="⚠"),"파견근거 확인",IF(NOT(AND(ISNUMBER(파견표[[#This Row],[시작일(계산)]]),ISNUMBER(파견표[[#This Row],[종료일(계산)]]))),"날짜 형식/누락",IF(파견표[[#This Row],[종료일(계산)]]&lt;파견표[[#This Row],[시작일(계산)]],"종료일&lt;시작일","")))))))))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>한양대학교병원</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>산부인과</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>최ㅇㅇ</t>
-        </is>
-      </c>
-      <c r="G9" s="7" t="inlineStr">
-        <is>
-          <t>11-1114</t>
-        </is>
-      </c>
-      <c r="H9" s="13" t="n">
-        <v>46027</v>
-      </c>
-      <c r="I9" s="13" t="n">
-        <v>46112</v>
-      </c>
-      <c r="J9" s="6" t="n"/>
-      <c r="K9" s="6" t="inlineStr">
-        <is>
-          <t>창원</t>
-        </is>
-      </c>
-      <c r="L9" s="6" t="inlineStr">
-        <is>
-          <t>산부인과</t>
-        </is>
-      </c>
-      <c r="M9" s="6" t="inlineStr">
-        <is>
-          <t>다기관</t>
-        </is>
-      </c>
-      <c r="N9" s="6" t="n"/>
-      <c r="O9" s="6" t="n"/>
-      <c r="P9" s="8">
-        <f>IF(TRIM(파견표[[#This Row],[전공의등록번호]]&amp;"")="","","R|"&amp;TRIM(파견표[[#This Row],[전공의등록번호]]&amp;""))</f>
-        <v/>
-      </c>
-      <c r="Q9" s="10">
-        <f>_xlfn.LET(_xlpm.v_x,파견표[[#This Row],[파견시작일]],IF(ISNUMBER(_xlpm.v_x),_xlpm.v_x,IF(TRIM(_xlpm.v_x&amp;"")="","",IFERROR(DATE(VALUE(LEFT(_xlpm.v_x,4)),VALUE(MID(_xlpm.v_x,6,2)),VALUE(MID(_xlpm.v_x,9,2))),"⚠"&amp;_xlpm.v_x))))</f>
-        <v/>
-      </c>
-      <c r="R9" s="10">
-        <f>_xlfn.LET(_xlpm.v_x,파견표[[#This Row],[파견종료일]],IF(ISNUMBER(_xlpm.v_x),_xlpm.v_x,IF(TRIM(_xlpm.v_x&amp;"")="","",IFERROR(DATE(VALUE(LEFT(_xlpm.v_x,4)),VALUE(MID(_xlpm.v_x,6,2)),VALUE(MID(_xlpm.v_x,9,2))),"⚠"&amp;_xlpm.v_x))))</f>
-        <v/>
-      </c>
-      <c r="S9" s="8">
-        <f>_xlfn.LET(_xlpm.v_x,TRIM(파견표[[#This Row],[모병원명]]&amp;""),IF(_xlpm.v_x="","",_xlfn.XLOOKUP(_xlpm.v_x,병원약칭표[표기],병원약칭표[정식 병원],"⚠"&amp;_xlpm.v_x)))</f>
-        <v/>
-      </c>
-      <c r="T9" s="8">
-        <f>_xlfn.LET(_xlpm.v_x,TRIM(파견표[[#This Row],[파견병원]]&amp;""),IF(_xlpm.v_x="","",_xlfn.XLOOKUP(_xlpm.v_x,병원약칭표[표기],병원약칭표[정식 병원],"⚠"&amp;_xlpm.v_x)))</f>
-        <v/>
-      </c>
-      <c r="U9" s="8">
-        <f>_xlfn.LET(_xlpm.v_x,TRIM(파견표[[#This Row],[파견근거(모자/통합수련)]]&amp;""),IF(_xlpm.v_x="","",_xlfn.XLOOKUP(_xlpm.v_x,근거표[파견근거],근거표[파견근거],"⚠"&amp;_xlpm.v_x)))</f>
-        <v/>
-      </c>
-      <c r="V9" s="8">
-        <f>_xlfn.LET(_xlpm.v_x,TRIM(파견표[[#This Row],[파견과목]]&amp;""),IF(_xlpm.v_x="","",_xlfn.XLOOKUP(_xlpm.v_x,과약칭표[약칭],과약칭표[정식 명칭],"⚠"&amp;_xlpm.v_x)))</f>
-        <v/>
-      </c>
-      <c r="W9" s="11">
-        <f>IF(AND(ISNUMBER(파견표[[#This Row],[시작일(계산)]]),ISNUMBER(파견표[[#This Row],[종료일(계산)]])),파견표[[#This Row],[종료일(계산)]]-파견표[[#This Row],[시작일(계산)]]+1,"")</f>
-        <v/>
-      </c>
-      <c r="X9" s="11">
-        <f>IF(ISNUMBER(파견표[[#This Row],[시작일(계산)]]),MAX(0,MIN(IF(ISNUMBER(파견표[[#This Row],[종료일(계산)]]),파견표[[#This Row],[종료일(계산)]],EOMONTH(급여기준월,0)),EOMONTH(급여기준월,0))-MAX(파견표[[#This Row],[시작일(계산)]],급여기준월)+1),0)</f>
-        <v/>
-      </c>
-      <c r="Y9" s="8">
-        <f>IF(OR(NOT(ISNUMBER(파견표[[#This Row],[시작일(계산)]])),파견표[[#This Row],[키]]=""),"",IF(TODAY()&lt;파견표[[#This Row],[시작일(계산)]],"파견예정",IF(AND(ISNUMBER(파견표[[#This Row],[종료일(계산)]]),TODAY()&gt;파견표[[#This Row],[종료일(계산)]]),"파견종료","파견중")))</f>
-        <v/>
-      </c>
-      <c r="Z9" s="8">
-        <f>IF(OR(파견표[[#This Row],[키]]="",파견표[[#This Row],[상태]]=""),"",파견표[[#This Row],[키]]&amp;"|"&amp;파견표[[#This Row],[상태]])</f>
-        <v/>
-      </c>
-      <c r="AA9" s="8">
-        <f>IF(AND(파견표[[#This Row],[키]]&lt;&gt;"",파견표[[#This Row],[기준월 겹침일수]]&gt;0),파견표[[#This Row],[키]]&amp;"|월","")</f>
-        <v/>
-      </c>
-      <c r="AB9" s="10">
-        <f>_xlfn.LET(_xlpm.v_n,TRIM(파견표[[#This Row],[비고]]&amp;" "&amp;파견표[[#This Row],[추가메모]]),IF(ISNUMBER(SEARCH("다기관",_xlpm.v_n)),IFERROR(DATE(VALUE(MID(_xlpm.v_n,1,4)),VALUE(MID(_xlpm.v_n,6,2)),VALUE(MID(_xlpm.v_n,9,2))),IF(ISNUMBER(파견표[[#This Row],[시작일(계산)]]),파견표[[#This Row],[시작일(계산)]],"")),""))</f>
-        <v/>
-      </c>
-      <c r="AC9" s="10">
-        <f>_xlfn.LET(_xlpm.v_n,TRIM(파견표[[#This Row],[비고]]&amp;" "&amp;파견표[[#This Row],[추가메모]]),IF(ISNUMBER(SEARCH("다기관",_xlpm.v_n)),IFERROR(DATE(VALUE(MID(_xlpm.v_n,12,4)),VALUE(MID(_xlpm.v_n,17,2)),VALUE(MID(_xlpm.v_n,20,2))),IF(ISNUMBER(파견표[[#This Row],[종료일(계산)]]),파견표[[#This Row],[종료일(계산)]],"")),""))</f>
-        <v/>
-      </c>
-      <c r="AD9" s="11">
-        <f>IF(AND(ISNUMBER(파견표[[#This Row],[다기관 시작]]),ISNUMBER(파견표[[#This Row],[다기관 종료]])),MAX(0,MIN(파견표[[#This Row],[다기관 종료]],EOMONTH(급여기준월,0))-MAX(파견표[[#This Row],[다기관 시작]],급여기준월)+1),0)</f>
-        <v/>
-      </c>
-      <c r="AE9" s="8">
-        <f>IF(AND(파견표[[#This Row],[키]]&lt;&gt;"",ISNUMBER(파견표[[#This Row],[다기관 시작]])),파견표[[#This Row],[키]]&amp;"|다기관","")</f>
-        <v/>
-      </c>
-      <c r="AF9" s="8">
-        <f>IF(COUNTA(파견표[[#This Row],[모병원명]:[파견종료일]],파견표[[#This Row],[파견병원]:[비고]])=0,"",IF(파견표[[#This Row],[키]]="","등록번호 없음",IF(LEFT(파견표[[#This Row],[모병원(정규화)]],1)="⚠","모병원명 미등록",IF(파견표[[#This Row],[파견병원(정규화)]]="","파견병원 입력",IF(LEFT(파견표[[#This Row],[파견병원(정규화)]],1)="⚠","파견병원명 미등록",IF(LEFT(파견표[[#This Row],[파견과목(정규화)]],1)="⚠","파견과목 미등록",IF(OR(파견표[[#This Row],[파견근거(정규화)]]="",LEFT(파견표[[#This Row],[파견근거(정규화)]],1)="⚠"),"파견근거 확인",IF(NOT(AND(ISNUMBER(파견표[[#This Row],[시작일(계산)]]),ISNUMBER(파견표[[#This Row],[종료일(계산)]]))),"날짜 형식/누락",IF(파견표[[#This Row],[종료일(계산)]]&lt;파견표[[#This Row],[시작일(계산)]],"종료일&lt;시작일","")))))))))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>한양대구리병원</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>인턴</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t>인턴</t>
-        </is>
-      </c>
-      <c r="F10" s="6" t="inlineStr">
-        <is>
-          <t>박ㅇㅇ</t>
-        </is>
-      </c>
-      <c r="G10" s="7" t="inlineStr">
-        <is>
-          <t>22-2224</t>
-        </is>
-      </c>
-      <c r="H10" s="13" t="n">
-        <v>46327</v>
-      </c>
-      <c r="I10" s="13" t="n">
-        <v>46356</v>
-      </c>
-      <c r="J10" s="6" t="n"/>
-      <c r="K10" s="6" t="inlineStr">
-        <is>
-          <t>한양대학교병원</t>
-        </is>
-      </c>
-      <c r="L10" s="6" t="inlineStr">
-        <is>
-          <t>응급의학과</t>
-        </is>
-      </c>
-      <c r="M10" s="6" t="inlineStr">
-        <is>
-          <t>모자</t>
-        </is>
-      </c>
-      <c r="N10" s="6" t="n"/>
-      <c r="O10" s="6" t="n"/>
-      <c r="P10" s="8">
-        <f>IF(TRIM(파견표[[#This Row],[전공의등록번호]]&amp;"")="","","R|"&amp;TRIM(파견표[[#This Row],[전공의등록번호]]&amp;""))</f>
-        <v/>
-      </c>
-      <c r="Q10" s="10">
-        <f>_xlfn.LET(_xlpm.v_x,파견표[[#This Row],[파견시작일]],IF(ISNUMBER(_xlpm.v_x),_xlpm.v_x,IF(TRIM(_xlpm.v_x&amp;"")="","",IFERROR(DATE(VALUE(LEFT(_xlpm.v_x,4)),VALUE(MID(_xlpm.v_x,6,2)),VALUE(MID(_xlpm.v_x,9,2))),"⚠"&amp;_xlpm.v_x))))</f>
-        <v/>
-      </c>
-      <c r="R10" s="10">
-        <f>_xlfn.LET(_xlpm.v_x,파견표[[#This Row],[파견종료일]],IF(ISNUMBER(_xlpm.v_x),_xlpm.v_x,IF(TRIM(_xlpm.v_x&amp;"")="","",IFERROR(DATE(VALUE(LEFT(_xlpm.v_x,4)),VALUE(MID(_xlpm.v_x,6,2)),VALUE(MID(_xlpm.v_x,9,2))),"⚠"&amp;_xlpm.v_x))))</f>
-        <v/>
-      </c>
-      <c r="S10" s="8">
-        <f>_xlfn.LET(_xlpm.v_x,TRIM(파견표[[#This Row],[모병원명]]&amp;""),IF(_xlpm.v_x="","",_xlfn.XLOOKUP(_xlpm.v_x,병원약칭표[표기],병원약칭표[정식 병원],"⚠"&amp;_xlpm.v_x)))</f>
-        <v/>
-      </c>
-      <c r="T10" s="8">
-        <f>_xlfn.LET(_xlpm.v_x,TRIM(파견표[[#This Row],[파견병원]]&amp;""),IF(_xlpm.v_x="","",_xlfn.XLOOKUP(_xlpm.v_x,병원약칭표[표기],병원약칭표[정식 병원],"⚠"&amp;_xlpm.v_x)))</f>
-        <v/>
-      </c>
-      <c r="U10" s="8">
-        <f>_xlfn.LET(_xlpm.v_x,TRIM(파견표[[#This Row],[파견근거(모자/통합수련)]]&amp;""),IF(_xlpm.v_x="","",_xlfn.XLOOKUP(_xlpm.v_x,근거표[파견근거],근거표[파견근거],"⚠"&amp;_xlpm.v_x)))</f>
-        <v/>
-      </c>
-      <c r="V10" s="8">
-        <f>_xlfn.LET(_xlpm.v_x,TRIM(파견표[[#This Row],[파견과목]]&amp;""),IF(_xlpm.v_x="","",_xlfn.XLOOKUP(_xlpm.v_x,과약칭표[약칭],과약칭표[정식 명칭],"⚠"&amp;_xlpm.v_x)))</f>
-        <v/>
-      </c>
-      <c r="W10" s="11">
-        <f>IF(AND(ISNUMBER(파견표[[#This Row],[시작일(계산)]]),ISNUMBER(파견표[[#This Row],[종료일(계산)]])),파견표[[#This Row],[종료일(계산)]]-파견표[[#This Row],[시작일(계산)]]+1,"")</f>
-        <v/>
-      </c>
-      <c r="X10" s="11">
-        <f>IF(ISNUMBER(파견표[[#This Row],[시작일(계산)]]),MAX(0,MIN(IF(ISNUMBER(파견표[[#This Row],[종료일(계산)]]),파견표[[#This Row],[종료일(계산)]],EOMONTH(급여기준월,0)),EOMONTH(급여기준월,0))-MAX(파견표[[#This Row],[시작일(계산)]],급여기준월)+1),0)</f>
-        <v/>
-      </c>
-      <c r="Y10" s="8">
-        <f>IF(OR(NOT(ISNUMBER(파견표[[#This Row],[시작일(계산)]])),파견표[[#This Row],[키]]=""),"",IF(TODAY()&lt;파견표[[#This Row],[시작일(계산)]],"파견예정",IF(AND(ISNUMBER(파견표[[#This Row],[종료일(계산)]]),TODAY()&gt;파견표[[#This Row],[종료일(계산)]]),"파견종료","파견중")))</f>
-        <v/>
-      </c>
-      <c r="Z10" s="8">
-        <f>IF(OR(파견표[[#This Row],[키]]="",파견표[[#This Row],[상태]]=""),"",파견표[[#This Row],[키]]&amp;"|"&amp;파견표[[#This Row],[상태]])</f>
-        <v/>
-      </c>
-      <c r="AA10" s="8">
-        <f>IF(AND(파견표[[#This Row],[키]]&lt;&gt;"",파견표[[#This Row],[기준월 겹침일수]]&gt;0),파견표[[#This Row],[키]]&amp;"|월","")</f>
-        <v/>
-      </c>
-      <c r="AB10" s="10">
-        <f>_xlfn.LET(_xlpm.v_n,TRIM(파견표[[#This Row],[비고]]&amp;" "&amp;파견표[[#This Row],[추가메모]]),IF(ISNUMBER(SEARCH("다기관",_xlpm.v_n)),IFERROR(DATE(VALUE(MID(_xlpm.v_n,1,4)),VALUE(MID(_xlpm.v_n,6,2)),VALUE(MID(_xlpm.v_n,9,2))),IF(ISNUMBER(파견표[[#This Row],[시작일(계산)]]),파견표[[#This Row],[시작일(계산)]],"")),""))</f>
-        <v/>
-      </c>
-      <c r="AC10" s="10">
-        <f>_xlfn.LET(_xlpm.v_n,TRIM(파견표[[#This Row],[비고]]&amp;" "&amp;파견표[[#This Row],[추가메모]]),IF(ISNUMBER(SEARCH("다기관",_xlpm.v_n)),IFERROR(DATE(VALUE(MID(_xlpm.v_n,12,4)),VALUE(MID(_xlpm.v_n,17,2)),VALUE(MID(_xlpm.v_n,20,2))),IF(ISNUMBER(파견표[[#This Row],[종료일(계산)]]),파견표[[#This Row],[종료일(계산)]],"")),""))</f>
-        <v/>
-      </c>
-      <c r="AD10" s="11">
-        <f>IF(AND(ISNUMBER(파견표[[#This Row],[다기관 시작]]),ISNUMBER(파견표[[#This Row],[다기관 종료]])),MAX(0,MIN(파견표[[#This Row],[다기관 종료]],EOMONTH(급여기준월,0))-MAX(파견표[[#This Row],[다기관 시작]],급여기준월)+1),0)</f>
-        <v/>
-      </c>
-      <c r="AE10" s="8">
-        <f>IF(AND(파견표[[#This Row],[키]]&lt;&gt;"",ISNUMBER(파견표[[#This Row],[다기관 시작]])),파견표[[#This Row],[키]]&amp;"|다기관","")</f>
-        <v/>
-      </c>
-      <c r="AF10" s="8">
-        <f>IF(COUNTA(파견표[[#This Row],[모병원명]:[파견종료일]],파견표[[#This Row],[파견병원]:[비고]])=0,"",IF(파견표[[#This Row],[키]]="","등록번호 없음",IF(LEFT(파견표[[#This Row],[모병원(정규화)]],1)="⚠","모병원명 미등록",IF(파견표[[#This Row],[파견병원(정규화)]]="","파견병원 입력",IF(LEFT(파견표[[#This Row],[파견병원(정규화)]],1)="⚠","파견병원명 미등록",IF(LEFT(파견표[[#This Row],[파견과목(정규화)]],1)="⚠","파견과목 미등록",IF(OR(파견표[[#This Row],[파견근거(정규화)]]="",LEFT(파견표[[#This Row],[파견근거(정규화)]],1)="⚠"),"파견근거 확인",IF(NOT(AND(ISNUMBER(파견표[[#This Row],[시작일(계산)]]),ISNUMBER(파견표[[#This Row],[종료일(계산)]]))),"날짜 형식/누락",IF(파견표[[#This Row],[종료일(계산)]]&lt;파견표[[#This Row],[시작일(계산)]],"종료일&lt;시작일","")))))))))</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="A4:O1048576">
-    <cfRule type="expression" priority="1" dxfId="0">
-      <formula>$AF4&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AF4:AF1048576">
-    <cfRule type="expression" priority="2" dxfId="1">
-      <formula>$AF4&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <dataValidations count="5">
-    <dataValidation sqref="B4:B1048576" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="등록되지 않은 값" error="병원명 목록에 없습니다. 새 기관이면 '설정_코드표' 병원약칭표에 먼저 추가하세요." type="list" errorStyle="stop">
-      <formula1>=병원표기목록</formula1>
-    </dataValidation>
-    <dataValidation sqref="K4:K1048576" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="등록되지 않은 값" error="병원명 목록에 없습니다. 새 기관이면 '설정_코드표' 병원약칭표에 먼저 추가하세요." type="list" errorStyle="stop">
-      <formula1>=병원표기목록</formula1>
-    </dataValidation>
-    <dataValidation sqref="L4:L1048576" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="등록되지 않은 값" error="진료과 목록에 없습니다. 새 과·약칭이면 '설정_코드표' 과약칭표에 먼저 추가하세요." type="list" errorStyle="stop">
-      <formula1>=과약칭목록</formula1>
-    </dataValidation>
-    <dataValidation sqref="M4:M1048576" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="등록되지 않은 값" error="파견근거 목록에 없습니다. 새 값이면 '설정_코드표' 근거표에 먼저 추가하세요." type="list" errorStyle="stop">
-      <formula1>=근거목록</formula1>
-    </dataValidation>
-    <dataValidation sqref="C4:C1048576" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="수련종별" error="I(인턴) 또는 R(레지던트)로 입력하세요." type="list" errorStyle="stop">
-      <formula1>"I,R"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="002F5597"/>
@@ -5474,187 +3842,187 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="14" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>내과</t>
         </is>
       </c>
-      <c r="B4" s="14" t="n">
+      <c r="B4" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="C4" s="14" t="inlineStr">
+      <c r="C4" s="12" t="inlineStr">
         <is>
           <t>박ㅇㅇ</t>
         </is>
       </c>
-      <c r="I4" s="14" t="inlineStr">
+      <c r="I4" s="12" t="inlineStr">
         <is>
           <t>박ㅇㅇ</t>
         </is>
       </c>
-      <c r="J4" s="14" t="inlineStr">
+      <c r="J4" s="12" t="inlineStr">
         <is>
           <t>박ㅇㅇ</t>
         </is>
       </c>
-      <c r="K4" s="14" t="inlineStr">
+      <c r="K4" s="12" t="inlineStr">
         <is>
           <t>2026.10.01</t>
         </is>
       </c>
-      <c r="L4" s="14" t="inlineStr">
+      <c r="L4" s="12" t="inlineStr">
         <is>
           <t>2026.10.31</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="14" t="inlineStr">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t>가정의학과</t>
         </is>
       </c>
-      <c r="B5" s="14" t="n">
+      <c r="B5" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I5" s="14" t="inlineStr">
+      <c r="I5" s="12" t="inlineStr">
         <is>
           <t>김ㅇㅇ</t>
         </is>
       </c>
-      <c r="J5" s="14" t="inlineStr">
+      <c r="J5" s="12" t="inlineStr">
         <is>
           <t>김ㅇㅇ</t>
         </is>
       </c>
-      <c r="K5" s="14" t="inlineStr">
+      <c r="K5" s="12" t="inlineStr">
         <is>
           <t>2026.10.21</t>
         </is>
       </c>
-      <c r="L5" s="14" t="inlineStr">
+      <c r="L5" s="12" t="inlineStr">
         <is>
           <t>2026.10.31</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>마취통증의학과</t>
         </is>
       </c>
-      <c r="B6" s="14" t="n">
+      <c r="B6" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="C6" s="14" t="inlineStr">
+      <c r="C6" s="12" t="inlineStr">
         <is>
           <t>정ㅇㅇ</t>
         </is>
       </c>
-      <c r="H6" s="14" t="inlineStr">
+      <c r="H6" s="12" t="inlineStr">
         <is>
           <t>구리독자</t>
         </is>
       </c>
-      <c r="I6" s="14" t="inlineStr">
+      <c r="I6" s="12" t="inlineStr">
         <is>
           <t>정ㅇㅇ</t>
         </is>
       </c>
-      <c r="J6" s="14" t="inlineStr">
+      <c r="J6" s="12" t="inlineStr">
         <is>
           <t>정ㅇㅇ</t>
         </is>
       </c>
-      <c r="K6" s="14" t="inlineStr">
+      <c r="K6" s="12" t="inlineStr">
         <is>
           <t>2026.10.01</t>
         </is>
       </c>
-      <c r="L6" s="14" t="inlineStr">
+      <c r="L6" s="12" t="inlineStr">
         <is>
           <t>2026.10.17</t>
         </is>
       </c>
-      <c r="N6" s="14" t="inlineStr">
+      <c r="N6" s="12" t="inlineStr">
         <is>
           <t>구리독자</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="14" t="inlineStr">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>외과</t>
         </is>
       </c>
-      <c r="B7" s="14" t="n">
+      <c r="B7" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="C7" s="14" t="inlineStr">
+      <c r="C7" s="12" t="inlineStr">
         <is>
           <t>홍ㅇㅇ</t>
         </is>
       </c>
-      <c r="H7" s="14" t="inlineStr">
+      <c r="H7" s="12" t="inlineStr">
         <is>
           <t>구리독자</t>
         </is>
       </c>
-      <c r="I7" s="14" t="inlineStr">
+      <c r="I7" s="12" t="inlineStr">
         <is>
           <t>홍ㅇㅇ</t>
         </is>
       </c>
-      <c r="J7" s="14" t="inlineStr">
+      <c r="J7" s="12" t="inlineStr">
         <is>
           <t>홍ㅇㅇ</t>
         </is>
       </c>
-      <c r="K7" s="14" t="inlineStr">
+      <c r="K7" s="12" t="inlineStr">
         <is>
           <t>2026.10.01</t>
         </is>
       </c>
-      <c r="L7" s="14" t="inlineStr">
+      <c r="L7" s="12" t="inlineStr">
         <is>
           <t>2026.10.31</t>
         </is>
       </c>
-      <c r="N7" s="14" t="inlineStr">
+      <c r="N7" s="12" t="inlineStr">
         <is>
           <t>구리독자</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="14" t="inlineStr">
+      <c r="A8" s="12" t="inlineStr">
         <is>
           <t>수련교육부</t>
         </is>
       </c>
-      <c r="B8" s="14" t="inlineStr">
+      <c r="B8" s="12" t="inlineStr">
         <is>
           <t>인턴</t>
         </is>
       </c>
-      <c r="I8" s="14" t="inlineStr">
+      <c r="I8" s="12" t="inlineStr">
         <is>
           <t>김ㅇㅇ</t>
         </is>
       </c>
-      <c r="J8" s="14" t="inlineStr">
+      <c r="J8" s="12" t="inlineStr">
         <is>
           <t>김ㅇㅇ</t>
         </is>
       </c>
-      <c r="K8" s="14" t="inlineStr">
+      <c r="K8" s="12" t="inlineStr">
         <is>
           <t>2026.10.01</t>
         </is>
       </c>
-      <c r="L8" s="14" t="inlineStr">
+      <c r="L8" s="12" t="inlineStr">
         <is>
           <t>2026.10.31</t>
         </is>
@@ -5665,14 +4033,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="002F5597"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AS9"/>
+  <dimension ref="A1:AH9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -5690,36 +4058,25 @@
     <col width="10" customWidth="1" min="13" max="13"/>
     <col width="11" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
-    <col width="9" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="17"/>
-    <col width="13" customWidth="1" min="18" max="18"/>
-    <col width="11" customWidth="1" min="19" max="19"/>
-    <col width="11" customWidth="1" min="20" max="20"/>
-    <col width="9" customWidth="1" min="21" max="21"/>
-    <col width="8" customWidth="1" min="22" max="22"/>
-    <col width="8" customWidth="1" min="23" max="23"/>
-    <col width="9" customWidth="1" min="24" max="24"/>
-    <col width="9" customWidth="1" min="25" max="25"/>
-    <col width="9" customWidth="1" min="26" max="26"/>
-    <col width="13" customWidth="1" min="27" max="27"/>
-    <col width="30" customWidth="1" min="28" max="28"/>
-    <col width="24" customWidth="1" min="29" max="29"/>
-    <col width="22" customWidth="1" min="30" max="30"/>
-    <col width="16" customWidth="1" min="31" max="31"/>
-    <col width="8" customWidth="1" min="32" max="32"/>
-    <col width="11" customWidth="1" min="33" max="33"/>
-    <col width="14" customWidth="1" min="34" max="34"/>
-    <col width="8" customWidth="1" min="35" max="35"/>
-    <col width="15" customWidth="1" min="36" max="36"/>
-    <col width="15" customWidth="1" min="37" max="37"/>
-    <col width="10" customWidth="1" min="38" max="38"/>
-    <col width="10" customWidth="1" min="39" max="39"/>
-    <col width="8" customWidth="1" min="40" max="40"/>
-    <col width="8" customWidth="1" min="41" max="41"/>
-    <col width="8" customWidth="1" min="42" max="42"/>
-    <col width="8" customWidth="1" min="43" max="43"/>
-    <col width="7" customWidth="1" min="44" max="44"/>
-    <col width="8" customWidth="1" min="45" max="45"/>
+    <col width="11" customWidth="1" min="16" max="16"/>
+    <col width="11" customWidth="1" min="17" max="17"/>
+    <col width="8" customWidth="1" min="18" max="18"/>
+    <col width="9" customWidth="1" min="19" max="19"/>
+    <col width="9" customWidth="1" min="20" max="20"/>
+    <col width="13" customWidth="1" min="21" max="21"/>
+    <col width="30" customWidth="1" min="22" max="22"/>
+    <col width="26" customWidth="1" min="23" max="23"/>
+    <col width="16" customWidth="1" min="24" max="24"/>
+    <col width="8" customWidth="1" min="25" max="25"/>
+    <col width="14" customWidth="1" min="26" max="26"/>
+    <col width="8" customWidth="1" min="27" max="27"/>
+    <col width="15" customWidth="1" min="28" max="28"/>
+    <col width="15" customWidth="1" min="29" max="29"/>
+    <col width="10" customWidth="1" min="30" max="30"/>
+    <col width="10" customWidth="1" min="31" max="31"/>
+    <col width="7" customWidth="1" min="32" max="32"/>
+    <col width="8" customWidth="1" min="33" max="33"/>
+    <col width="7" customWidth="1" min="34" max="34"/>
   </cols>
   <sheetData>
     <row r="1" ht="42" customHeight="1">
@@ -5800,152 +4157,97 @@
       </c>
       <c r="P1" s="5" t="inlineStr">
         <is>
-          <t>파견근거</t>
+          <t>구리 근무 시작일(기준월)</t>
         </is>
       </c>
       <c r="Q1" s="5" t="inlineStr">
         <is>
-          <t>파견병원</t>
+          <t>구리 근무 종료일(기준월)</t>
         </is>
       </c>
       <c r="R1" s="5" t="inlineStr">
         <is>
-          <t>파견진료과</t>
+          <t>구리독자</t>
         </is>
       </c>
       <c r="S1" s="5" t="inlineStr">
         <is>
-          <t>파견시작일</t>
+          <t>서울 근무일(기준월)</t>
         </is>
       </c>
       <c r="T1" s="5" t="inlineStr">
         <is>
-          <t>파견종료일</t>
+          <t>구리 근무일(기준월)</t>
         </is>
       </c>
       <c r="U1" s="5" t="inlineStr">
         <is>
-          <t>파견상태</t>
+          <t>급여지급병원(기준월)</t>
         </is>
       </c>
       <c r="V1" s="5" t="inlineStr">
         <is>
-          <t>파견기간(일)</t>
+          <t>급여 판정 근거</t>
         </is>
       </c>
       <c r="W1" s="5" t="inlineStr">
         <is>
-          <t>종료까지(일)</t>
-        </is>
-      </c>
-      <c r="X1" s="5" t="inlineStr">
-        <is>
-          <t>급여기준월 파견일수</t>
+          <t>점검</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>비고</t>
         </is>
       </c>
       <c r="Y1" s="5" t="inlineStr">
         <is>
-          <t>서울 근무일(기준월)</t>
+          <t>기본자료행</t>
         </is>
       </c>
       <c r="Z1" s="5" t="inlineStr">
         <is>
-          <t>구리 근무일(기준월)</t>
+          <t>이름|과</t>
         </is>
       </c>
       <c r="AA1" s="5" t="inlineStr">
         <is>
-          <t>급여지급병원(기준월)</t>
+          <t>인턴계획행</t>
         </is>
       </c>
       <c r="AB1" s="5" t="inlineStr">
         <is>
-          <t>급여 판정 근거</t>
+          <t>인턴 이번달</t>
         </is>
       </c>
       <c r="AC1" s="5" t="inlineStr">
         <is>
-          <t>점검</t>
+          <t>인턴 기준월</t>
         </is>
       </c>
       <c r="AD1" s="5" t="inlineStr">
         <is>
-          <t>다기관(비고 기재 기간)</t>
-        </is>
-      </c>
-      <c r="AE1" s="4" t="inlineStr">
-        <is>
-          <t>비고</t>
+          <t>소속병원</t>
+        </is>
+      </c>
+      <c r="AE1" s="5" t="inlineStr">
+        <is>
+          <t>기준월 근무병원</t>
         </is>
       </c>
       <c r="AF1" s="5" t="inlineStr">
         <is>
-          <t>기본자료행</t>
+          <t>구리행</t>
         </is>
       </c>
       <c r="AG1" s="5" t="inlineStr">
         <is>
-          <t>키</t>
+          <t>구리명단 근무일</t>
         </is>
       </c>
       <c r="AH1" s="5" t="inlineStr">
         <is>
-          <t>이름|과</t>
-        </is>
-      </c>
-      <c r="AI1" s="5" t="inlineStr">
-        <is>
-          <t>인턴계획행</t>
-        </is>
-      </c>
-      <c r="AJ1" s="5" t="inlineStr">
-        <is>
-          <t>인턴 이번달</t>
-        </is>
-      </c>
-      <c r="AK1" s="5" t="inlineStr">
-        <is>
-          <t>인턴 기준월</t>
-        </is>
-      </c>
-      <c r="AL1" s="5" t="inlineStr">
-        <is>
-          <t>소속병원</t>
-        </is>
-      </c>
-      <c r="AM1" s="5" t="inlineStr">
-        <is>
-          <t>기준월 근무병원</t>
-        </is>
-      </c>
-      <c r="AN1" s="5" t="inlineStr">
-        <is>
-          <t>파견기록행</t>
-        </is>
-      </c>
-      <c r="AO1" s="5" t="inlineStr">
-        <is>
-          <t>기준월 대표파견행</t>
-        </is>
-      </c>
-      <c r="AP1" s="5" t="inlineStr">
-        <is>
-          <t>다기관 기록행</t>
-        </is>
-      </c>
-      <c r="AQ1" s="5" t="inlineStr">
-        <is>
-          <t>다기관 겹침일수</t>
-        </is>
-      </c>
-      <c r="AR1" s="5" t="inlineStr">
-        <is>
-          <t>구리행</t>
-        </is>
-      </c>
-      <c r="AS1" s="5" t="inlineStr">
-        <is>
-          <t>구리명단 근무일</t>
+          <t>구리 근무 중</t>
         </is>
       </c>
     </row>
@@ -6005,132 +4307,88 @@
         </is>
       </c>
       <c r="N2" s="8">
-        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(AND(명단표[[#This Row],[파견상태]]="파견중",명단표[[#This Row],[파견병원]]&lt;&gt;""),명단표[[#This Row],[파견병원]],IF(AND(명단표[[#This Row],[인턴 이번달]]&lt;&gt;"",LEFT(명단표[[#This Row],[인턴 이번달]],1)&lt;&gt;"⚠"),LEFT(명단표[[#This Row],[인턴 이번달]],FIND(" ",명단표[[#This Row],[인턴 이번달]])-1),IF(명단표[[#This Row],[근무지]]="","",_xlfn.XLOOKUP(TRIM(명단표[[#This Row],[근무지]]&amp;""),병원약칭표[표기],병원약칭표[정식 병원],명단표[[#This Row],[근무지]]&amp;"")))))</f>
+        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(AND(명단표[[#This Row],[인턴 이번달]]&lt;&gt;"",LEFT(명단표[[#This Row],[인턴 이번달]],1)&lt;&gt;"⚠"),LEFT(명단표[[#This Row],[인턴 이번달]],FIND(" ",명단표[[#This Row],[인턴 이번달]])-1),IF(명단표[[#This Row],[구리 근무 중]]="Y","구리병원",IF(명단표[[#This Row],[근무지]]="","",_xlfn.XLOOKUP(TRIM(명단표[[#This Row],[근무지]]&amp;""),병원약칭표[표기],병원약칭표[정식 병원],명단표[[#This Row],[근무지]]&amp;"")))))</f>
         <v/>
       </c>
       <c r="O2" s="8">
-        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(AND(명단표[[#This Row],[파견상태]]="파견중",명단표[[#This Row],[파견병원]]&lt;&gt;""),IF(명단표[[#This Row],[파견진료과]]&lt;&gt;"",명단표[[#This Row],[파견진료과]],"파견과 미입력"),IF(AND(명단표[[#This Row],[인턴 이번달]]&lt;&gt;"",LEFT(명단표[[#This Row],[인턴 이번달]],1)&lt;&gt;"⚠"),MID(명단표[[#This Row],[인턴 이번달]],FIND(" ",명단표[[#This Row],[인턴 이번달]])+1,60),IF(명단표[[#This Row],[수련과목]]="","",IF(명단표[[#This Row],[수련과목]]="인턴","수련교육부(인턴)",명단표[[#This Row],[수련과목]])))))</f>
+        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(AND(명단표[[#This Row],[인턴 이번달]]&lt;&gt;"",LEFT(명단표[[#This Row],[인턴 이번달]],1)&lt;&gt;"⚠"),MID(명단표[[#This Row],[인턴 이번달]],FIND(" ",명단표[[#This Row],[인턴 이번달]])+1,60),IF(명단표[[#This Row],[수련과목]]="","",IF(명단표[[#This Row],[수련과목]]="인턴","수련교육부(인턴)",명단표[[#This Row],[수련과목]]))))</f>
         <v/>
       </c>
       <c r="P2" s="8">
-        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(명단표[[#This Row],[다기관 기록행]]&lt;&gt;"",IF(AND(TODAY()&gt;=INDEX(파견표[다기관 시작],명단표[[#This Row],[다기관 기록행]]),OR(NOT(ISNUMBER(INDEX(파견표[다기관 종료],명단표[[#This Row],[다기관 기록행]]))),TODAY()&lt;=INDEX(파견표[다기관 종료],명단표[[#This Row],[다기관 기록행]]))),"다기관",IF(명단표[[#This Row],[파견기록행]]="","",INDEX(파견표[파견근거(정규화)],명단표[[#This Row],[파견기록행]]))),IF(명단표[[#This Row],[파견기록행]]="","",INDEX(파견표[파견근거(정규화)],명단표[[#This Row],[파견기록행]]))))</f>
+        <f>IF(명단표[[#This Row],[구리행]]="","",INDEX(구리_시작,명단표[[#This Row],[구리행]]))</f>
         <v/>
       </c>
       <c r="Q2" s="8">
-        <f>IF(명단표[[#This Row],[파견기록행]]="","",INDEX(파견표[파견병원(정규화)],명단표[[#This Row],[파견기록행]]))</f>
+        <f>IF(명단표[[#This Row],[구리행]]="","",INDEX(구리_종료,명단표[[#This Row],[구리행]]))</f>
         <v/>
       </c>
       <c r="R2" s="8">
-        <f>IF(명단표[[#This Row],[파견기록행]]="","",INDEX(파견표[파견과목(정규화)],명단표[[#This Row],[파견기록행]]))</f>
-        <v/>
-      </c>
-      <c r="S2" s="10">
-        <f>IF(명단표[[#This Row],[파견기록행]]="","",INDEX(파견표[시작일(계산)],명단표[[#This Row],[파견기록행]]))</f>
-        <v/>
-      </c>
-      <c r="T2" s="10">
-        <f>IF(명단표[[#This Row],[파견기록행]]="","",INDEX(파견표[종료일(계산)],명단표[[#This Row],[파견기록행]]))</f>
+        <f>IF(명단표[[#This Row],[구리행]]="","",INDEX(구리_독자,명단표[[#This Row],[구리행]]))</f>
+        <v/>
+      </c>
+      <c r="S2" s="11">
+        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(명단표[[#This Row],[구리행]]&lt;&gt;"",MAX(0,DAY(EOMONTH(급여기준월,0))-N(명단표[[#This Row],[구리명단 근무일]])),IF(명단표[[#This Row],[기준월 근무병원]]="서울병원",DAY(EOMONTH(급여기준월,0)),0)))</f>
+        <v/>
+      </c>
+      <c r="T2" s="11">
+        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(명단표[[#This Row],[구리행]]&lt;&gt;"",N(명단표[[#This Row],[구리명단 근무일]]),IF(명단표[[#This Row],[기준월 근무병원]]="구리병원",DAY(EOMONTH(급여기준월,0)),0)))</f>
         <v/>
       </c>
       <c r="U2" s="8">
-        <f>IF(명단표[[#This Row],[파견기록행]]="","",INDEX(파견표[상태],명단표[[#This Row],[파견기록행]]))</f>
-        <v/>
-      </c>
-      <c r="V2" s="11">
-        <f>IF(명단표[[#This Row],[파견기록행]]="","",INDEX(파견표[파견일수(계산)],명단표[[#This Row],[파견기록행]]))</f>
-        <v/>
-      </c>
-      <c r="W2" s="11">
-        <f>IF(AND(명단표[[#This Row],[파견상태]]="파견중",ISNUMBER(명단표[[#This Row],[파견종료일]])),명단표[[#This Row],[파견종료일]]-TODAY(),"")</f>
-        <v/>
-      </c>
-      <c r="X2" s="11">
-        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(명단표[[#This Row],[키]]="",0,SUMIFS(파견표[기준월 겹침일수],파견표[키],명단표[[#This Row],[키]])))</f>
-        <v/>
-      </c>
-      <c r="Y2" s="11">
-        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(명단표[[#This Row],[구리행]]&lt;&gt;"",MAX(0,DAY(EOMONTH(급여기준월,0))-N(명단표[[#This Row],[구리명단 근무일]])),IF(명단표[[#This Row],[키]]="",0,SUMIFS(파견표[기준월 겹침일수],파견표[키],명단표[[#This Row],[키]],파견표[파견병원(정규화)],"서울병원"))+IF(명단표[[#This Row],[기준월 근무병원]]="서울병원",MAX(0,DAY(EOMONTH(급여기준월,0))-N(명단표[[#This Row],[급여기준월 파견일수]])),0)))</f>
-        <v/>
-      </c>
-      <c r="Z2" s="11">
-        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(명단표[[#This Row],[구리행]]&lt;&gt;"",N(명단표[[#This Row],[구리명단 근무일]]),IF(명단표[[#This Row],[키]]="",0,SUMIFS(파견표[기준월 겹침일수],파견표[키],명단표[[#This Row],[키]],파견표[파견병원(정규화)],"구리병원"))+IF(명단표[[#This Row],[기준월 근무병원]]="구리병원",MAX(0,DAY(EOMONTH(급여기준월,0))-N(명단표[[#This Row],[급여기준월 파견일수]])),0)))</f>
+        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(명단표[[#This Row],[기준월 근무병원]]="","",IF(명단표[[#This Row],[구리행]]="",명단표[[#This Row],[기준월 근무병원]],IF(AND(명단표[[#This Row],[서울 근무일(기준월)]]&gt;=판정기준일,명단표[[#This Row],[구리 근무일(기준월)]]&lt;판정기준일),"서울병원",IF(AND(명단표[[#This Row],[구리 근무일(기준월)]]&gt;=판정기준일,명단표[[#This Row],[서울 근무일(기준월)]]&lt;판정기준일),"구리병원","⚠15일 판정불가(서울 "&amp;명단표[[#This Row],[서울 근무일(기준월)]]&amp;"일/구리 "&amp;명단표[[#This Row],[구리 근무일(기준월)]]&amp;"일)")))))</f>
+        <v/>
+      </c>
+      <c r="V2" s="8">
+        <f>IF(OR(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),명단표[[#This Row],[급여지급병원(기준월)]]=""),"",IF(명단표[[#This Row],[구리행]]&lt;&gt;"","서울 "&amp;명단표[[#This Row],[서울 근무일(기준월)]]&amp;"일 / 구리 "&amp;명단표[[#This Row],[구리 근무일(기준월)]]&amp;"일 (구리 근무자명단) → 15일 이상 근무 병원 지급",IF(AND(명단표[[#This Row],[인턴 기준월]]&lt;&gt;"",LEFT(명단표[[#This Row],[인턴 기준월]],1)&lt;&gt;"⚠"),"인턴 근무계획 → 그 달 근무병원 지급","구리 근무자명단에 없음 → 소속병원 지급")))</f>
+        <v/>
+      </c>
+      <c r="W2" s="8">
+        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(명단표[[#This Row],[기본자료행]]="","기본자료에 없는 사번",IF(COUNTIF(명단표[사번],명단표[[#This Row],[사번]])&gt;1,"중복 사번",IF(명단표[[#This Row],[소속병원]]="","소속(입사장소) 입력",IF(LEFT(명단표[[#This Row],[급여지급병원(기준월)]],1)="⚠","서울·구리 15일 판정 불가(양쪽 모두 이상/미만)",IF(IF(명단표[[#This Row],[인턴계획행]]="",0,N(INDEX(인턴계획표[입력오류],명단표[[#This Row],[인턴계획행]])))&gt;0,"인턴계획 입력오류 확인",IF(AND(명단표[[#This Row],[구리행]]="",COUNTIF(구리_이름,명단표[[#This Row],[이름]])&gt;0),"구리 근무자명단 연결 확인(동명이인·과 불일치)","정상")))))))</f>
+        <v/>
+      </c>
+      <c r="X2" s="6" t="inlineStr">
+        <is>
+          <t>예시 데이터</t>
+        </is>
+      </c>
+      <c r="Y2" s="8">
+        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IFERROR(_xlfn.XMATCH("S|"&amp;TRIM(명단표[[#This Row],[사번]]&amp;""),기본자료표[사번키]),""))</f>
+        <v/>
+      </c>
+      <c r="Z2" s="8">
+        <f>IF(명단표[[#This Row],[이름]]="","",명단표[[#This Row],[이름]]&amp;"|"&amp;명단표[[#This Row],[수련과목]])</f>
         <v/>
       </c>
       <c r="AA2" s="8">
-        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(명단표[[#This Row],[기준월 근무병원]]="","",IF(명단표[[#This Row],[다기관 겹침일수]]&gt;0,명단표[[#This Row],[소속병원]],IF(AND(N(명단표[[#This Row],[급여기준월 파견일수]])&lt;=0,명단표[[#This Row],[구리행]]=""),명단표[[#This Row],[기준월 근무병원]],IF(명단표[[#This Row],[서울 근무일(기준월)]]+명단표[[#This Row],[구리 근무일(기준월)]]=DAY(EOMONTH(급여기준월,0)),IF(AND(명단표[[#This Row],[서울 근무일(기준월)]]&gt;=판정기준일,명단표[[#This Row],[구리 근무일(기준월)]]&lt;판정기준일),"서울병원",IF(AND(명단표[[#This Row],[구리 근무일(기준월)]]&gt;=판정기준일,명단표[[#This Row],[서울 근무일(기준월)]]&lt;판정기준일),"구리병원","⚠15일 판정불가(서울 "&amp;명단표[[#This Row],[서울 근무일(기준월)]]&amp;"일/구리 "&amp;명단표[[#This Row],[구리 근무일(기준월)]]&amp;"일)")),IF(명단표[[#This Row],[기준월 대표파견행]]="",명단표[[#This Row],[소속병원]],IF(INDEX(파견표[파견근거(정규화)],명단표[[#This Row],[기준월 대표파견행]])="통합수련",INDEX(파견표[파견병원(정규화)],명단표[[#This Row],[기준월 대표파견행]]),명단표[[#This Row],[소속병원]])))))))</f>
+        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IFERROR(_xlfn.XMATCH("S|"&amp;TRIM(명단표[[#This Row],[사번]]&amp;""),인턴계획표[사번키]),""))</f>
         <v/>
       </c>
       <c r="AB2" s="8">
-        <f>IF(OR(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),명단표[[#This Row],[급여지급병원(기준월)]]=""),"",IF(명단표[[#This Row],[다기관 겹침일수]]&gt;0,"다기관 기간 → 소속병원 지급",IF(AND(N(명단표[[#This Row],[급여기준월 파견일수]])&lt;=0,명단표[[#This Row],[구리행]]=""),"파견 없음 → 그 달 근무병원 지급",IF(명단표[[#This Row],[서울 근무일(기준월)]]+명단표[[#This Row],[구리 근무일(기준월)]]=DAY(EOMONTH(급여기준월,0)),"서울 "&amp;명단표[[#This Row],[서울 근무일(기준월)]]&amp;"일 / 구리 "&amp;명단표[[#This Row],[구리 근무일(기준월)]]&amp;"일"&amp;IF(명단표[[#This Row],[구리행]]&lt;&gt;""," (구리 근무자명단 반영)","")&amp;" → 15일 이상 근무 병원 지급","타 병원 포함 → "&amp;IF(명단표[[#This Row],[기준월 대표파견행]]="","소속",INDEX(파견표[파견근거(정규화)],명단표[[#This Row],[기준월 대표파견행]]))&amp;" 규칙"))))</f>
+        <f>IF(OR(명단표[[#This Row],[인턴계획행]]="",인턴위치_이번=""),"",INDEX(인턴계획표[[정규화1]:[정규화6]],명단표[[#This Row],[인턴계획행]],인턴위치_이번)&amp;"")</f>
         <v/>
       </c>
       <c r="AC2" s="8">
-        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(명단표[[#This Row],[기본자료행]]="","기본자료에 없는 사번",IF(COUNTIF(명단표[사번],명단표[[#This Row],[사번]])&gt;1,"중복 사번",IF(명단표[[#This Row],[소속병원]]="","소속(입사장소) 입력",IF(IF(명단표[[#This Row],[키]]="",0,COUNTIFS(파견표[키],명단표[[#This Row],[키]],파견표[입력오류],"?*"))&gt;0,"파견수련계획 입력오류 확인",IF(LEFT(명단표[[#This Row],[급여지급병원(기준월)]],1)="⚠","서울·구리 15일 판정 불가(양쪽 모두 이상/미만)",IF(IF(명단표[[#This Row],[인턴계획행]]="",0,N(INDEX(인턴계획표[입력오류],명단표[[#This Row],[인턴계획행]])))&gt;0,"인턴계획 입력오류 확인",IF(AND(명단표[[#This Row],[구리행]]&lt;&gt;"",명단표[[#This Row],[기준월 근무병원]]&lt;&gt;"구리병원",IF(명단표[[#This Row],[키]]="",0,SUMIFS(파견표[기준월 겹침일수],파견표[키],명단표[[#This Row],[키]],파견표[파견병원(정규화)],"구리병원"))=0),"구리 근무자명단에만 있음(파견수련계획 확인)",IF(AND(명단표[[#This Row],[인턴계획행]]&lt;&gt;"",명단표[[#This Row],[파견상태]]&lt;&gt;"파견중",명단표[[#This Row],[현재 근무병원]]&lt;&gt;명단표[[#This Row],[소속병원]]),"인턴 타지역 근무: 파견 여부 확인","정상")))))))))</f>
+        <f>IF(OR(명단표[[#This Row],[인턴계획행]]="",인턴위치_기준월=""),"",INDEX(인턴계획표[[정규화1]:[정규화6]],명단표[[#This Row],[인턴계획행]],인턴위치_기준월)&amp;"")</f>
         <v/>
       </c>
       <c r="AD2" s="8">
-        <f>IF(명단표[[#This Row],[다기관 기록행]]="","","다기관 "&amp;TEXT(INDEX(파견표[다기관 시작],명단표[[#This Row],[다기관 기록행]]),"yyyy-mm-dd")&amp;"~"&amp;IF(ISNUMBER(INDEX(파견표[다기관 종료],명단표[[#This Row],[다기관 기록행]])),TEXT(INDEX(파견표[다기관 종료],명단표[[#This Row],[다기관 기록행]]),"yyyy-mm-dd"),""))</f>
-        <v/>
-      </c>
-      <c r="AE2" s="6" t="inlineStr">
-        <is>
-          <t>예시 데이터</t>
-        </is>
+        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(명단표[[#This Row],[입사장소]]&lt;&gt;"",명단표[[#This Row],[입사장소]],IF(명단표[[#This Row],[구리독자]]="구리독자","구리병원",IF(명단표[[#This Row],[근무지]]="","",_xlfn.XLOOKUP(TRIM(명단표[[#This Row],[근무지]]&amp;""),병원약칭표[표기],병원약칭표[정식 병원],명단표[[#This Row],[근무지]]&amp;"")))))</f>
+        <v/>
+      </c>
+      <c r="AE2" s="8">
+        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(AND(명단표[[#This Row],[인턴 기준월]]&lt;&gt;"",LEFT(명단표[[#This Row],[인턴 기준월]],1)&lt;&gt;"⚠"),LEFT(명단표[[#This Row],[인턴 기준월]],FIND(" ",명단표[[#This Row],[인턴 기준월]])-1),명단표[[#This Row],[소속병원]]))</f>
+        <v/>
       </c>
       <c r="AF2" s="8">
-        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IFERROR(_xlfn.XMATCH("S|"&amp;TRIM(명단표[[#This Row],[사번]]&amp;""),기본자료표[사번키]),""))</f>
-        <v/>
-      </c>
-      <c r="AG2" s="8">
-        <f>IF(TRIM(명단표[[#This Row],[전공의등록번호]]&amp;"")="","","R|"&amp;TRIM(명단표[[#This Row],[전공의등록번호]]&amp;""))</f>
+        <f>IF(명단표[[#This Row],[이름]]="","",_xlfn.LET(_xlpm.v_a,_xlfn.XMATCH(명단표[[#This Row],[이름|과]],구리_키),IF(ISNUMBER(_xlpm.v_a),_xlpm.v_a,IF(AND(COUNTIF(구리_이름,명단표[[#This Row],[이름]])=1,COUNTIF(명단표[이름],명단표[[#This Row],[이름]])=1),_xlfn.XMATCH(명단표[[#This Row],[이름]],구리_이름),""))))</f>
+        <v/>
+      </c>
+      <c r="AG2" s="11">
+        <f>IF(명단표[[#This Row],[구리행]]="","",INDEX(구리_근무일,명단표[[#This Row],[구리행]]))</f>
         <v/>
       </c>
       <c r="AH2" s="8">
-        <f>IF(명단표[[#This Row],[이름]]="","",명단표[[#This Row],[이름]]&amp;"|"&amp;명단표[[#This Row],[수련과목]])</f>
-        <v/>
-      </c>
-      <c r="AI2" s="8">
-        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IFERROR(_xlfn.XMATCH("S|"&amp;TRIM(명단표[[#This Row],[사번]]&amp;""),인턴계획표[사번키]),""))</f>
-        <v/>
-      </c>
-      <c r="AJ2" s="8">
-        <f>IF(OR(명단표[[#This Row],[인턴계획행]]="",인턴위치_이번=""),"",INDEX(인턴계획표[[정규화1]:[정규화6]],명단표[[#This Row],[인턴계획행]],인턴위치_이번)&amp;"")</f>
-        <v/>
-      </c>
-      <c r="AK2" s="8">
-        <f>IF(OR(명단표[[#This Row],[인턴계획행]]="",인턴위치_기준월=""),"",INDEX(인턴계획표[[정규화1]:[정규화6]],명단표[[#This Row],[인턴계획행]],인턴위치_기준월)&amp;"")</f>
-        <v/>
-      </c>
-      <c r="AL2" s="8">
-        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(명단표[[#This Row],[입사장소]]&lt;&gt;"",명단표[[#This Row],[입사장소]],IF(IF(명단표[[#This Row],[구리행]]="",FALSE,INDEX(구리_독자,명단표[[#This Row],[구리행]])="구리독자"),"구리병원",IF(명단표[[#This Row],[파견기록행]]&lt;&gt;"",_xlfn.LET(_xlpm.v_m,INDEX(파견표[모병원(정규화)],명단표[[#This Row],[파견기록행]]),IF(AND(_xlpm.v_m&lt;&gt;"",LEFT(_xlpm.v_m,1)&lt;&gt;"⚠"),_xlpm.v_m,IF(명단표[[#This Row],[근무지]]="","",_xlfn.XLOOKUP(TRIM(명단표[[#This Row],[근무지]]&amp;""),병원약칭표[표기],병원약칭표[정식 병원],명단표[[#This Row],[근무지]]&amp;"")))),IF(명단표[[#This Row],[근무지]]="","",_xlfn.XLOOKUP(TRIM(명단표[[#This Row],[근무지]]&amp;""),병원약칭표[표기],병원약칭표[정식 병원],명단표[[#This Row],[근무지]]&amp;""))))))</f>
-        <v/>
-      </c>
-      <c r="AM2" s="8">
-        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(AND(명단표[[#This Row],[인턴 기준월]]&lt;&gt;"",LEFT(명단표[[#This Row],[인턴 기준월]],1)&lt;&gt;"⚠"),LEFT(명단표[[#This Row],[인턴 기준월]],FIND(" ",명단표[[#This Row],[인턴 기준월]])-1),명단표[[#This Row],[소속병원]]))</f>
-        <v/>
-      </c>
-      <c r="AN2" s="8">
-        <f>IF(명단표[[#This Row],[키]]="","",IFERROR(_xlfn.XMATCH(명단표[[#This Row],[키]]&amp;"|파견중",파견표[키|상태]),IFERROR(_xlfn.XMATCH(명단표[[#This Row],[키]]&amp;"|파견예정",파견표[키|상태]),IFERROR(_xlfn.XMATCH(명단표[[#This Row],[키]]&amp;"|파견종료",파견표[키|상태]),""))))</f>
-        <v/>
-      </c>
-      <c r="AO2" s="8">
-        <f>IF(명단표[[#This Row],[키]]="","",IFERROR(_xlfn.XMATCH(명단표[[#This Row],[키]]&amp;"|월",파견표[키|월]),""))</f>
-        <v/>
-      </c>
-      <c r="AP2" s="8">
-        <f>IF(명단표[[#This Row],[키]]="","",IFERROR(_xlfn.XMATCH(명단표[[#This Row],[키]]&amp;"|다기관",파견표[키|다기관]),""))</f>
-        <v/>
-      </c>
-      <c r="AQ2" s="11">
-        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),0,IF(명단표[[#This Row],[키]]="",0,SUMIFS(파견표[다기관 겹침일수],파견표[키],명단표[[#This Row],[키]])))</f>
-        <v/>
-      </c>
-      <c r="AR2" s="8">
-        <f>IF(명단표[[#This Row],[이름]]="","",_xlfn.LET(_xlpm.v_a,_xlfn.XMATCH(명단표[[#This Row],[이름|과]],구리_키),IF(ISNUMBER(_xlpm.v_a),_xlpm.v_a,IF(AND(COUNTIF(구리_이름,명단표[[#This Row],[이름]])=1,COUNTIF(명단표[이름],명단표[[#This Row],[이름]])=1),_xlfn.XMATCH(명단표[[#This Row],[이름]],구리_이름),""))))</f>
-        <v/>
-      </c>
-      <c r="AS2" s="11">
-        <f>IF(명단표[[#This Row],[구리행]]="","",INDEX(구리_근무일,명단표[[#This Row],[구리행]]))</f>
+        <f>IF(명단표[[#This Row],[구리행]]="","",_xlfn.LET(_xlpm.v_s,IFERROR(DATEVALUE(명단표[[#This Row],[구리 근무 시작일(기준월)]]),""),_xlpm.v_e,IFERROR(DATEVALUE(명단표[[#This Row],[구리 근무 종료일(기준월)]]),""),IF(AND(ISNUMBER(_xlpm.v_s),ISNUMBER(_xlpm.v_e)),IF(AND(TODAY()&gt;=_xlpm.v_s,TODAY()&lt;=_xlpm.v_e),"Y",""),"")))</f>
         <v/>
       </c>
     </row>
@@ -6190,132 +4448,88 @@
         </is>
       </c>
       <c r="N3" s="8">
-        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(AND(명단표[[#This Row],[파견상태]]="파견중",명단표[[#This Row],[파견병원]]&lt;&gt;""),명단표[[#This Row],[파견병원]],IF(AND(명단표[[#This Row],[인턴 이번달]]&lt;&gt;"",LEFT(명단표[[#This Row],[인턴 이번달]],1)&lt;&gt;"⚠"),LEFT(명단표[[#This Row],[인턴 이번달]],FIND(" ",명단표[[#This Row],[인턴 이번달]])-1),IF(명단표[[#This Row],[근무지]]="","",_xlfn.XLOOKUP(TRIM(명단표[[#This Row],[근무지]]&amp;""),병원약칭표[표기],병원약칭표[정식 병원],명단표[[#This Row],[근무지]]&amp;"")))))</f>
+        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(AND(명단표[[#This Row],[인턴 이번달]]&lt;&gt;"",LEFT(명단표[[#This Row],[인턴 이번달]],1)&lt;&gt;"⚠"),LEFT(명단표[[#This Row],[인턴 이번달]],FIND(" ",명단표[[#This Row],[인턴 이번달]])-1),IF(명단표[[#This Row],[구리 근무 중]]="Y","구리병원",IF(명단표[[#This Row],[근무지]]="","",_xlfn.XLOOKUP(TRIM(명단표[[#This Row],[근무지]]&amp;""),병원약칭표[표기],병원약칭표[정식 병원],명단표[[#This Row],[근무지]]&amp;"")))))</f>
         <v/>
       </c>
       <c r="O3" s="8">
-        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(AND(명단표[[#This Row],[파견상태]]="파견중",명단표[[#This Row],[파견병원]]&lt;&gt;""),IF(명단표[[#This Row],[파견진료과]]&lt;&gt;"",명단표[[#This Row],[파견진료과]],"파견과 미입력"),IF(AND(명단표[[#This Row],[인턴 이번달]]&lt;&gt;"",LEFT(명단표[[#This Row],[인턴 이번달]],1)&lt;&gt;"⚠"),MID(명단표[[#This Row],[인턴 이번달]],FIND(" ",명단표[[#This Row],[인턴 이번달]])+1,60),IF(명단표[[#This Row],[수련과목]]="","",IF(명단표[[#This Row],[수련과목]]="인턴","수련교육부(인턴)",명단표[[#This Row],[수련과목]])))))</f>
+        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(AND(명단표[[#This Row],[인턴 이번달]]&lt;&gt;"",LEFT(명단표[[#This Row],[인턴 이번달]],1)&lt;&gt;"⚠"),MID(명단표[[#This Row],[인턴 이번달]],FIND(" ",명단표[[#This Row],[인턴 이번달]])+1,60),IF(명단표[[#This Row],[수련과목]]="","",IF(명단표[[#This Row],[수련과목]]="인턴","수련교육부(인턴)",명단표[[#This Row],[수련과목]]))))</f>
         <v/>
       </c>
       <c r="P3" s="8">
-        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(명단표[[#This Row],[다기관 기록행]]&lt;&gt;"",IF(AND(TODAY()&gt;=INDEX(파견표[다기관 시작],명단표[[#This Row],[다기관 기록행]]),OR(NOT(ISNUMBER(INDEX(파견표[다기관 종료],명단표[[#This Row],[다기관 기록행]]))),TODAY()&lt;=INDEX(파견표[다기관 종료],명단표[[#This Row],[다기관 기록행]]))),"다기관",IF(명단표[[#This Row],[파견기록행]]="","",INDEX(파견표[파견근거(정규화)],명단표[[#This Row],[파견기록행]]))),IF(명단표[[#This Row],[파견기록행]]="","",INDEX(파견표[파견근거(정규화)],명단표[[#This Row],[파견기록행]]))))</f>
+        <f>IF(명단표[[#This Row],[구리행]]="","",INDEX(구리_시작,명단표[[#This Row],[구리행]]))</f>
         <v/>
       </c>
       <c r="Q3" s="8">
-        <f>IF(명단표[[#This Row],[파견기록행]]="","",INDEX(파견표[파견병원(정규화)],명단표[[#This Row],[파견기록행]]))</f>
+        <f>IF(명단표[[#This Row],[구리행]]="","",INDEX(구리_종료,명단표[[#This Row],[구리행]]))</f>
         <v/>
       </c>
       <c r="R3" s="8">
-        <f>IF(명단표[[#This Row],[파견기록행]]="","",INDEX(파견표[파견과목(정규화)],명단표[[#This Row],[파견기록행]]))</f>
-        <v/>
-      </c>
-      <c r="S3" s="10">
-        <f>IF(명단표[[#This Row],[파견기록행]]="","",INDEX(파견표[시작일(계산)],명단표[[#This Row],[파견기록행]]))</f>
-        <v/>
-      </c>
-      <c r="T3" s="10">
-        <f>IF(명단표[[#This Row],[파견기록행]]="","",INDEX(파견표[종료일(계산)],명단표[[#This Row],[파견기록행]]))</f>
+        <f>IF(명단표[[#This Row],[구리행]]="","",INDEX(구리_독자,명단표[[#This Row],[구리행]]))</f>
+        <v/>
+      </c>
+      <c r="S3" s="11">
+        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(명단표[[#This Row],[구리행]]&lt;&gt;"",MAX(0,DAY(EOMONTH(급여기준월,0))-N(명단표[[#This Row],[구리명단 근무일]])),IF(명단표[[#This Row],[기준월 근무병원]]="서울병원",DAY(EOMONTH(급여기준월,0)),0)))</f>
+        <v/>
+      </c>
+      <c r="T3" s="11">
+        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(명단표[[#This Row],[구리행]]&lt;&gt;"",N(명단표[[#This Row],[구리명단 근무일]]),IF(명단표[[#This Row],[기준월 근무병원]]="구리병원",DAY(EOMONTH(급여기준월,0)),0)))</f>
         <v/>
       </c>
       <c r="U3" s="8">
-        <f>IF(명단표[[#This Row],[파견기록행]]="","",INDEX(파견표[상태],명단표[[#This Row],[파견기록행]]))</f>
-        <v/>
-      </c>
-      <c r="V3" s="11">
-        <f>IF(명단표[[#This Row],[파견기록행]]="","",INDEX(파견표[파견일수(계산)],명단표[[#This Row],[파견기록행]]))</f>
-        <v/>
-      </c>
-      <c r="W3" s="11">
-        <f>IF(AND(명단표[[#This Row],[파견상태]]="파견중",ISNUMBER(명단표[[#This Row],[파견종료일]])),명단표[[#This Row],[파견종료일]]-TODAY(),"")</f>
-        <v/>
-      </c>
-      <c r="X3" s="11">
-        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(명단표[[#This Row],[키]]="",0,SUMIFS(파견표[기준월 겹침일수],파견표[키],명단표[[#This Row],[키]])))</f>
-        <v/>
-      </c>
-      <c r="Y3" s="11">
-        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(명단표[[#This Row],[구리행]]&lt;&gt;"",MAX(0,DAY(EOMONTH(급여기준월,0))-N(명단표[[#This Row],[구리명단 근무일]])),IF(명단표[[#This Row],[키]]="",0,SUMIFS(파견표[기준월 겹침일수],파견표[키],명단표[[#This Row],[키]],파견표[파견병원(정규화)],"서울병원"))+IF(명단표[[#This Row],[기준월 근무병원]]="서울병원",MAX(0,DAY(EOMONTH(급여기준월,0))-N(명단표[[#This Row],[급여기준월 파견일수]])),0)))</f>
-        <v/>
-      </c>
-      <c r="Z3" s="11">
-        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(명단표[[#This Row],[구리행]]&lt;&gt;"",N(명단표[[#This Row],[구리명단 근무일]]),IF(명단표[[#This Row],[키]]="",0,SUMIFS(파견표[기준월 겹침일수],파견표[키],명단표[[#This Row],[키]],파견표[파견병원(정규화)],"구리병원"))+IF(명단표[[#This Row],[기준월 근무병원]]="구리병원",MAX(0,DAY(EOMONTH(급여기준월,0))-N(명단표[[#This Row],[급여기준월 파견일수]])),0)))</f>
+        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(명단표[[#This Row],[기준월 근무병원]]="","",IF(명단표[[#This Row],[구리행]]="",명단표[[#This Row],[기준월 근무병원]],IF(AND(명단표[[#This Row],[서울 근무일(기준월)]]&gt;=판정기준일,명단표[[#This Row],[구리 근무일(기준월)]]&lt;판정기준일),"서울병원",IF(AND(명단표[[#This Row],[구리 근무일(기준월)]]&gt;=판정기준일,명단표[[#This Row],[서울 근무일(기준월)]]&lt;판정기준일),"구리병원","⚠15일 판정불가(서울 "&amp;명단표[[#This Row],[서울 근무일(기준월)]]&amp;"일/구리 "&amp;명단표[[#This Row],[구리 근무일(기준월)]]&amp;"일)")))))</f>
+        <v/>
+      </c>
+      <c r="V3" s="8">
+        <f>IF(OR(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),명단표[[#This Row],[급여지급병원(기준월)]]=""),"",IF(명단표[[#This Row],[구리행]]&lt;&gt;"","서울 "&amp;명단표[[#This Row],[서울 근무일(기준월)]]&amp;"일 / 구리 "&amp;명단표[[#This Row],[구리 근무일(기준월)]]&amp;"일 (구리 근무자명단) → 15일 이상 근무 병원 지급",IF(AND(명단표[[#This Row],[인턴 기준월]]&lt;&gt;"",LEFT(명단표[[#This Row],[인턴 기준월]],1)&lt;&gt;"⚠"),"인턴 근무계획 → 그 달 근무병원 지급","구리 근무자명단에 없음 → 소속병원 지급")))</f>
+        <v/>
+      </c>
+      <c r="W3" s="8">
+        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(명단표[[#This Row],[기본자료행]]="","기본자료에 없는 사번",IF(COUNTIF(명단표[사번],명단표[[#This Row],[사번]])&gt;1,"중복 사번",IF(명단표[[#This Row],[소속병원]]="","소속(입사장소) 입력",IF(LEFT(명단표[[#This Row],[급여지급병원(기준월)]],1)="⚠","서울·구리 15일 판정 불가(양쪽 모두 이상/미만)",IF(IF(명단표[[#This Row],[인턴계획행]]="",0,N(INDEX(인턴계획표[입력오류],명단표[[#This Row],[인턴계획행]])))&gt;0,"인턴계획 입력오류 확인",IF(AND(명단표[[#This Row],[구리행]]="",COUNTIF(구리_이름,명단표[[#This Row],[이름]])&gt;0),"구리 근무자명단 연결 확인(동명이인·과 불일치)","정상")))))))</f>
+        <v/>
+      </c>
+      <c r="X3" s="6" t="inlineStr">
+        <is>
+          <t>예시 데이터</t>
+        </is>
+      </c>
+      <c r="Y3" s="8">
+        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IFERROR(_xlfn.XMATCH("S|"&amp;TRIM(명단표[[#This Row],[사번]]&amp;""),기본자료표[사번키]),""))</f>
+        <v/>
+      </c>
+      <c r="Z3" s="8">
+        <f>IF(명단표[[#This Row],[이름]]="","",명단표[[#This Row],[이름]]&amp;"|"&amp;명단표[[#This Row],[수련과목]])</f>
         <v/>
       </c>
       <c r="AA3" s="8">
-        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(명단표[[#This Row],[기준월 근무병원]]="","",IF(명단표[[#This Row],[다기관 겹침일수]]&gt;0,명단표[[#This Row],[소속병원]],IF(AND(N(명단표[[#This Row],[급여기준월 파견일수]])&lt;=0,명단표[[#This Row],[구리행]]=""),명단표[[#This Row],[기준월 근무병원]],IF(명단표[[#This Row],[서울 근무일(기준월)]]+명단표[[#This Row],[구리 근무일(기준월)]]=DAY(EOMONTH(급여기준월,0)),IF(AND(명단표[[#This Row],[서울 근무일(기준월)]]&gt;=판정기준일,명단표[[#This Row],[구리 근무일(기준월)]]&lt;판정기준일),"서울병원",IF(AND(명단표[[#This Row],[구리 근무일(기준월)]]&gt;=판정기준일,명단표[[#This Row],[서울 근무일(기준월)]]&lt;판정기준일),"구리병원","⚠15일 판정불가(서울 "&amp;명단표[[#This Row],[서울 근무일(기준월)]]&amp;"일/구리 "&amp;명단표[[#This Row],[구리 근무일(기준월)]]&amp;"일)")),IF(명단표[[#This Row],[기준월 대표파견행]]="",명단표[[#This Row],[소속병원]],IF(INDEX(파견표[파견근거(정규화)],명단표[[#This Row],[기준월 대표파견행]])="통합수련",INDEX(파견표[파견병원(정규화)],명단표[[#This Row],[기준월 대표파견행]]),명단표[[#This Row],[소속병원]])))))))</f>
+        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IFERROR(_xlfn.XMATCH("S|"&amp;TRIM(명단표[[#This Row],[사번]]&amp;""),인턴계획표[사번키]),""))</f>
         <v/>
       </c>
       <c r="AB3" s="8">
-        <f>IF(OR(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),명단표[[#This Row],[급여지급병원(기준월)]]=""),"",IF(명단표[[#This Row],[다기관 겹침일수]]&gt;0,"다기관 기간 → 소속병원 지급",IF(AND(N(명단표[[#This Row],[급여기준월 파견일수]])&lt;=0,명단표[[#This Row],[구리행]]=""),"파견 없음 → 그 달 근무병원 지급",IF(명단표[[#This Row],[서울 근무일(기준월)]]+명단표[[#This Row],[구리 근무일(기준월)]]=DAY(EOMONTH(급여기준월,0)),"서울 "&amp;명단표[[#This Row],[서울 근무일(기준월)]]&amp;"일 / 구리 "&amp;명단표[[#This Row],[구리 근무일(기준월)]]&amp;"일"&amp;IF(명단표[[#This Row],[구리행]]&lt;&gt;""," (구리 근무자명단 반영)","")&amp;" → 15일 이상 근무 병원 지급","타 병원 포함 → "&amp;IF(명단표[[#This Row],[기준월 대표파견행]]="","소속",INDEX(파견표[파견근거(정규화)],명단표[[#This Row],[기준월 대표파견행]]))&amp;" 규칙"))))</f>
+        <f>IF(OR(명단표[[#This Row],[인턴계획행]]="",인턴위치_이번=""),"",INDEX(인턴계획표[[정규화1]:[정규화6]],명단표[[#This Row],[인턴계획행]],인턴위치_이번)&amp;"")</f>
         <v/>
       </c>
       <c r="AC3" s="8">
-        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(명단표[[#This Row],[기본자료행]]="","기본자료에 없는 사번",IF(COUNTIF(명단표[사번],명단표[[#This Row],[사번]])&gt;1,"중복 사번",IF(명단표[[#This Row],[소속병원]]="","소속(입사장소) 입력",IF(IF(명단표[[#This Row],[키]]="",0,COUNTIFS(파견표[키],명단표[[#This Row],[키]],파견표[입력오류],"?*"))&gt;0,"파견수련계획 입력오류 확인",IF(LEFT(명단표[[#This Row],[급여지급병원(기준월)]],1)="⚠","서울·구리 15일 판정 불가(양쪽 모두 이상/미만)",IF(IF(명단표[[#This Row],[인턴계획행]]="",0,N(INDEX(인턴계획표[입력오류],명단표[[#This Row],[인턴계획행]])))&gt;0,"인턴계획 입력오류 확인",IF(AND(명단표[[#This Row],[구리행]]&lt;&gt;"",명단표[[#This Row],[기준월 근무병원]]&lt;&gt;"구리병원",IF(명단표[[#This Row],[키]]="",0,SUMIFS(파견표[기준월 겹침일수],파견표[키],명단표[[#This Row],[키]],파견표[파견병원(정규화)],"구리병원"))=0),"구리 근무자명단에만 있음(파견수련계획 확인)",IF(AND(명단표[[#This Row],[인턴계획행]]&lt;&gt;"",명단표[[#This Row],[파견상태]]&lt;&gt;"파견중",명단표[[#This Row],[현재 근무병원]]&lt;&gt;명단표[[#This Row],[소속병원]]),"인턴 타지역 근무: 파견 여부 확인","정상")))))))))</f>
+        <f>IF(OR(명단표[[#This Row],[인턴계획행]]="",인턴위치_기준월=""),"",INDEX(인턴계획표[[정규화1]:[정규화6]],명단표[[#This Row],[인턴계획행]],인턴위치_기준월)&amp;"")</f>
         <v/>
       </c>
       <c r="AD3" s="8">
-        <f>IF(명단표[[#This Row],[다기관 기록행]]="","","다기관 "&amp;TEXT(INDEX(파견표[다기관 시작],명단표[[#This Row],[다기관 기록행]]),"yyyy-mm-dd")&amp;"~"&amp;IF(ISNUMBER(INDEX(파견표[다기관 종료],명단표[[#This Row],[다기관 기록행]])),TEXT(INDEX(파견표[다기관 종료],명단표[[#This Row],[다기관 기록행]]),"yyyy-mm-dd"),""))</f>
-        <v/>
-      </c>
-      <c r="AE3" s="6" t="inlineStr">
-        <is>
-          <t>예시 데이터</t>
-        </is>
+        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(명단표[[#This Row],[입사장소]]&lt;&gt;"",명단표[[#This Row],[입사장소]],IF(명단표[[#This Row],[구리독자]]="구리독자","구리병원",IF(명단표[[#This Row],[근무지]]="","",_xlfn.XLOOKUP(TRIM(명단표[[#This Row],[근무지]]&amp;""),병원약칭표[표기],병원약칭표[정식 병원],명단표[[#This Row],[근무지]]&amp;"")))))</f>
+        <v/>
+      </c>
+      <c r="AE3" s="8">
+        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(AND(명단표[[#This Row],[인턴 기준월]]&lt;&gt;"",LEFT(명단표[[#This Row],[인턴 기준월]],1)&lt;&gt;"⚠"),LEFT(명단표[[#This Row],[인턴 기준월]],FIND(" ",명단표[[#This Row],[인턴 기준월]])-1),명단표[[#This Row],[소속병원]]))</f>
+        <v/>
       </c>
       <c r="AF3" s="8">
-        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IFERROR(_xlfn.XMATCH("S|"&amp;TRIM(명단표[[#This Row],[사번]]&amp;""),기본자료표[사번키]),""))</f>
-        <v/>
-      </c>
-      <c r="AG3" s="8">
-        <f>IF(TRIM(명단표[[#This Row],[전공의등록번호]]&amp;"")="","","R|"&amp;TRIM(명단표[[#This Row],[전공의등록번호]]&amp;""))</f>
+        <f>IF(명단표[[#This Row],[이름]]="","",_xlfn.LET(_xlpm.v_a,_xlfn.XMATCH(명단표[[#This Row],[이름|과]],구리_키),IF(ISNUMBER(_xlpm.v_a),_xlpm.v_a,IF(AND(COUNTIF(구리_이름,명단표[[#This Row],[이름]])=1,COUNTIF(명단표[이름],명단표[[#This Row],[이름]])=1),_xlfn.XMATCH(명단표[[#This Row],[이름]],구리_이름),""))))</f>
+        <v/>
+      </c>
+      <c r="AG3" s="11">
+        <f>IF(명단표[[#This Row],[구리행]]="","",INDEX(구리_근무일,명단표[[#This Row],[구리행]]))</f>
         <v/>
       </c>
       <c r="AH3" s="8">
-        <f>IF(명단표[[#This Row],[이름]]="","",명단표[[#This Row],[이름]]&amp;"|"&amp;명단표[[#This Row],[수련과목]])</f>
-        <v/>
-      </c>
-      <c r="AI3" s="8">
-        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IFERROR(_xlfn.XMATCH("S|"&amp;TRIM(명단표[[#This Row],[사번]]&amp;""),인턴계획표[사번키]),""))</f>
-        <v/>
-      </c>
-      <c r="AJ3" s="8">
-        <f>IF(OR(명단표[[#This Row],[인턴계획행]]="",인턴위치_이번=""),"",INDEX(인턴계획표[[정규화1]:[정규화6]],명단표[[#This Row],[인턴계획행]],인턴위치_이번)&amp;"")</f>
-        <v/>
-      </c>
-      <c r="AK3" s="8">
-        <f>IF(OR(명단표[[#This Row],[인턴계획행]]="",인턴위치_기준월=""),"",INDEX(인턴계획표[[정규화1]:[정규화6]],명단표[[#This Row],[인턴계획행]],인턴위치_기준월)&amp;"")</f>
-        <v/>
-      </c>
-      <c r="AL3" s="8">
-        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(명단표[[#This Row],[입사장소]]&lt;&gt;"",명단표[[#This Row],[입사장소]],IF(IF(명단표[[#This Row],[구리행]]="",FALSE,INDEX(구리_독자,명단표[[#This Row],[구리행]])="구리독자"),"구리병원",IF(명단표[[#This Row],[파견기록행]]&lt;&gt;"",_xlfn.LET(_xlpm.v_m,INDEX(파견표[모병원(정규화)],명단표[[#This Row],[파견기록행]]),IF(AND(_xlpm.v_m&lt;&gt;"",LEFT(_xlpm.v_m,1)&lt;&gt;"⚠"),_xlpm.v_m,IF(명단표[[#This Row],[근무지]]="","",_xlfn.XLOOKUP(TRIM(명단표[[#This Row],[근무지]]&amp;""),병원약칭표[표기],병원약칭표[정식 병원],명단표[[#This Row],[근무지]]&amp;"")))),IF(명단표[[#This Row],[근무지]]="","",_xlfn.XLOOKUP(TRIM(명단표[[#This Row],[근무지]]&amp;""),병원약칭표[표기],병원약칭표[정식 병원],명단표[[#This Row],[근무지]]&amp;""))))))</f>
-        <v/>
-      </c>
-      <c r="AM3" s="8">
-        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(AND(명단표[[#This Row],[인턴 기준월]]&lt;&gt;"",LEFT(명단표[[#This Row],[인턴 기준월]],1)&lt;&gt;"⚠"),LEFT(명단표[[#This Row],[인턴 기준월]],FIND(" ",명단표[[#This Row],[인턴 기준월]])-1),명단표[[#This Row],[소속병원]]))</f>
-        <v/>
-      </c>
-      <c r="AN3" s="8">
-        <f>IF(명단표[[#This Row],[키]]="","",IFERROR(_xlfn.XMATCH(명단표[[#This Row],[키]]&amp;"|파견중",파견표[키|상태]),IFERROR(_xlfn.XMATCH(명단표[[#This Row],[키]]&amp;"|파견예정",파견표[키|상태]),IFERROR(_xlfn.XMATCH(명단표[[#This Row],[키]]&amp;"|파견종료",파견표[키|상태]),""))))</f>
-        <v/>
-      </c>
-      <c r="AO3" s="8">
-        <f>IF(명단표[[#This Row],[키]]="","",IFERROR(_xlfn.XMATCH(명단표[[#This Row],[키]]&amp;"|월",파견표[키|월]),""))</f>
-        <v/>
-      </c>
-      <c r="AP3" s="8">
-        <f>IF(명단표[[#This Row],[키]]="","",IFERROR(_xlfn.XMATCH(명단표[[#This Row],[키]]&amp;"|다기관",파견표[키|다기관]),""))</f>
-        <v/>
-      </c>
-      <c r="AQ3" s="11">
-        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),0,IF(명단표[[#This Row],[키]]="",0,SUMIFS(파견표[다기관 겹침일수],파견표[키],명단표[[#This Row],[키]])))</f>
-        <v/>
-      </c>
-      <c r="AR3" s="8">
-        <f>IF(명단표[[#This Row],[이름]]="","",_xlfn.LET(_xlpm.v_a,_xlfn.XMATCH(명단표[[#This Row],[이름|과]],구리_키),IF(ISNUMBER(_xlpm.v_a),_xlpm.v_a,IF(AND(COUNTIF(구리_이름,명단표[[#This Row],[이름]])=1,COUNTIF(명단표[이름],명단표[[#This Row],[이름]])=1),_xlfn.XMATCH(명단표[[#This Row],[이름]],구리_이름),""))))</f>
-        <v/>
-      </c>
-      <c r="AS3" s="11">
-        <f>IF(명단표[[#This Row],[구리행]]="","",INDEX(구리_근무일,명단표[[#This Row],[구리행]]))</f>
+        <f>IF(명단표[[#This Row],[구리행]]="","",_xlfn.LET(_xlpm.v_s,IFERROR(DATEVALUE(명단표[[#This Row],[구리 근무 시작일(기준월)]]),""),_xlpm.v_e,IFERROR(DATEVALUE(명단표[[#This Row],[구리 근무 종료일(기준월)]]),""),IF(AND(ISNUMBER(_xlpm.v_s),ISNUMBER(_xlpm.v_e)),IF(AND(TODAY()&gt;=_xlpm.v_s,TODAY()&lt;=_xlpm.v_e),"Y",""),"")))</f>
         <v/>
       </c>
     </row>
@@ -6375,132 +4589,88 @@
         </is>
       </c>
       <c r="N4" s="8">
-        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(AND(명단표[[#This Row],[파견상태]]="파견중",명단표[[#This Row],[파견병원]]&lt;&gt;""),명단표[[#This Row],[파견병원]],IF(AND(명단표[[#This Row],[인턴 이번달]]&lt;&gt;"",LEFT(명단표[[#This Row],[인턴 이번달]],1)&lt;&gt;"⚠"),LEFT(명단표[[#This Row],[인턴 이번달]],FIND(" ",명단표[[#This Row],[인턴 이번달]])-1),IF(명단표[[#This Row],[근무지]]="","",_xlfn.XLOOKUP(TRIM(명단표[[#This Row],[근무지]]&amp;""),병원약칭표[표기],병원약칭표[정식 병원],명단표[[#This Row],[근무지]]&amp;"")))))</f>
+        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(AND(명단표[[#This Row],[인턴 이번달]]&lt;&gt;"",LEFT(명단표[[#This Row],[인턴 이번달]],1)&lt;&gt;"⚠"),LEFT(명단표[[#This Row],[인턴 이번달]],FIND(" ",명단표[[#This Row],[인턴 이번달]])-1),IF(명단표[[#This Row],[구리 근무 중]]="Y","구리병원",IF(명단표[[#This Row],[근무지]]="","",_xlfn.XLOOKUP(TRIM(명단표[[#This Row],[근무지]]&amp;""),병원약칭표[표기],병원약칭표[정식 병원],명단표[[#This Row],[근무지]]&amp;"")))))</f>
         <v/>
       </c>
       <c r="O4" s="8">
-        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(AND(명단표[[#This Row],[파견상태]]="파견중",명단표[[#This Row],[파견병원]]&lt;&gt;""),IF(명단표[[#This Row],[파견진료과]]&lt;&gt;"",명단표[[#This Row],[파견진료과]],"파견과 미입력"),IF(AND(명단표[[#This Row],[인턴 이번달]]&lt;&gt;"",LEFT(명단표[[#This Row],[인턴 이번달]],1)&lt;&gt;"⚠"),MID(명단표[[#This Row],[인턴 이번달]],FIND(" ",명단표[[#This Row],[인턴 이번달]])+1,60),IF(명단표[[#This Row],[수련과목]]="","",IF(명단표[[#This Row],[수련과목]]="인턴","수련교육부(인턴)",명단표[[#This Row],[수련과목]])))))</f>
+        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(AND(명단표[[#This Row],[인턴 이번달]]&lt;&gt;"",LEFT(명단표[[#This Row],[인턴 이번달]],1)&lt;&gt;"⚠"),MID(명단표[[#This Row],[인턴 이번달]],FIND(" ",명단표[[#This Row],[인턴 이번달]])+1,60),IF(명단표[[#This Row],[수련과목]]="","",IF(명단표[[#This Row],[수련과목]]="인턴","수련교육부(인턴)",명단표[[#This Row],[수련과목]]))))</f>
         <v/>
       </c>
       <c r="P4" s="8">
-        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(명단표[[#This Row],[다기관 기록행]]&lt;&gt;"",IF(AND(TODAY()&gt;=INDEX(파견표[다기관 시작],명단표[[#This Row],[다기관 기록행]]),OR(NOT(ISNUMBER(INDEX(파견표[다기관 종료],명단표[[#This Row],[다기관 기록행]]))),TODAY()&lt;=INDEX(파견표[다기관 종료],명단표[[#This Row],[다기관 기록행]]))),"다기관",IF(명단표[[#This Row],[파견기록행]]="","",INDEX(파견표[파견근거(정규화)],명단표[[#This Row],[파견기록행]]))),IF(명단표[[#This Row],[파견기록행]]="","",INDEX(파견표[파견근거(정규화)],명단표[[#This Row],[파견기록행]]))))</f>
+        <f>IF(명단표[[#This Row],[구리행]]="","",INDEX(구리_시작,명단표[[#This Row],[구리행]]))</f>
         <v/>
       </c>
       <c r="Q4" s="8">
-        <f>IF(명단표[[#This Row],[파견기록행]]="","",INDEX(파견표[파견병원(정규화)],명단표[[#This Row],[파견기록행]]))</f>
+        <f>IF(명단표[[#This Row],[구리행]]="","",INDEX(구리_종료,명단표[[#This Row],[구리행]]))</f>
         <v/>
       </c>
       <c r="R4" s="8">
-        <f>IF(명단표[[#This Row],[파견기록행]]="","",INDEX(파견표[파견과목(정규화)],명단표[[#This Row],[파견기록행]]))</f>
-        <v/>
-      </c>
-      <c r="S4" s="10">
-        <f>IF(명단표[[#This Row],[파견기록행]]="","",INDEX(파견표[시작일(계산)],명단표[[#This Row],[파견기록행]]))</f>
-        <v/>
-      </c>
-      <c r="T4" s="10">
-        <f>IF(명단표[[#This Row],[파견기록행]]="","",INDEX(파견표[종료일(계산)],명단표[[#This Row],[파견기록행]]))</f>
+        <f>IF(명단표[[#This Row],[구리행]]="","",INDEX(구리_독자,명단표[[#This Row],[구리행]]))</f>
+        <v/>
+      </c>
+      <c r="S4" s="11">
+        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(명단표[[#This Row],[구리행]]&lt;&gt;"",MAX(0,DAY(EOMONTH(급여기준월,0))-N(명단표[[#This Row],[구리명단 근무일]])),IF(명단표[[#This Row],[기준월 근무병원]]="서울병원",DAY(EOMONTH(급여기준월,0)),0)))</f>
+        <v/>
+      </c>
+      <c r="T4" s="11">
+        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(명단표[[#This Row],[구리행]]&lt;&gt;"",N(명단표[[#This Row],[구리명단 근무일]]),IF(명단표[[#This Row],[기준월 근무병원]]="구리병원",DAY(EOMONTH(급여기준월,0)),0)))</f>
         <v/>
       </c>
       <c r="U4" s="8">
-        <f>IF(명단표[[#This Row],[파견기록행]]="","",INDEX(파견표[상태],명단표[[#This Row],[파견기록행]]))</f>
-        <v/>
-      </c>
-      <c r="V4" s="11">
-        <f>IF(명단표[[#This Row],[파견기록행]]="","",INDEX(파견표[파견일수(계산)],명단표[[#This Row],[파견기록행]]))</f>
-        <v/>
-      </c>
-      <c r="W4" s="11">
-        <f>IF(AND(명단표[[#This Row],[파견상태]]="파견중",ISNUMBER(명단표[[#This Row],[파견종료일]])),명단표[[#This Row],[파견종료일]]-TODAY(),"")</f>
-        <v/>
-      </c>
-      <c r="X4" s="11">
-        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(명단표[[#This Row],[키]]="",0,SUMIFS(파견표[기준월 겹침일수],파견표[키],명단표[[#This Row],[키]])))</f>
-        <v/>
-      </c>
-      <c r="Y4" s="11">
-        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(명단표[[#This Row],[구리행]]&lt;&gt;"",MAX(0,DAY(EOMONTH(급여기준월,0))-N(명단표[[#This Row],[구리명단 근무일]])),IF(명단표[[#This Row],[키]]="",0,SUMIFS(파견표[기준월 겹침일수],파견표[키],명단표[[#This Row],[키]],파견표[파견병원(정규화)],"서울병원"))+IF(명단표[[#This Row],[기준월 근무병원]]="서울병원",MAX(0,DAY(EOMONTH(급여기준월,0))-N(명단표[[#This Row],[급여기준월 파견일수]])),0)))</f>
-        <v/>
-      </c>
-      <c r="Z4" s="11">
-        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(명단표[[#This Row],[구리행]]&lt;&gt;"",N(명단표[[#This Row],[구리명단 근무일]]),IF(명단표[[#This Row],[키]]="",0,SUMIFS(파견표[기준월 겹침일수],파견표[키],명단표[[#This Row],[키]],파견표[파견병원(정규화)],"구리병원"))+IF(명단표[[#This Row],[기준월 근무병원]]="구리병원",MAX(0,DAY(EOMONTH(급여기준월,0))-N(명단표[[#This Row],[급여기준월 파견일수]])),0)))</f>
+        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(명단표[[#This Row],[기준월 근무병원]]="","",IF(명단표[[#This Row],[구리행]]="",명단표[[#This Row],[기준월 근무병원]],IF(AND(명단표[[#This Row],[서울 근무일(기준월)]]&gt;=판정기준일,명단표[[#This Row],[구리 근무일(기준월)]]&lt;판정기준일),"서울병원",IF(AND(명단표[[#This Row],[구리 근무일(기준월)]]&gt;=판정기준일,명단표[[#This Row],[서울 근무일(기준월)]]&lt;판정기준일),"구리병원","⚠15일 판정불가(서울 "&amp;명단표[[#This Row],[서울 근무일(기준월)]]&amp;"일/구리 "&amp;명단표[[#This Row],[구리 근무일(기준월)]]&amp;"일)")))))</f>
+        <v/>
+      </c>
+      <c r="V4" s="8">
+        <f>IF(OR(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),명단표[[#This Row],[급여지급병원(기준월)]]=""),"",IF(명단표[[#This Row],[구리행]]&lt;&gt;"","서울 "&amp;명단표[[#This Row],[서울 근무일(기준월)]]&amp;"일 / 구리 "&amp;명단표[[#This Row],[구리 근무일(기준월)]]&amp;"일 (구리 근무자명단) → 15일 이상 근무 병원 지급",IF(AND(명단표[[#This Row],[인턴 기준월]]&lt;&gt;"",LEFT(명단표[[#This Row],[인턴 기준월]],1)&lt;&gt;"⚠"),"인턴 근무계획 → 그 달 근무병원 지급","구리 근무자명단에 없음 → 소속병원 지급")))</f>
+        <v/>
+      </c>
+      <c r="W4" s="8">
+        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(명단표[[#This Row],[기본자료행]]="","기본자료에 없는 사번",IF(COUNTIF(명단표[사번],명단표[[#This Row],[사번]])&gt;1,"중복 사번",IF(명단표[[#This Row],[소속병원]]="","소속(입사장소) 입력",IF(LEFT(명단표[[#This Row],[급여지급병원(기준월)]],1)="⚠","서울·구리 15일 판정 불가(양쪽 모두 이상/미만)",IF(IF(명단표[[#This Row],[인턴계획행]]="",0,N(INDEX(인턴계획표[입력오류],명단표[[#This Row],[인턴계획행]])))&gt;0,"인턴계획 입력오류 확인",IF(AND(명단표[[#This Row],[구리행]]="",COUNTIF(구리_이름,명단표[[#This Row],[이름]])&gt;0),"구리 근무자명단 연결 확인(동명이인·과 불일치)","정상")))))))</f>
+        <v/>
+      </c>
+      <c r="X4" s="6" t="inlineStr">
+        <is>
+          <t>예시 데이터</t>
+        </is>
+      </c>
+      <c r="Y4" s="8">
+        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IFERROR(_xlfn.XMATCH("S|"&amp;TRIM(명단표[[#This Row],[사번]]&amp;""),기본자료표[사번키]),""))</f>
+        <v/>
+      </c>
+      <c r="Z4" s="8">
+        <f>IF(명단표[[#This Row],[이름]]="","",명단표[[#This Row],[이름]]&amp;"|"&amp;명단표[[#This Row],[수련과목]])</f>
         <v/>
       </c>
       <c r="AA4" s="8">
-        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(명단표[[#This Row],[기준월 근무병원]]="","",IF(명단표[[#This Row],[다기관 겹침일수]]&gt;0,명단표[[#This Row],[소속병원]],IF(AND(N(명단표[[#This Row],[급여기준월 파견일수]])&lt;=0,명단표[[#This Row],[구리행]]=""),명단표[[#This Row],[기준월 근무병원]],IF(명단표[[#This Row],[서울 근무일(기준월)]]+명단표[[#This Row],[구리 근무일(기준월)]]=DAY(EOMONTH(급여기준월,0)),IF(AND(명단표[[#This Row],[서울 근무일(기준월)]]&gt;=판정기준일,명단표[[#This Row],[구리 근무일(기준월)]]&lt;판정기준일),"서울병원",IF(AND(명단표[[#This Row],[구리 근무일(기준월)]]&gt;=판정기준일,명단표[[#This Row],[서울 근무일(기준월)]]&lt;판정기준일),"구리병원","⚠15일 판정불가(서울 "&amp;명단표[[#This Row],[서울 근무일(기준월)]]&amp;"일/구리 "&amp;명단표[[#This Row],[구리 근무일(기준월)]]&amp;"일)")),IF(명단표[[#This Row],[기준월 대표파견행]]="",명단표[[#This Row],[소속병원]],IF(INDEX(파견표[파견근거(정규화)],명단표[[#This Row],[기준월 대표파견행]])="통합수련",INDEX(파견표[파견병원(정규화)],명단표[[#This Row],[기준월 대표파견행]]),명단표[[#This Row],[소속병원]])))))))</f>
+        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IFERROR(_xlfn.XMATCH("S|"&amp;TRIM(명단표[[#This Row],[사번]]&amp;""),인턴계획표[사번키]),""))</f>
         <v/>
       </c>
       <c r="AB4" s="8">
-        <f>IF(OR(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),명단표[[#This Row],[급여지급병원(기준월)]]=""),"",IF(명단표[[#This Row],[다기관 겹침일수]]&gt;0,"다기관 기간 → 소속병원 지급",IF(AND(N(명단표[[#This Row],[급여기준월 파견일수]])&lt;=0,명단표[[#This Row],[구리행]]=""),"파견 없음 → 그 달 근무병원 지급",IF(명단표[[#This Row],[서울 근무일(기준월)]]+명단표[[#This Row],[구리 근무일(기준월)]]=DAY(EOMONTH(급여기준월,0)),"서울 "&amp;명단표[[#This Row],[서울 근무일(기준월)]]&amp;"일 / 구리 "&amp;명단표[[#This Row],[구리 근무일(기준월)]]&amp;"일"&amp;IF(명단표[[#This Row],[구리행]]&lt;&gt;""," (구리 근무자명단 반영)","")&amp;" → 15일 이상 근무 병원 지급","타 병원 포함 → "&amp;IF(명단표[[#This Row],[기준월 대표파견행]]="","소속",INDEX(파견표[파견근거(정규화)],명단표[[#This Row],[기준월 대표파견행]]))&amp;" 규칙"))))</f>
+        <f>IF(OR(명단표[[#This Row],[인턴계획행]]="",인턴위치_이번=""),"",INDEX(인턴계획표[[정규화1]:[정규화6]],명단표[[#This Row],[인턴계획행]],인턴위치_이번)&amp;"")</f>
         <v/>
       </c>
       <c r="AC4" s="8">
-        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(명단표[[#This Row],[기본자료행]]="","기본자료에 없는 사번",IF(COUNTIF(명단표[사번],명단표[[#This Row],[사번]])&gt;1,"중복 사번",IF(명단표[[#This Row],[소속병원]]="","소속(입사장소) 입력",IF(IF(명단표[[#This Row],[키]]="",0,COUNTIFS(파견표[키],명단표[[#This Row],[키]],파견표[입력오류],"?*"))&gt;0,"파견수련계획 입력오류 확인",IF(LEFT(명단표[[#This Row],[급여지급병원(기준월)]],1)="⚠","서울·구리 15일 판정 불가(양쪽 모두 이상/미만)",IF(IF(명단표[[#This Row],[인턴계획행]]="",0,N(INDEX(인턴계획표[입력오류],명단표[[#This Row],[인턴계획행]])))&gt;0,"인턴계획 입력오류 확인",IF(AND(명단표[[#This Row],[구리행]]&lt;&gt;"",명단표[[#This Row],[기준월 근무병원]]&lt;&gt;"구리병원",IF(명단표[[#This Row],[키]]="",0,SUMIFS(파견표[기준월 겹침일수],파견표[키],명단표[[#This Row],[키]],파견표[파견병원(정규화)],"구리병원"))=0),"구리 근무자명단에만 있음(파견수련계획 확인)",IF(AND(명단표[[#This Row],[인턴계획행]]&lt;&gt;"",명단표[[#This Row],[파견상태]]&lt;&gt;"파견중",명단표[[#This Row],[현재 근무병원]]&lt;&gt;명단표[[#This Row],[소속병원]]),"인턴 타지역 근무: 파견 여부 확인","정상")))))))))</f>
+        <f>IF(OR(명단표[[#This Row],[인턴계획행]]="",인턴위치_기준월=""),"",INDEX(인턴계획표[[정규화1]:[정규화6]],명단표[[#This Row],[인턴계획행]],인턴위치_기준월)&amp;"")</f>
         <v/>
       </c>
       <c r="AD4" s="8">
-        <f>IF(명단표[[#This Row],[다기관 기록행]]="","","다기관 "&amp;TEXT(INDEX(파견표[다기관 시작],명단표[[#This Row],[다기관 기록행]]),"yyyy-mm-dd")&amp;"~"&amp;IF(ISNUMBER(INDEX(파견표[다기관 종료],명단표[[#This Row],[다기관 기록행]])),TEXT(INDEX(파견표[다기관 종료],명단표[[#This Row],[다기관 기록행]]),"yyyy-mm-dd"),""))</f>
-        <v/>
-      </c>
-      <c r="AE4" s="6" t="inlineStr">
-        <is>
-          <t>예시 데이터</t>
-        </is>
+        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(명단표[[#This Row],[입사장소]]&lt;&gt;"",명단표[[#This Row],[입사장소]],IF(명단표[[#This Row],[구리독자]]="구리독자","구리병원",IF(명단표[[#This Row],[근무지]]="","",_xlfn.XLOOKUP(TRIM(명단표[[#This Row],[근무지]]&amp;""),병원약칭표[표기],병원약칭표[정식 병원],명단표[[#This Row],[근무지]]&amp;"")))))</f>
+        <v/>
+      </c>
+      <c r="AE4" s="8">
+        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(AND(명단표[[#This Row],[인턴 기준월]]&lt;&gt;"",LEFT(명단표[[#This Row],[인턴 기준월]],1)&lt;&gt;"⚠"),LEFT(명단표[[#This Row],[인턴 기준월]],FIND(" ",명단표[[#This Row],[인턴 기준월]])-1),명단표[[#This Row],[소속병원]]))</f>
+        <v/>
       </c>
       <c r="AF4" s="8">
-        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IFERROR(_xlfn.XMATCH("S|"&amp;TRIM(명단표[[#This Row],[사번]]&amp;""),기본자료표[사번키]),""))</f>
-        <v/>
-      </c>
-      <c r="AG4" s="8">
-        <f>IF(TRIM(명단표[[#This Row],[전공의등록번호]]&amp;"")="","","R|"&amp;TRIM(명단표[[#This Row],[전공의등록번호]]&amp;""))</f>
+        <f>IF(명단표[[#This Row],[이름]]="","",_xlfn.LET(_xlpm.v_a,_xlfn.XMATCH(명단표[[#This Row],[이름|과]],구리_키),IF(ISNUMBER(_xlpm.v_a),_xlpm.v_a,IF(AND(COUNTIF(구리_이름,명단표[[#This Row],[이름]])=1,COUNTIF(명단표[이름],명단표[[#This Row],[이름]])=1),_xlfn.XMATCH(명단표[[#This Row],[이름]],구리_이름),""))))</f>
+        <v/>
+      </c>
+      <c r="AG4" s="11">
+        <f>IF(명단표[[#This Row],[구리행]]="","",INDEX(구리_근무일,명단표[[#This Row],[구리행]]))</f>
         <v/>
       </c>
       <c r="AH4" s="8">
-        <f>IF(명단표[[#This Row],[이름]]="","",명단표[[#This Row],[이름]]&amp;"|"&amp;명단표[[#This Row],[수련과목]])</f>
-        <v/>
-      </c>
-      <c r="AI4" s="8">
-        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IFERROR(_xlfn.XMATCH("S|"&amp;TRIM(명단표[[#This Row],[사번]]&amp;""),인턴계획표[사번키]),""))</f>
-        <v/>
-      </c>
-      <c r="AJ4" s="8">
-        <f>IF(OR(명단표[[#This Row],[인턴계획행]]="",인턴위치_이번=""),"",INDEX(인턴계획표[[정규화1]:[정규화6]],명단표[[#This Row],[인턴계획행]],인턴위치_이번)&amp;"")</f>
-        <v/>
-      </c>
-      <c r="AK4" s="8">
-        <f>IF(OR(명단표[[#This Row],[인턴계획행]]="",인턴위치_기준월=""),"",INDEX(인턴계획표[[정규화1]:[정규화6]],명단표[[#This Row],[인턴계획행]],인턴위치_기준월)&amp;"")</f>
-        <v/>
-      </c>
-      <c r="AL4" s="8">
-        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(명단표[[#This Row],[입사장소]]&lt;&gt;"",명단표[[#This Row],[입사장소]],IF(IF(명단표[[#This Row],[구리행]]="",FALSE,INDEX(구리_독자,명단표[[#This Row],[구리행]])="구리독자"),"구리병원",IF(명단표[[#This Row],[파견기록행]]&lt;&gt;"",_xlfn.LET(_xlpm.v_m,INDEX(파견표[모병원(정규화)],명단표[[#This Row],[파견기록행]]),IF(AND(_xlpm.v_m&lt;&gt;"",LEFT(_xlpm.v_m,1)&lt;&gt;"⚠"),_xlpm.v_m,IF(명단표[[#This Row],[근무지]]="","",_xlfn.XLOOKUP(TRIM(명단표[[#This Row],[근무지]]&amp;""),병원약칭표[표기],병원약칭표[정식 병원],명단표[[#This Row],[근무지]]&amp;"")))),IF(명단표[[#This Row],[근무지]]="","",_xlfn.XLOOKUP(TRIM(명단표[[#This Row],[근무지]]&amp;""),병원약칭표[표기],병원약칭표[정식 병원],명단표[[#This Row],[근무지]]&amp;""))))))</f>
-        <v/>
-      </c>
-      <c r="AM4" s="8">
-        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(AND(명단표[[#This Row],[인턴 기준월]]&lt;&gt;"",LEFT(명단표[[#This Row],[인턴 기준월]],1)&lt;&gt;"⚠"),LEFT(명단표[[#This Row],[인턴 기준월]],FIND(" ",명단표[[#This Row],[인턴 기준월]])-1),명단표[[#This Row],[소속병원]]))</f>
-        <v/>
-      </c>
-      <c r="AN4" s="8">
-        <f>IF(명단표[[#This Row],[키]]="","",IFERROR(_xlfn.XMATCH(명단표[[#This Row],[키]]&amp;"|파견중",파견표[키|상태]),IFERROR(_xlfn.XMATCH(명단표[[#This Row],[키]]&amp;"|파견예정",파견표[키|상태]),IFERROR(_xlfn.XMATCH(명단표[[#This Row],[키]]&amp;"|파견종료",파견표[키|상태]),""))))</f>
-        <v/>
-      </c>
-      <c r="AO4" s="8">
-        <f>IF(명단표[[#This Row],[키]]="","",IFERROR(_xlfn.XMATCH(명단표[[#This Row],[키]]&amp;"|월",파견표[키|월]),""))</f>
-        <v/>
-      </c>
-      <c r="AP4" s="8">
-        <f>IF(명단표[[#This Row],[키]]="","",IFERROR(_xlfn.XMATCH(명단표[[#This Row],[키]]&amp;"|다기관",파견표[키|다기관]),""))</f>
-        <v/>
-      </c>
-      <c r="AQ4" s="11">
-        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),0,IF(명단표[[#This Row],[키]]="",0,SUMIFS(파견표[다기관 겹침일수],파견표[키],명단표[[#This Row],[키]])))</f>
-        <v/>
-      </c>
-      <c r="AR4" s="8">
-        <f>IF(명단표[[#This Row],[이름]]="","",_xlfn.LET(_xlpm.v_a,_xlfn.XMATCH(명단표[[#This Row],[이름|과]],구리_키),IF(ISNUMBER(_xlpm.v_a),_xlpm.v_a,IF(AND(COUNTIF(구리_이름,명단표[[#This Row],[이름]])=1,COUNTIF(명단표[이름],명단표[[#This Row],[이름]])=1),_xlfn.XMATCH(명단표[[#This Row],[이름]],구리_이름),""))))</f>
-        <v/>
-      </c>
-      <c r="AS4" s="11">
-        <f>IF(명단표[[#This Row],[구리행]]="","",INDEX(구리_근무일,명단표[[#This Row],[구리행]]))</f>
+        <f>IF(명단표[[#This Row],[구리행]]="","",_xlfn.LET(_xlpm.v_s,IFERROR(DATEVALUE(명단표[[#This Row],[구리 근무 시작일(기준월)]]),""),_xlpm.v_e,IFERROR(DATEVALUE(명단표[[#This Row],[구리 근무 종료일(기준월)]]),""),IF(AND(ISNUMBER(_xlpm.v_s),ISNUMBER(_xlpm.v_e)),IF(AND(TODAY()&gt;=_xlpm.v_s,TODAY()&lt;=_xlpm.v_e),"Y",""),"")))</f>
         <v/>
       </c>
     </row>
@@ -6560,132 +4730,88 @@
         </is>
       </c>
       <c r="N5" s="8">
-        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(AND(명단표[[#This Row],[파견상태]]="파견중",명단표[[#This Row],[파견병원]]&lt;&gt;""),명단표[[#This Row],[파견병원]],IF(AND(명단표[[#This Row],[인턴 이번달]]&lt;&gt;"",LEFT(명단표[[#This Row],[인턴 이번달]],1)&lt;&gt;"⚠"),LEFT(명단표[[#This Row],[인턴 이번달]],FIND(" ",명단표[[#This Row],[인턴 이번달]])-1),IF(명단표[[#This Row],[근무지]]="","",_xlfn.XLOOKUP(TRIM(명단표[[#This Row],[근무지]]&amp;""),병원약칭표[표기],병원약칭표[정식 병원],명단표[[#This Row],[근무지]]&amp;"")))))</f>
+        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(AND(명단표[[#This Row],[인턴 이번달]]&lt;&gt;"",LEFT(명단표[[#This Row],[인턴 이번달]],1)&lt;&gt;"⚠"),LEFT(명단표[[#This Row],[인턴 이번달]],FIND(" ",명단표[[#This Row],[인턴 이번달]])-1),IF(명단표[[#This Row],[구리 근무 중]]="Y","구리병원",IF(명단표[[#This Row],[근무지]]="","",_xlfn.XLOOKUP(TRIM(명단표[[#This Row],[근무지]]&amp;""),병원약칭표[표기],병원약칭표[정식 병원],명단표[[#This Row],[근무지]]&amp;"")))))</f>
         <v/>
       </c>
       <c r="O5" s="8">
-        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(AND(명단표[[#This Row],[파견상태]]="파견중",명단표[[#This Row],[파견병원]]&lt;&gt;""),IF(명단표[[#This Row],[파견진료과]]&lt;&gt;"",명단표[[#This Row],[파견진료과]],"파견과 미입력"),IF(AND(명단표[[#This Row],[인턴 이번달]]&lt;&gt;"",LEFT(명단표[[#This Row],[인턴 이번달]],1)&lt;&gt;"⚠"),MID(명단표[[#This Row],[인턴 이번달]],FIND(" ",명단표[[#This Row],[인턴 이번달]])+1,60),IF(명단표[[#This Row],[수련과목]]="","",IF(명단표[[#This Row],[수련과목]]="인턴","수련교육부(인턴)",명단표[[#This Row],[수련과목]])))))</f>
+        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(AND(명단표[[#This Row],[인턴 이번달]]&lt;&gt;"",LEFT(명단표[[#This Row],[인턴 이번달]],1)&lt;&gt;"⚠"),MID(명단표[[#This Row],[인턴 이번달]],FIND(" ",명단표[[#This Row],[인턴 이번달]])+1,60),IF(명단표[[#This Row],[수련과목]]="","",IF(명단표[[#This Row],[수련과목]]="인턴","수련교육부(인턴)",명단표[[#This Row],[수련과목]]))))</f>
         <v/>
       </c>
       <c r="P5" s="8">
-        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(명단표[[#This Row],[다기관 기록행]]&lt;&gt;"",IF(AND(TODAY()&gt;=INDEX(파견표[다기관 시작],명단표[[#This Row],[다기관 기록행]]),OR(NOT(ISNUMBER(INDEX(파견표[다기관 종료],명단표[[#This Row],[다기관 기록행]]))),TODAY()&lt;=INDEX(파견표[다기관 종료],명단표[[#This Row],[다기관 기록행]]))),"다기관",IF(명단표[[#This Row],[파견기록행]]="","",INDEX(파견표[파견근거(정규화)],명단표[[#This Row],[파견기록행]]))),IF(명단표[[#This Row],[파견기록행]]="","",INDEX(파견표[파견근거(정규화)],명단표[[#This Row],[파견기록행]]))))</f>
+        <f>IF(명단표[[#This Row],[구리행]]="","",INDEX(구리_시작,명단표[[#This Row],[구리행]]))</f>
         <v/>
       </c>
       <c r="Q5" s="8">
-        <f>IF(명단표[[#This Row],[파견기록행]]="","",INDEX(파견표[파견병원(정규화)],명단표[[#This Row],[파견기록행]]))</f>
+        <f>IF(명단표[[#This Row],[구리행]]="","",INDEX(구리_종료,명단표[[#This Row],[구리행]]))</f>
         <v/>
       </c>
       <c r="R5" s="8">
-        <f>IF(명단표[[#This Row],[파견기록행]]="","",INDEX(파견표[파견과목(정규화)],명단표[[#This Row],[파견기록행]]))</f>
-        <v/>
-      </c>
-      <c r="S5" s="10">
-        <f>IF(명단표[[#This Row],[파견기록행]]="","",INDEX(파견표[시작일(계산)],명단표[[#This Row],[파견기록행]]))</f>
-        <v/>
-      </c>
-      <c r="T5" s="10">
-        <f>IF(명단표[[#This Row],[파견기록행]]="","",INDEX(파견표[종료일(계산)],명단표[[#This Row],[파견기록행]]))</f>
+        <f>IF(명단표[[#This Row],[구리행]]="","",INDEX(구리_독자,명단표[[#This Row],[구리행]]))</f>
+        <v/>
+      </c>
+      <c r="S5" s="11">
+        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(명단표[[#This Row],[구리행]]&lt;&gt;"",MAX(0,DAY(EOMONTH(급여기준월,0))-N(명단표[[#This Row],[구리명단 근무일]])),IF(명단표[[#This Row],[기준월 근무병원]]="서울병원",DAY(EOMONTH(급여기준월,0)),0)))</f>
+        <v/>
+      </c>
+      <c r="T5" s="11">
+        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(명단표[[#This Row],[구리행]]&lt;&gt;"",N(명단표[[#This Row],[구리명단 근무일]]),IF(명단표[[#This Row],[기준월 근무병원]]="구리병원",DAY(EOMONTH(급여기준월,0)),0)))</f>
         <v/>
       </c>
       <c r="U5" s="8">
-        <f>IF(명단표[[#This Row],[파견기록행]]="","",INDEX(파견표[상태],명단표[[#This Row],[파견기록행]]))</f>
-        <v/>
-      </c>
-      <c r="V5" s="11">
-        <f>IF(명단표[[#This Row],[파견기록행]]="","",INDEX(파견표[파견일수(계산)],명단표[[#This Row],[파견기록행]]))</f>
-        <v/>
-      </c>
-      <c r="W5" s="11">
-        <f>IF(AND(명단표[[#This Row],[파견상태]]="파견중",ISNUMBER(명단표[[#This Row],[파견종료일]])),명단표[[#This Row],[파견종료일]]-TODAY(),"")</f>
-        <v/>
-      </c>
-      <c r="X5" s="11">
-        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(명단표[[#This Row],[키]]="",0,SUMIFS(파견표[기준월 겹침일수],파견표[키],명단표[[#This Row],[키]])))</f>
-        <v/>
-      </c>
-      <c r="Y5" s="11">
-        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(명단표[[#This Row],[구리행]]&lt;&gt;"",MAX(0,DAY(EOMONTH(급여기준월,0))-N(명단표[[#This Row],[구리명단 근무일]])),IF(명단표[[#This Row],[키]]="",0,SUMIFS(파견표[기준월 겹침일수],파견표[키],명단표[[#This Row],[키]],파견표[파견병원(정규화)],"서울병원"))+IF(명단표[[#This Row],[기준월 근무병원]]="서울병원",MAX(0,DAY(EOMONTH(급여기준월,0))-N(명단표[[#This Row],[급여기준월 파견일수]])),0)))</f>
-        <v/>
-      </c>
-      <c r="Z5" s="11">
-        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(명단표[[#This Row],[구리행]]&lt;&gt;"",N(명단표[[#This Row],[구리명단 근무일]]),IF(명단표[[#This Row],[키]]="",0,SUMIFS(파견표[기준월 겹침일수],파견표[키],명단표[[#This Row],[키]],파견표[파견병원(정규화)],"구리병원"))+IF(명단표[[#This Row],[기준월 근무병원]]="구리병원",MAX(0,DAY(EOMONTH(급여기준월,0))-N(명단표[[#This Row],[급여기준월 파견일수]])),0)))</f>
+        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(명단표[[#This Row],[기준월 근무병원]]="","",IF(명단표[[#This Row],[구리행]]="",명단표[[#This Row],[기준월 근무병원]],IF(AND(명단표[[#This Row],[서울 근무일(기준월)]]&gt;=판정기준일,명단표[[#This Row],[구리 근무일(기준월)]]&lt;판정기준일),"서울병원",IF(AND(명단표[[#This Row],[구리 근무일(기준월)]]&gt;=판정기준일,명단표[[#This Row],[서울 근무일(기준월)]]&lt;판정기준일),"구리병원","⚠15일 판정불가(서울 "&amp;명단표[[#This Row],[서울 근무일(기준월)]]&amp;"일/구리 "&amp;명단표[[#This Row],[구리 근무일(기준월)]]&amp;"일)")))))</f>
+        <v/>
+      </c>
+      <c r="V5" s="8">
+        <f>IF(OR(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),명단표[[#This Row],[급여지급병원(기준월)]]=""),"",IF(명단표[[#This Row],[구리행]]&lt;&gt;"","서울 "&amp;명단표[[#This Row],[서울 근무일(기준월)]]&amp;"일 / 구리 "&amp;명단표[[#This Row],[구리 근무일(기준월)]]&amp;"일 (구리 근무자명단) → 15일 이상 근무 병원 지급",IF(AND(명단표[[#This Row],[인턴 기준월]]&lt;&gt;"",LEFT(명단표[[#This Row],[인턴 기준월]],1)&lt;&gt;"⚠"),"인턴 근무계획 → 그 달 근무병원 지급","구리 근무자명단에 없음 → 소속병원 지급")))</f>
+        <v/>
+      </c>
+      <c r="W5" s="8">
+        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(명단표[[#This Row],[기본자료행]]="","기본자료에 없는 사번",IF(COUNTIF(명단표[사번],명단표[[#This Row],[사번]])&gt;1,"중복 사번",IF(명단표[[#This Row],[소속병원]]="","소속(입사장소) 입력",IF(LEFT(명단표[[#This Row],[급여지급병원(기준월)]],1)="⚠","서울·구리 15일 판정 불가(양쪽 모두 이상/미만)",IF(IF(명단표[[#This Row],[인턴계획행]]="",0,N(INDEX(인턴계획표[입력오류],명단표[[#This Row],[인턴계획행]])))&gt;0,"인턴계획 입력오류 확인",IF(AND(명단표[[#This Row],[구리행]]="",COUNTIF(구리_이름,명단표[[#This Row],[이름]])&gt;0),"구리 근무자명단 연결 확인(동명이인·과 불일치)","정상")))))))</f>
+        <v/>
+      </c>
+      <c r="X5" s="6" t="inlineStr">
+        <is>
+          <t>예시 데이터</t>
+        </is>
+      </c>
+      <c r="Y5" s="8">
+        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IFERROR(_xlfn.XMATCH("S|"&amp;TRIM(명단표[[#This Row],[사번]]&amp;""),기본자료표[사번키]),""))</f>
+        <v/>
+      </c>
+      <c r="Z5" s="8">
+        <f>IF(명단표[[#This Row],[이름]]="","",명단표[[#This Row],[이름]]&amp;"|"&amp;명단표[[#This Row],[수련과목]])</f>
         <v/>
       </c>
       <c r="AA5" s="8">
-        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(명단표[[#This Row],[기준월 근무병원]]="","",IF(명단표[[#This Row],[다기관 겹침일수]]&gt;0,명단표[[#This Row],[소속병원]],IF(AND(N(명단표[[#This Row],[급여기준월 파견일수]])&lt;=0,명단표[[#This Row],[구리행]]=""),명단표[[#This Row],[기준월 근무병원]],IF(명단표[[#This Row],[서울 근무일(기준월)]]+명단표[[#This Row],[구리 근무일(기준월)]]=DAY(EOMONTH(급여기준월,0)),IF(AND(명단표[[#This Row],[서울 근무일(기준월)]]&gt;=판정기준일,명단표[[#This Row],[구리 근무일(기준월)]]&lt;판정기준일),"서울병원",IF(AND(명단표[[#This Row],[구리 근무일(기준월)]]&gt;=판정기준일,명단표[[#This Row],[서울 근무일(기준월)]]&lt;판정기준일),"구리병원","⚠15일 판정불가(서울 "&amp;명단표[[#This Row],[서울 근무일(기준월)]]&amp;"일/구리 "&amp;명단표[[#This Row],[구리 근무일(기준월)]]&amp;"일)")),IF(명단표[[#This Row],[기준월 대표파견행]]="",명단표[[#This Row],[소속병원]],IF(INDEX(파견표[파견근거(정규화)],명단표[[#This Row],[기준월 대표파견행]])="통합수련",INDEX(파견표[파견병원(정규화)],명단표[[#This Row],[기준월 대표파견행]]),명단표[[#This Row],[소속병원]])))))))</f>
+        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IFERROR(_xlfn.XMATCH("S|"&amp;TRIM(명단표[[#This Row],[사번]]&amp;""),인턴계획표[사번키]),""))</f>
         <v/>
       </c>
       <c r="AB5" s="8">
-        <f>IF(OR(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),명단표[[#This Row],[급여지급병원(기준월)]]=""),"",IF(명단표[[#This Row],[다기관 겹침일수]]&gt;0,"다기관 기간 → 소속병원 지급",IF(AND(N(명단표[[#This Row],[급여기준월 파견일수]])&lt;=0,명단표[[#This Row],[구리행]]=""),"파견 없음 → 그 달 근무병원 지급",IF(명단표[[#This Row],[서울 근무일(기준월)]]+명단표[[#This Row],[구리 근무일(기준월)]]=DAY(EOMONTH(급여기준월,0)),"서울 "&amp;명단표[[#This Row],[서울 근무일(기준월)]]&amp;"일 / 구리 "&amp;명단표[[#This Row],[구리 근무일(기준월)]]&amp;"일"&amp;IF(명단표[[#This Row],[구리행]]&lt;&gt;""," (구리 근무자명단 반영)","")&amp;" → 15일 이상 근무 병원 지급","타 병원 포함 → "&amp;IF(명단표[[#This Row],[기준월 대표파견행]]="","소속",INDEX(파견표[파견근거(정규화)],명단표[[#This Row],[기준월 대표파견행]]))&amp;" 규칙"))))</f>
+        <f>IF(OR(명단표[[#This Row],[인턴계획행]]="",인턴위치_이번=""),"",INDEX(인턴계획표[[정규화1]:[정규화6]],명단표[[#This Row],[인턴계획행]],인턴위치_이번)&amp;"")</f>
         <v/>
       </c>
       <c r="AC5" s="8">
-        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(명단표[[#This Row],[기본자료행]]="","기본자료에 없는 사번",IF(COUNTIF(명단표[사번],명단표[[#This Row],[사번]])&gt;1,"중복 사번",IF(명단표[[#This Row],[소속병원]]="","소속(입사장소) 입력",IF(IF(명단표[[#This Row],[키]]="",0,COUNTIFS(파견표[키],명단표[[#This Row],[키]],파견표[입력오류],"?*"))&gt;0,"파견수련계획 입력오류 확인",IF(LEFT(명단표[[#This Row],[급여지급병원(기준월)]],1)="⚠","서울·구리 15일 판정 불가(양쪽 모두 이상/미만)",IF(IF(명단표[[#This Row],[인턴계획행]]="",0,N(INDEX(인턴계획표[입력오류],명단표[[#This Row],[인턴계획행]])))&gt;0,"인턴계획 입력오류 확인",IF(AND(명단표[[#This Row],[구리행]]&lt;&gt;"",명단표[[#This Row],[기준월 근무병원]]&lt;&gt;"구리병원",IF(명단표[[#This Row],[키]]="",0,SUMIFS(파견표[기준월 겹침일수],파견표[키],명단표[[#This Row],[키]],파견표[파견병원(정규화)],"구리병원"))=0),"구리 근무자명단에만 있음(파견수련계획 확인)",IF(AND(명단표[[#This Row],[인턴계획행]]&lt;&gt;"",명단표[[#This Row],[파견상태]]&lt;&gt;"파견중",명단표[[#This Row],[현재 근무병원]]&lt;&gt;명단표[[#This Row],[소속병원]]),"인턴 타지역 근무: 파견 여부 확인","정상")))))))))</f>
+        <f>IF(OR(명단표[[#This Row],[인턴계획행]]="",인턴위치_기준월=""),"",INDEX(인턴계획표[[정규화1]:[정규화6]],명단표[[#This Row],[인턴계획행]],인턴위치_기준월)&amp;"")</f>
         <v/>
       </c>
       <c r="AD5" s="8">
-        <f>IF(명단표[[#This Row],[다기관 기록행]]="","","다기관 "&amp;TEXT(INDEX(파견표[다기관 시작],명단표[[#This Row],[다기관 기록행]]),"yyyy-mm-dd")&amp;"~"&amp;IF(ISNUMBER(INDEX(파견표[다기관 종료],명단표[[#This Row],[다기관 기록행]])),TEXT(INDEX(파견표[다기관 종료],명단표[[#This Row],[다기관 기록행]]),"yyyy-mm-dd"),""))</f>
-        <v/>
-      </c>
-      <c r="AE5" s="6" t="inlineStr">
-        <is>
-          <t>예시 데이터(종료됨)</t>
-        </is>
+        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(명단표[[#This Row],[입사장소]]&lt;&gt;"",명단표[[#This Row],[입사장소]],IF(명단표[[#This Row],[구리독자]]="구리독자","구리병원",IF(명단표[[#This Row],[근무지]]="","",_xlfn.XLOOKUP(TRIM(명단표[[#This Row],[근무지]]&amp;""),병원약칭표[표기],병원약칭표[정식 병원],명단표[[#This Row],[근무지]]&amp;"")))))</f>
+        <v/>
+      </c>
+      <c r="AE5" s="8">
+        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(AND(명단표[[#This Row],[인턴 기준월]]&lt;&gt;"",LEFT(명단표[[#This Row],[인턴 기준월]],1)&lt;&gt;"⚠"),LEFT(명단표[[#This Row],[인턴 기준월]],FIND(" ",명단표[[#This Row],[인턴 기준월]])-1),명단표[[#This Row],[소속병원]]))</f>
+        <v/>
       </c>
       <c r="AF5" s="8">
-        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IFERROR(_xlfn.XMATCH("S|"&amp;TRIM(명단표[[#This Row],[사번]]&amp;""),기본자료표[사번키]),""))</f>
-        <v/>
-      </c>
-      <c r="AG5" s="8">
-        <f>IF(TRIM(명단표[[#This Row],[전공의등록번호]]&amp;"")="","","R|"&amp;TRIM(명단표[[#This Row],[전공의등록번호]]&amp;""))</f>
+        <f>IF(명단표[[#This Row],[이름]]="","",_xlfn.LET(_xlpm.v_a,_xlfn.XMATCH(명단표[[#This Row],[이름|과]],구리_키),IF(ISNUMBER(_xlpm.v_a),_xlpm.v_a,IF(AND(COUNTIF(구리_이름,명단표[[#This Row],[이름]])=1,COUNTIF(명단표[이름],명단표[[#This Row],[이름]])=1),_xlfn.XMATCH(명단표[[#This Row],[이름]],구리_이름),""))))</f>
+        <v/>
+      </c>
+      <c r="AG5" s="11">
+        <f>IF(명단표[[#This Row],[구리행]]="","",INDEX(구리_근무일,명단표[[#This Row],[구리행]]))</f>
         <v/>
       </c>
       <c r="AH5" s="8">
-        <f>IF(명단표[[#This Row],[이름]]="","",명단표[[#This Row],[이름]]&amp;"|"&amp;명단표[[#This Row],[수련과목]])</f>
-        <v/>
-      </c>
-      <c r="AI5" s="8">
-        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IFERROR(_xlfn.XMATCH("S|"&amp;TRIM(명단표[[#This Row],[사번]]&amp;""),인턴계획표[사번키]),""))</f>
-        <v/>
-      </c>
-      <c r="AJ5" s="8">
-        <f>IF(OR(명단표[[#This Row],[인턴계획행]]="",인턴위치_이번=""),"",INDEX(인턴계획표[[정규화1]:[정규화6]],명단표[[#This Row],[인턴계획행]],인턴위치_이번)&amp;"")</f>
-        <v/>
-      </c>
-      <c r="AK5" s="8">
-        <f>IF(OR(명단표[[#This Row],[인턴계획행]]="",인턴위치_기준월=""),"",INDEX(인턴계획표[[정규화1]:[정규화6]],명단표[[#This Row],[인턴계획행]],인턴위치_기준월)&amp;"")</f>
-        <v/>
-      </c>
-      <c r="AL5" s="8">
-        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(명단표[[#This Row],[입사장소]]&lt;&gt;"",명단표[[#This Row],[입사장소]],IF(IF(명단표[[#This Row],[구리행]]="",FALSE,INDEX(구리_독자,명단표[[#This Row],[구리행]])="구리독자"),"구리병원",IF(명단표[[#This Row],[파견기록행]]&lt;&gt;"",_xlfn.LET(_xlpm.v_m,INDEX(파견표[모병원(정규화)],명단표[[#This Row],[파견기록행]]),IF(AND(_xlpm.v_m&lt;&gt;"",LEFT(_xlpm.v_m,1)&lt;&gt;"⚠"),_xlpm.v_m,IF(명단표[[#This Row],[근무지]]="","",_xlfn.XLOOKUP(TRIM(명단표[[#This Row],[근무지]]&amp;""),병원약칭표[표기],병원약칭표[정식 병원],명단표[[#This Row],[근무지]]&amp;"")))),IF(명단표[[#This Row],[근무지]]="","",_xlfn.XLOOKUP(TRIM(명단표[[#This Row],[근무지]]&amp;""),병원약칭표[표기],병원약칭표[정식 병원],명단표[[#This Row],[근무지]]&amp;""))))))</f>
-        <v/>
-      </c>
-      <c r="AM5" s="8">
-        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(AND(명단표[[#This Row],[인턴 기준월]]&lt;&gt;"",LEFT(명단표[[#This Row],[인턴 기준월]],1)&lt;&gt;"⚠"),LEFT(명단표[[#This Row],[인턴 기준월]],FIND(" ",명단표[[#This Row],[인턴 기준월]])-1),명단표[[#This Row],[소속병원]]))</f>
-        <v/>
-      </c>
-      <c r="AN5" s="8">
-        <f>IF(명단표[[#This Row],[키]]="","",IFERROR(_xlfn.XMATCH(명단표[[#This Row],[키]]&amp;"|파견중",파견표[키|상태]),IFERROR(_xlfn.XMATCH(명단표[[#This Row],[키]]&amp;"|파견예정",파견표[키|상태]),IFERROR(_xlfn.XMATCH(명단표[[#This Row],[키]]&amp;"|파견종료",파견표[키|상태]),""))))</f>
-        <v/>
-      </c>
-      <c r="AO5" s="8">
-        <f>IF(명단표[[#This Row],[키]]="","",IFERROR(_xlfn.XMATCH(명단표[[#This Row],[키]]&amp;"|월",파견표[키|월]),""))</f>
-        <v/>
-      </c>
-      <c r="AP5" s="8">
-        <f>IF(명단표[[#This Row],[키]]="","",IFERROR(_xlfn.XMATCH(명단표[[#This Row],[키]]&amp;"|다기관",파견표[키|다기관]),""))</f>
-        <v/>
-      </c>
-      <c r="AQ5" s="11">
-        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),0,IF(명단표[[#This Row],[키]]="",0,SUMIFS(파견표[다기관 겹침일수],파견표[키],명단표[[#This Row],[키]])))</f>
-        <v/>
-      </c>
-      <c r="AR5" s="8">
-        <f>IF(명단표[[#This Row],[이름]]="","",_xlfn.LET(_xlpm.v_a,_xlfn.XMATCH(명단표[[#This Row],[이름|과]],구리_키),IF(ISNUMBER(_xlpm.v_a),_xlpm.v_a,IF(AND(COUNTIF(구리_이름,명단표[[#This Row],[이름]])=1,COUNTIF(명단표[이름],명단표[[#This Row],[이름]])=1),_xlfn.XMATCH(명단표[[#This Row],[이름]],구리_이름),""))))</f>
-        <v/>
-      </c>
-      <c r="AS5" s="11">
-        <f>IF(명단표[[#This Row],[구리행]]="","",INDEX(구리_근무일,명단표[[#This Row],[구리행]]))</f>
+        <f>IF(명단표[[#This Row],[구리행]]="","",_xlfn.LET(_xlpm.v_s,IFERROR(DATEVALUE(명단표[[#This Row],[구리 근무 시작일(기준월)]]),""),_xlpm.v_e,IFERROR(DATEVALUE(명단표[[#This Row],[구리 근무 종료일(기준월)]]),""),IF(AND(ISNUMBER(_xlpm.v_s),ISNUMBER(_xlpm.v_e)),IF(AND(TODAY()&gt;=_xlpm.v_s,TODAY()&lt;=_xlpm.v_e),"Y",""),"")))</f>
         <v/>
       </c>
     </row>
@@ -6745,132 +4871,88 @@
         </is>
       </c>
       <c r="N6" s="8">
-        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(AND(명단표[[#This Row],[파견상태]]="파견중",명단표[[#This Row],[파견병원]]&lt;&gt;""),명단표[[#This Row],[파견병원]],IF(AND(명단표[[#This Row],[인턴 이번달]]&lt;&gt;"",LEFT(명단표[[#This Row],[인턴 이번달]],1)&lt;&gt;"⚠"),LEFT(명단표[[#This Row],[인턴 이번달]],FIND(" ",명단표[[#This Row],[인턴 이번달]])-1),IF(명단표[[#This Row],[근무지]]="","",_xlfn.XLOOKUP(TRIM(명단표[[#This Row],[근무지]]&amp;""),병원약칭표[표기],병원약칭표[정식 병원],명단표[[#This Row],[근무지]]&amp;"")))))</f>
+        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(AND(명단표[[#This Row],[인턴 이번달]]&lt;&gt;"",LEFT(명단표[[#This Row],[인턴 이번달]],1)&lt;&gt;"⚠"),LEFT(명단표[[#This Row],[인턴 이번달]],FIND(" ",명단표[[#This Row],[인턴 이번달]])-1),IF(명단표[[#This Row],[구리 근무 중]]="Y","구리병원",IF(명단표[[#This Row],[근무지]]="","",_xlfn.XLOOKUP(TRIM(명단표[[#This Row],[근무지]]&amp;""),병원약칭표[표기],병원약칭표[정식 병원],명단표[[#This Row],[근무지]]&amp;"")))))</f>
         <v/>
       </c>
       <c r="O6" s="8">
-        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(AND(명단표[[#This Row],[파견상태]]="파견중",명단표[[#This Row],[파견병원]]&lt;&gt;""),IF(명단표[[#This Row],[파견진료과]]&lt;&gt;"",명단표[[#This Row],[파견진료과]],"파견과 미입력"),IF(AND(명단표[[#This Row],[인턴 이번달]]&lt;&gt;"",LEFT(명단표[[#This Row],[인턴 이번달]],1)&lt;&gt;"⚠"),MID(명단표[[#This Row],[인턴 이번달]],FIND(" ",명단표[[#This Row],[인턴 이번달]])+1,60),IF(명단표[[#This Row],[수련과목]]="","",IF(명단표[[#This Row],[수련과목]]="인턴","수련교육부(인턴)",명단표[[#This Row],[수련과목]])))))</f>
+        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(AND(명단표[[#This Row],[인턴 이번달]]&lt;&gt;"",LEFT(명단표[[#This Row],[인턴 이번달]],1)&lt;&gt;"⚠"),MID(명단표[[#This Row],[인턴 이번달]],FIND(" ",명단표[[#This Row],[인턴 이번달]])+1,60),IF(명단표[[#This Row],[수련과목]]="","",IF(명단표[[#This Row],[수련과목]]="인턴","수련교육부(인턴)",명단표[[#This Row],[수련과목]]))))</f>
         <v/>
       </c>
       <c r="P6" s="8">
-        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(명단표[[#This Row],[다기관 기록행]]&lt;&gt;"",IF(AND(TODAY()&gt;=INDEX(파견표[다기관 시작],명단표[[#This Row],[다기관 기록행]]),OR(NOT(ISNUMBER(INDEX(파견표[다기관 종료],명단표[[#This Row],[다기관 기록행]]))),TODAY()&lt;=INDEX(파견표[다기관 종료],명단표[[#This Row],[다기관 기록행]]))),"다기관",IF(명단표[[#This Row],[파견기록행]]="","",INDEX(파견표[파견근거(정규화)],명단표[[#This Row],[파견기록행]]))),IF(명단표[[#This Row],[파견기록행]]="","",INDEX(파견표[파견근거(정규화)],명단표[[#This Row],[파견기록행]]))))</f>
+        <f>IF(명단표[[#This Row],[구리행]]="","",INDEX(구리_시작,명단표[[#This Row],[구리행]]))</f>
         <v/>
       </c>
       <c r="Q6" s="8">
-        <f>IF(명단표[[#This Row],[파견기록행]]="","",INDEX(파견표[파견병원(정규화)],명단표[[#This Row],[파견기록행]]))</f>
+        <f>IF(명단표[[#This Row],[구리행]]="","",INDEX(구리_종료,명단표[[#This Row],[구리행]]))</f>
         <v/>
       </c>
       <c r="R6" s="8">
-        <f>IF(명단표[[#This Row],[파견기록행]]="","",INDEX(파견표[파견과목(정규화)],명단표[[#This Row],[파견기록행]]))</f>
-        <v/>
-      </c>
-      <c r="S6" s="10">
-        <f>IF(명단표[[#This Row],[파견기록행]]="","",INDEX(파견표[시작일(계산)],명단표[[#This Row],[파견기록행]]))</f>
-        <v/>
-      </c>
-      <c r="T6" s="10">
-        <f>IF(명단표[[#This Row],[파견기록행]]="","",INDEX(파견표[종료일(계산)],명단표[[#This Row],[파견기록행]]))</f>
+        <f>IF(명단표[[#This Row],[구리행]]="","",INDEX(구리_독자,명단표[[#This Row],[구리행]]))</f>
+        <v/>
+      </c>
+      <c r="S6" s="11">
+        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(명단표[[#This Row],[구리행]]&lt;&gt;"",MAX(0,DAY(EOMONTH(급여기준월,0))-N(명단표[[#This Row],[구리명단 근무일]])),IF(명단표[[#This Row],[기준월 근무병원]]="서울병원",DAY(EOMONTH(급여기준월,0)),0)))</f>
+        <v/>
+      </c>
+      <c r="T6" s="11">
+        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(명단표[[#This Row],[구리행]]&lt;&gt;"",N(명단표[[#This Row],[구리명단 근무일]]),IF(명단표[[#This Row],[기준월 근무병원]]="구리병원",DAY(EOMONTH(급여기준월,0)),0)))</f>
         <v/>
       </c>
       <c r="U6" s="8">
-        <f>IF(명단표[[#This Row],[파견기록행]]="","",INDEX(파견표[상태],명단표[[#This Row],[파견기록행]]))</f>
-        <v/>
-      </c>
-      <c r="V6" s="11">
-        <f>IF(명단표[[#This Row],[파견기록행]]="","",INDEX(파견표[파견일수(계산)],명단표[[#This Row],[파견기록행]]))</f>
-        <v/>
-      </c>
-      <c r="W6" s="11">
-        <f>IF(AND(명단표[[#This Row],[파견상태]]="파견중",ISNUMBER(명단표[[#This Row],[파견종료일]])),명단표[[#This Row],[파견종료일]]-TODAY(),"")</f>
-        <v/>
-      </c>
-      <c r="X6" s="11">
-        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(명단표[[#This Row],[키]]="",0,SUMIFS(파견표[기준월 겹침일수],파견표[키],명단표[[#This Row],[키]])))</f>
-        <v/>
-      </c>
-      <c r="Y6" s="11">
-        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(명단표[[#This Row],[구리행]]&lt;&gt;"",MAX(0,DAY(EOMONTH(급여기준월,0))-N(명단표[[#This Row],[구리명단 근무일]])),IF(명단표[[#This Row],[키]]="",0,SUMIFS(파견표[기준월 겹침일수],파견표[키],명단표[[#This Row],[키]],파견표[파견병원(정규화)],"서울병원"))+IF(명단표[[#This Row],[기준월 근무병원]]="서울병원",MAX(0,DAY(EOMONTH(급여기준월,0))-N(명단표[[#This Row],[급여기준월 파견일수]])),0)))</f>
-        <v/>
-      </c>
-      <c r="Z6" s="11">
-        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(명단표[[#This Row],[구리행]]&lt;&gt;"",N(명단표[[#This Row],[구리명단 근무일]]),IF(명단표[[#This Row],[키]]="",0,SUMIFS(파견표[기준월 겹침일수],파견표[키],명단표[[#This Row],[키]],파견표[파견병원(정규화)],"구리병원"))+IF(명단표[[#This Row],[기준월 근무병원]]="구리병원",MAX(0,DAY(EOMONTH(급여기준월,0))-N(명단표[[#This Row],[급여기준월 파견일수]])),0)))</f>
+        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(명단표[[#This Row],[기준월 근무병원]]="","",IF(명단표[[#This Row],[구리행]]="",명단표[[#This Row],[기준월 근무병원]],IF(AND(명단표[[#This Row],[서울 근무일(기준월)]]&gt;=판정기준일,명단표[[#This Row],[구리 근무일(기준월)]]&lt;판정기준일),"서울병원",IF(AND(명단표[[#This Row],[구리 근무일(기준월)]]&gt;=판정기준일,명단표[[#This Row],[서울 근무일(기준월)]]&lt;판정기준일),"구리병원","⚠15일 판정불가(서울 "&amp;명단표[[#This Row],[서울 근무일(기준월)]]&amp;"일/구리 "&amp;명단표[[#This Row],[구리 근무일(기준월)]]&amp;"일)")))))</f>
+        <v/>
+      </c>
+      <c r="V6" s="8">
+        <f>IF(OR(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),명단표[[#This Row],[급여지급병원(기준월)]]=""),"",IF(명단표[[#This Row],[구리행]]&lt;&gt;"","서울 "&amp;명단표[[#This Row],[서울 근무일(기준월)]]&amp;"일 / 구리 "&amp;명단표[[#This Row],[구리 근무일(기준월)]]&amp;"일 (구리 근무자명단) → 15일 이상 근무 병원 지급",IF(AND(명단표[[#This Row],[인턴 기준월]]&lt;&gt;"",LEFT(명단표[[#This Row],[인턴 기준월]],1)&lt;&gt;"⚠"),"인턴 근무계획 → 그 달 근무병원 지급","구리 근무자명단에 없음 → 소속병원 지급")))</f>
+        <v/>
+      </c>
+      <c r="W6" s="8">
+        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(명단표[[#This Row],[기본자료행]]="","기본자료에 없는 사번",IF(COUNTIF(명단표[사번],명단표[[#This Row],[사번]])&gt;1,"중복 사번",IF(명단표[[#This Row],[소속병원]]="","소속(입사장소) 입력",IF(LEFT(명단표[[#This Row],[급여지급병원(기준월)]],1)="⚠","서울·구리 15일 판정 불가(양쪽 모두 이상/미만)",IF(IF(명단표[[#This Row],[인턴계획행]]="",0,N(INDEX(인턴계획표[입력오류],명단표[[#This Row],[인턴계획행]])))&gt;0,"인턴계획 입력오류 확인",IF(AND(명단표[[#This Row],[구리행]]="",COUNTIF(구리_이름,명단표[[#This Row],[이름]])&gt;0),"구리 근무자명단 연결 확인(동명이인·과 불일치)","정상")))))))</f>
+        <v/>
+      </c>
+      <c r="X6" s="6" t="inlineStr">
+        <is>
+          <t>예시 데이터</t>
+        </is>
+      </c>
+      <c r="Y6" s="8">
+        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IFERROR(_xlfn.XMATCH("S|"&amp;TRIM(명단표[[#This Row],[사번]]&amp;""),기본자료표[사번키]),""))</f>
+        <v/>
+      </c>
+      <c r="Z6" s="8">
+        <f>IF(명단표[[#This Row],[이름]]="","",명단표[[#This Row],[이름]]&amp;"|"&amp;명단표[[#This Row],[수련과목]])</f>
         <v/>
       </c>
       <c r="AA6" s="8">
-        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(명단표[[#This Row],[기준월 근무병원]]="","",IF(명단표[[#This Row],[다기관 겹침일수]]&gt;0,명단표[[#This Row],[소속병원]],IF(AND(N(명단표[[#This Row],[급여기준월 파견일수]])&lt;=0,명단표[[#This Row],[구리행]]=""),명단표[[#This Row],[기준월 근무병원]],IF(명단표[[#This Row],[서울 근무일(기준월)]]+명단표[[#This Row],[구리 근무일(기준월)]]=DAY(EOMONTH(급여기준월,0)),IF(AND(명단표[[#This Row],[서울 근무일(기준월)]]&gt;=판정기준일,명단표[[#This Row],[구리 근무일(기준월)]]&lt;판정기준일),"서울병원",IF(AND(명단표[[#This Row],[구리 근무일(기준월)]]&gt;=판정기준일,명단표[[#This Row],[서울 근무일(기준월)]]&lt;판정기준일),"구리병원","⚠15일 판정불가(서울 "&amp;명단표[[#This Row],[서울 근무일(기준월)]]&amp;"일/구리 "&amp;명단표[[#This Row],[구리 근무일(기준월)]]&amp;"일)")),IF(명단표[[#This Row],[기준월 대표파견행]]="",명단표[[#This Row],[소속병원]],IF(INDEX(파견표[파견근거(정규화)],명단표[[#This Row],[기준월 대표파견행]])="통합수련",INDEX(파견표[파견병원(정규화)],명단표[[#This Row],[기준월 대표파견행]]),명단표[[#This Row],[소속병원]])))))))</f>
+        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IFERROR(_xlfn.XMATCH("S|"&amp;TRIM(명단표[[#This Row],[사번]]&amp;""),인턴계획표[사번키]),""))</f>
         <v/>
       </c>
       <c r="AB6" s="8">
-        <f>IF(OR(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),명단표[[#This Row],[급여지급병원(기준월)]]=""),"",IF(명단표[[#This Row],[다기관 겹침일수]]&gt;0,"다기관 기간 → 소속병원 지급",IF(AND(N(명단표[[#This Row],[급여기준월 파견일수]])&lt;=0,명단표[[#This Row],[구리행]]=""),"파견 없음 → 그 달 근무병원 지급",IF(명단표[[#This Row],[서울 근무일(기준월)]]+명단표[[#This Row],[구리 근무일(기준월)]]=DAY(EOMONTH(급여기준월,0)),"서울 "&amp;명단표[[#This Row],[서울 근무일(기준월)]]&amp;"일 / 구리 "&amp;명단표[[#This Row],[구리 근무일(기준월)]]&amp;"일"&amp;IF(명단표[[#This Row],[구리행]]&lt;&gt;""," (구리 근무자명단 반영)","")&amp;" → 15일 이상 근무 병원 지급","타 병원 포함 → "&amp;IF(명단표[[#This Row],[기준월 대표파견행]]="","소속",INDEX(파견표[파견근거(정규화)],명단표[[#This Row],[기준월 대표파견행]]))&amp;" 규칙"))))</f>
+        <f>IF(OR(명단표[[#This Row],[인턴계획행]]="",인턴위치_이번=""),"",INDEX(인턴계획표[[정규화1]:[정규화6]],명단표[[#This Row],[인턴계획행]],인턴위치_이번)&amp;"")</f>
         <v/>
       </c>
       <c r="AC6" s="8">
-        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(명단표[[#This Row],[기본자료행]]="","기본자료에 없는 사번",IF(COUNTIF(명단표[사번],명단표[[#This Row],[사번]])&gt;1,"중복 사번",IF(명단표[[#This Row],[소속병원]]="","소속(입사장소) 입력",IF(IF(명단표[[#This Row],[키]]="",0,COUNTIFS(파견표[키],명단표[[#This Row],[키]],파견표[입력오류],"?*"))&gt;0,"파견수련계획 입력오류 확인",IF(LEFT(명단표[[#This Row],[급여지급병원(기준월)]],1)="⚠","서울·구리 15일 판정 불가(양쪽 모두 이상/미만)",IF(IF(명단표[[#This Row],[인턴계획행]]="",0,N(INDEX(인턴계획표[입력오류],명단표[[#This Row],[인턴계획행]])))&gt;0,"인턴계획 입력오류 확인",IF(AND(명단표[[#This Row],[구리행]]&lt;&gt;"",명단표[[#This Row],[기준월 근무병원]]&lt;&gt;"구리병원",IF(명단표[[#This Row],[키]]="",0,SUMIFS(파견표[기준월 겹침일수],파견표[키],명단표[[#This Row],[키]],파견표[파견병원(정규화)],"구리병원"))=0),"구리 근무자명단에만 있음(파견수련계획 확인)",IF(AND(명단표[[#This Row],[인턴계획행]]&lt;&gt;"",명단표[[#This Row],[파견상태]]&lt;&gt;"파견중",명단표[[#This Row],[현재 근무병원]]&lt;&gt;명단표[[#This Row],[소속병원]]),"인턴 타지역 근무: 파견 여부 확인","정상")))))))))</f>
+        <f>IF(OR(명단표[[#This Row],[인턴계획행]]="",인턴위치_기준월=""),"",INDEX(인턴계획표[[정규화1]:[정규화6]],명단표[[#This Row],[인턴계획행]],인턴위치_기준월)&amp;"")</f>
         <v/>
       </c>
       <c r="AD6" s="8">
-        <f>IF(명단표[[#This Row],[다기관 기록행]]="","","다기관 "&amp;TEXT(INDEX(파견표[다기관 시작],명단표[[#This Row],[다기관 기록행]]),"yyyy-mm-dd")&amp;"~"&amp;IF(ISNUMBER(INDEX(파견표[다기관 종료],명단표[[#This Row],[다기관 기록행]])),TEXT(INDEX(파견표[다기관 종료],명단표[[#This Row],[다기관 기록행]]),"yyyy-mm-dd"),""))</f>
-        <v/>
-      </c>
-      <c r="AE6" s="6" t="inlineStr">
-        <is>
-          <t>예시 데이터</t>
-        </is>
+        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(명단표[[#This Row],[입사장소]]&lt;&gt;"",명단표[[#This Row],[입사장소]],IF(명단표[[#This Row],[구리독자]]="구리독자","구리병원",IF(명단표[[#This Row],[근무지]]="","",_xlfn.XLOOKUP(TRIM(명단표[[#This Row],[근무지]]&amp;""),병원약칭표[표기],병원약칭표[정식 병원],명단표[[#This Row],[근무지]]&amp;"")))))</f>
+        <v/>
+      </c>
+      <c r="AE6" s="8">
+        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(AND(명단표[[#This Row],[인턴 기준월]]&lt;&gt;"",LEFT(명단표[[#This Row],[인턴 기준월]],1)&lt;&gt;"⚠"),LEFT(명단표[[#This Row],[인턴 기준월]],FIND(" ",명단표[[#This Row],[인턴 기준월]])-1),명단표[[#This Row],[소속병원]]))</f>
+        <v/>
       </c>
       <c r="AF6" s="8">
-        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IFERROR(_xlfn.XMATCH("S|"&amp;TRIM(명단표[[#This Row],[사번]]&amp;""),기본자료표[사번키]),""))</f>
-        <v/>
-      </c>
-      <c r="AG6" s="8">
-        <f>IF(TRIM(명단표[[#This Row],[전공의등록번호]]&amp;"")="","","R|"&amp;TRIM(명단표[[#This Row],[전공의등록번호]]&amp;""))</f>
+        <f>IF(명단표[[#This Row],[이름]]="","",_xlfn.LET(_xlpm.v_a,_xlfn.XMATCH(명단표[[#This Row],[이름|과]],구리_키),IF(ISNUMBER(_xlpm.v_a),_xlpm.v_a,IF(AND(COUNTIF(구리_이름,명단표[[#This Row],[이름]])=1,COUNTIF(명단표[이름],명단표[[#This Row],[이름]])=1),_xlfn.XMATCH(명단표[[#This Row],[이름]],구리_이름),""))))</f>
+        <v/>
+      </c>
+      <c r="AG6" s="11">
+        <f>IF(명단표[[#This Row],[구리행]]="","",INDEX(구리_근무일,명단표[[#This Row],[구리행]]))</f>
         <v/>
       </c>
       <c r="AH6" s="8">
-        <f>IF(명단표[[#This Row],[이름]]="","",명단표[[#This Row],[이름]]&amp;"|"&amp;명단표[[#This Row],[수련과목]])</f>
-        <v/>
-      </c>
-      <c r="AI6" s="8">
-        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IFERROR(_xlfn.XMATCH("S|"&amp;TRIM(명단표[[#This Row],[사번]]&amp;""),인턴계획표[사번키]),""))</f>
-        <v/>
-      </c>
-      <c r="AJ6" s="8">
-        <f>IF(OR(명단표[[#This Row],[인턴계획행]]="",인턴위치_이번=""),"",INDEX(인턴계획표[[정규화1]:[정규화6]],명단표[[#This Row],[인턴계획행]],인턴위치_이번)&amp;"")</f>
-        <v/>
-      </c>
-      <c r="AK6" s="8">
-        <f>IF(OR(명단표[[#This Row],[인턴계획행]]="",인턴위치_기준월=""),"",INDEX(인턴계획표[[정규화1]:[정규화6]],명단표[[#This Row],[인턴계획행]],인턴위치_기준월)&amp;"")</f>
-        <v/>
-      </c>
-      <c r="AL6" s="8">
-        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(명단표[[#This Row],[입사장소]]&lt;&gt;"",명단표[[#This Row],[입사장소]],IF(IF(명단표[[#This Row],[구리행]]="",FALSE,INDEX(구리_독자,명단표[[#This Row],[구리행]])="구리독자"),"구리병원",IF(명단표[[#This Row],[파견기록행]]&lt;&gt;"",_xlfn.LET(_xlpm.v_m,INDEX(파견표[모병원(정규화)],명단표[[#This Row],[파견기록행]]),IF(AND(_xlpm.v_m&lt;&gt;"",LEFT(_xlpm.v_m,1)&lt;&gt;"⚠"),_xlpm.v_m,IF(명단표[[#This Row],[근무지]]="","",_xlfn.XLOOKUP(TRIM(명단표[[#This Row],[근무지]]&amp;""),병원약칭표[표기],병원약칭표[정식 병원],명단표[[#This Row],[근무지]]&amp;"")))),IF(명단표[[#This Row],[근무지]]="","",_xlfn.XLOOKUP(TRIM(명단표[[#This Row],[근무지]]&amp;""),병원약칭표[표기],병원약칭표[정식 병원],명단표[[#This Row],[근무지]]&amp;""))))))</f>
-        <v/>
-      </c>
-      <c r="AM6" s="8">
-        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(AND(명단표[[#This Row],[인턴 기준월]]&lt;&gt;"",LEFT(명단표[[#This Row],[인턴 기준월]],1)&lt;&gt;"⚠"),LEFT(명단표[[#This Row],[인턴 기준월]],FIND(" ",명단표[[#This Row],[인턴 기준월]])-1),명단표[[#This Row],[소속병원]]))</f>
-        <v/>
-      </c>
-      <c r="AN6" s="8">
-        <f>IF(명단표[[#This Row],[키]]="","",IFERROR(_xlfn.XMATCH(명단표[[#This Row],[키]]&amp;"|파견중",파견표[키|상태]),IFERROR(_xlfn.XMATCH(명단표[[#This Row],[키]]&amp;"|파견예정",파견표[키|상태]),IFERROR(_xlfn.XMATCH(명단표[[#This Row],[키]]&amp;"|파견종료",파견표[키|상태]),""))))</f>
-        <v/>
-      </c>
-      <c r="AO6" s="8">
-        <f>IF(명단표[[#This Row],[키]]="","",IFERROR(_xlfn.XMATCH(명단표[[#This Row],[키]]&amp;"|월",파견표[키|월]),""))</f>
-        <v/>
-      </c>
-      <c r="AP6" s="8">
-        <f>IF(명단표[[#This Row],[키]]="","",IFERROR(_xlfn.XMATCH(명단표[[#This Row],[키]]&amp;"|다기관",파견표[키|다기관]),""))</f>
-        <v/>
-      </c>
-      <c r="AQ6" s="11">
-        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),0,IF(명단표[[#This Row],[키]]="",0,SUMIFS(파견표[다기관 겹침일수],파견표[키],명단표[[#This Row],[키]])))</f>
-        <v/>
-      </c>
-      <c r="AR6" s="8">
-        <f>IF(명단표[[#This Row],[이름]]="","",_xlfn.LET(_xlpm.v_a,_xlfn.XMATCH(명단표[[#This Row],[이름|과]],구리_키),IF(ISNUMBER(_xlpm.v_a),_xlpm.v_a,IF(AND(COUNTIF(구리_이름,명단표[[#This Row],[이름]])=1,COUNTIF(명단표[이름],명단표[[#This Row],[이름]])=1),_xlfn.XMATCH(명단표[[#This Row],[이름]],구리_이름),""))))</f>
-        <v/>
-      </c>
-      <c r="AS6" s="11">
-        <f>IF(명단표[[#This Row],[구리행]]="","",INDEX(구리_근무일,명단표[[#This Row],[구리행]]))</f>
+        <f>IF(명단표[[#This Row],[구리행]]="","",_xlfn.LET(_xlpm.v_s,IFERROR(DATEVALUE(명단표[[#This Row],[구리 근무 시작일(기준월)]]),""),_xlpm.v_e,IFERROR(DATEVALUE(명단표[[#This Row],[구리 근무 종료일(기준월)]]),""),IF(AND(ISNUMBER(_xlpm.v_s),ISNUMBER(_xlpm.v_e)),IF(AND(TODAY()&gt;=_xlpm.v_s,TODAY()&lt;=_xlpm.v_e),"Y",""),"")))</f>
         <v/>
       </c>
     </row>
@@ -6930,132 +5012,88 @@
         </is>
       </c>
       <c r="N7" s="8">
-        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(AND(명단표[[#This Row],[파견상태]]="파견중",명단표[[#This Row],[파견병원]]&lt;&gt;""),명단표[[#This Row],[파견병원]],IF(AND(명단표[[#This Row],[인턴 이번달]]&lt;&gt;"",LEFT(명단표[[#This Row],[인턴 이번달]],1)&lt;&gt;"⚠"),LEFT(명단표[[#This Row],[인턴 이번달]],FIND(" ",명단표[[#This Row],[인턴 이번달]])-1),IF(명단표[[#This Row],[근무지]]="","",_xlfn.XLOOKUP(TRIM(명단표[[#This Row],[근무지]]&amp;""),병원약칭표[표기],병원약칭표[정식 병원],명단표[[#This Row],[근무지]]&amp;"")))))</f>
+        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(AND(명단표[[#This Row],[인턴 이번달]]&lt;&gt;"",LEFT(명단표[[#This Row],[인턴 이번달]],1)&lt;&gt;"⚠"),LEFT(명단표[[#This Row],[인턴 이번달]],FIND(" ",명단표[[#This Row],[인턴 이번달]])-1),IF(명단표[[#This Row],[구리 근무 중]]="Y","구리병원",IF(명단표[[#This Row],[근무지]]="","",_xlfn.XLOOKUP(TRIM(명단표[[#This Row],[근무지]]&amp;""),병원약칭표[표기],병원약칭표[정식 병원],명단표[[#This Row],[근무지]]&amp;"")))))</f>
         <v/>
       </c>
       <c r="O7" s="8">
-        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(AND(명단표[[#This Row],[파견상태]]="파견중",명단표[[#This Row],[파견병원]]&lt;&gt;""),IF(명단표[[#This Row],[파견진료과]]&lt;&gt;"",명단표[[#This Row],[파견진료과]],"파견과 미입력"),IF(AND(명단표[[#This Row],[인턴 이번달]]&lt;&gt;"",LEFT(명단표[[#This Row],[인턴 이번달]],1)&lt;&gt;"⚠"),MID(명단표[[#This Row],[인턴 이번달]],FIND(" ",명단표[[#This Row],[인턴 이번달]])+1,60),IF(명단표[[#This Row],[수련과목]]="","",IF(명단표[[#This Row],[수련과목]]="인턴","수련교육부(인턴)",명단표[[#This Row],[수련과목]])))))</f>
+        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(AND(명단표[[#This Row],[인턴 이번달]]&lt;&gt;"",LEFT(명단표[[#This Row],[인턴 이번달]],1)&lt;&gt;"⚠"),MID(명단표[[#This Row],[인턴 이번달]],FIND(" ",명단표[[#This Row],[인턴 이번달]])+1,60),IF(명단표[[#This Row],[수련과목]]="","",IF(명단표[[#This Row],[수련과목]]="인턴","수련교육부(인턴)",명단표[[#This Row],[수련과목]]))))</f>
         <v/>
       </c>
       <c r="P7" s="8">
-        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(명단표[[#This Row],[다기관 기록행]]&lt;&gt;"",IF(AND(TODAY()&gt;=INDEX(파견표[다기관 시작],명단표[[#This Row],[다기관 기록행]]),OR(NOT(ISNUMBER(INDEX(파견표[다기관 종료],명단표[[#This Row],[다기관 기록행]]))),TODAY()&lt;=INDEX(파견표[다기관 종료],명단표[[#This Row],[다기관 기록행]]))),"다기관",IF(명단표[[#This Row],[파견기록행]]="","",INDEX(파견표[파견근거(정규화)],명단표[[#This Row],[파견기록행]]))),IF(명단표[[#This Row],[파견기록행]]="","",INDEX(파견표[파견근거(정규화)],명단표[[#This Row],[파견기록행]]))))</f>
+        <f>IF(명단표[[#This Row],[구리행]]="","",INDEX(구리_시작,명단표[[#This Row],[구리행]]))</f>
         <v/>
       </c>
       <c r="Q7" s="8">
-        <f>IF(명단표[[#This Row],[파견기록행]]="","",INDEX(파견표[파견병원(정규화)],명단표[[#This Row],[파견기록행]]))</f>
+        <f>IF(명단표[[#This Row],[구리행]]="","",INDEX(구리_종료,명단표[[#This Row],[구리행]]))</f>
         <v/>
       </c>
       <c r="R7" s="8">
-        <f>IF(명단표[[#This Row],[파견기록행]]="","",INDEX(파견표[파견과목(정규화)],명단표[[#This Row],[파견기록행]]))</f>
-        <v/>
-      </c>
-      <c r="S7" s="10">
-        <f>IF(명단표[[#This Row],[파견기록행]]="","",INDEX(파견표[시작일(계산)],명단표[[#This Row],[파견기록행]]))</f>
-        <v/>
-      </c>
-      <c r="T7" s="10">
-        <f>IF(명단표[[#This Row],[파견기록행]]="","",INDEX(파견표[종료일(계산)],명단표[[#This Row],[파견기록행]]))</f>
+        <f>IF(명단표[[#This Row],[구리행]]="","",INDEX(구리_독자,명단표[[#This Row],[구리행]]))</f>
+        <v/>
+      </c>
+      <c r="S7" s="11">
+        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(명단표[[#This Row],[구리행]]&lt;&gt;"",MAX(0,DAY(EOMONTH(급여기준월,0))-N(명단표[[#This Row],[구리명단 근무일]])),IF(명단표[[#This Row],[기준월 근무병원]]="서울병원",DAY(EOMONTH(급여기준월,0)),0)))</f>
+        <v/>
+      </c>
+      <c r="T7" s="11">
+        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(명단표[[#This Row],[구리행]]&lt;&gt;"",N(명단표[[#This Row],[구리명단 근무일]]),IF(명단표[[#This Row],[기준월 근무병원]]="구리병원",DAY(EOMONTH(급여기준월,0)),0)))</f>
         <v/>
       </c>
       <c r="U7" s="8">
-        <f>IF(명단표[[#This Row],[파견기록행]]="","",INDEX(파견표[상태],명단표[[#This Row],[파견기록행]]))</f>
-        <v/>
-      </c>
-      <c r="V7" s="11">
-        <f>IF(명단표[[#This Row],[파견기록행]]="","",INDEX(파견표[파견일수(계산)],명단표[[#This Row],[파견기록행]]))</f>
-        <v/>
-      </c>
-      <c r="W7" s="11">
-        <f>IF(AND(명단표[[#This Row],[파견상태]]="파견중",ISNUMBER(명단표[[#This Row],[파견종료일]])),명단표[[#This Row],[파견종료일]]-TODAY(),"")</f>
-        <v/>
-      </c>
-      <c r="X7" s="11">
-        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(명단표[[#This Row],[키]]="",0,SUMIFS(파견표[기준월 겹침일수],파견표[키],명단표[[#This Row],[키]])))</f>
-        <v/>
-      </c>
-      <c r="Y7" s="11">
-        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(명단표[[#This Row],[구리행]]&lt;&gt;"",MAX(0,DAY(EOMONTH(급여기준월,0))-N(명단표[[#This Row],[구리명단 근무일]])),IF(명단표[[#This Row],[키]]="",0,SUMIFS(파견표[기준월 겹침일수],파견표[키],명단표[[#This Row],[키]],파견표[파견병원(정규화)],"서울병원"))+IF(명단표[[#This Row],[기준월 근무병원]]="서울병원",MAX(0,DAY(EOMONTH(급여기준월,0))-N(명단표[[#This Row],[급여기준월 파견일수]])),0)))</f>
-        <v/>
-      </c>
-      <c r="Z7" s="11">
-        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(명단표[[#This Row],[구리행]]&lt;&gt;"",N(명단표[[#This Row],[구리명단 근무일]]),IF(명단표[[#This Row],[키]]="",0,SUMIFS(파견표[기준월 겹침일수],파견표[키],명단표[[#This Row],[키]],파견표[파견병원(정규화)],"구리병원"))+IF(명단표[[#This Row],[기준월 근무병원]]="구리병원",MAX(0,DAY(EOMONTH(급여기준월,0))-N(명단표[[#This Row],[급여기준월 파견일수]])),0)))</f>
+        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(명단표[[#This Row],[기준월 근무병원]]="","",IF(명단표[[#This Row],[구리행]]="",명단표[[#This Row],[기준월 근무병원]],IF(AND(명단표[[#This Row],[서울 근무일(기준월)]]&gt;=판정기준일,명단표[[#This Row],[구리 근무일(기준월)]]&lt;판정기준일),"서울병원",IF(AND(명단표[[#This Row],[구리 근무일(기준월)]]&gt;=판정기준일,명단표[[#This Row],[서울 근무일(기준월)]]&lt;판정기준일),"구리병원","⚠15일 판정불가(서울 "&amp;명단표[[#This Row],[서울 근무일(기준월)]]&amp;"일/구리 "&amp;명단표[[#This Row],[구리 근무일(기준월)]]&amp;"일)")))))</f>
+        <v/>
+      </c>
+      <c r="V7" s="8">
+        <f>IF(OR(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),명단표[[#This Row],[급여지급병원(기준월)]]=""),"",IF(명단표[[#This Row],[구리행]]&lt;&gt;"","서울 "&amp;명단표[[#This Row],[서울 근무일(기준월)]]&amp;"일 / 구리 "&amp;명단표[[#This Row],[구리 근무일(기준월)]]&amp;"일 (구리 근무자명단) → 15일 이상 근무 병원 지급",IF(AND(명단표[[#This Row],[인턴 기준월]]&lt;&gt;"",LEFT(명단표[[#This Row],[인턴 기준월]],1)&lt;&gt;"⚠"),"인턴 근무계획 → 그 달 근무병원 지급","구리 근무자명단에 없음 → 소속병원 지급")))</f>
+        <v/>
+      </c>
+      <c r="W7" s="8">
+        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(명단표[[#This Row],[기본자료행]]="","기본자료에 없는 사번",IF(COUNTIF(명단표[사번],명단표[[#This Row],[사번]])&gt;1,"중복 사번",IF(명단표[[#This Row],[소속병원]]="","소속(입사장소) 입력",IF(LEFT(명단표[[#This Row],[급여지급병원(기준월)]],1)="⚠","서울·구리 15일 판정 불가(양쪽 모두 이상/미만)",IF(IF(명단표[[#This Row],[인턴계획행]]="",0,N(INDEX(인턴계획표[입력오류],명단표[[#This Row],[인턴계획행]])))&gt;0,"인턴계획 입력오류 확인",IF(AND(명단표[[#This Row],[구리행]]="",COUNTIF(구리_이름,명단표[[#This Row],[이름]])&gt;0),"구리 근무자명단 연결 확인(동명이인·과 불일치)","정상")))))))</f>
+        <v/>
+      </c>
+      <c r="X7" s="6" t="inlineStr">
+        <is>
+          <t>예시(인턴)</t>
+        </is>
+      </c>
+      <c r="Y7" s="8">
+        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IFERROR(_xlfn.XMATCH("S|"&amp;TRIM(명단표[[#This Row],[사번]]&amp;""),기본자료표[사번키]),""))</f>
+        <v/>
+      </c>
+      <c r="Z7" s="8">
+        <f>IF(명단표[[#This Row],[이름]]="","",명단표[[#This Row],[이름]]&amp;"|"&amp;명단표[[#This Row],[수련과목]])</f>
         <v/>
       </c>
       <c r="AA7" s="8">
-        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(명단표[[#This Row],[기준월 근무병원]]="","",IF(명단표[[#This Row],[다기관 겹침일수]]&gt;0,명단표[[#This Row],[소속병원]],IF(AND(N(명단표[[#This Row],[급여기준월 파견일수]])&lt;=0,명단표[[#This Row],[구리행]]=""),명단표[[#This Row],[기준월 근무병원]],IF(명단표[[#This Row],[서울 근무일(기준월)]]+명단표[[#This Row],[구리 근무일(기준월)]]=DAY(EOMONTH(급여기준월,0)),IF(AND(명단표[[#This Row],[서울 근무일(기준월)]]&gt;=판정기준일,명단표[[#This Row],[구리 근무일(기준월)]]&lt;판정기준일),"서울병원",IF(AND(명단표[[#This Row],[구리 근무일(기준월)]]&gt;=판정기준일,명단표[[#This Row],[서울 근무일(기준월)]]&lt;판정기준일),"구리병원","⚠15일 판정불가(서울 "&amp;명단표[[#This Row],[서울 근무일(기준월)]]&amp;"일/구리 "&amp;명단표[[#This Row],[구리 근무일(기준월)]]&amp;"일)")),IF(명단표[[#This Row],[기준월 대표파견행]]="",명단표[[#This Row],[소속병원]],IF(INDEX(파견표[파견근거(정규화)],명단표[[#This Row],[기준월 대표파견행]])="통합수련",INDEX(파견표[파견병원(정규화)],명단표[[#This Row],[기준월 대표파견행]]),명단표[[#This Row],[소속병원]])))))))</f>
+        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IFERROR(_xlfn.XMATCH("S|"&amp;TRIM(명단표[[#This Row],[사번]]&amp;""),인턴계획표[사번키]),""))</f>
         <v/>
       </c>
       <c r="AB7" s="8">
-        <f>IF(OR(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),명단표[[#This Row],[급여지급병원(기준월)]]=""),"",IF(명단표[[#This Row],[다기관 겹침일수]]&gt;0,"다기관 기간 → 소속병원 지급",IF(AND(N(명단표[[#This Row],[급여기준월 파견일수]])&lt;=0,명단표[[#This Row],[구리행]]=""),"파견 없음 → 그 달 근무병원 지급",IF(명단표[[#This Row],[서울 근무일(기준월)]]+명단표[[#This Row],[구리 근무일(기준월)]]=DAY(EOMONTH(급여기준월,0)),"서울 "&amp;명단표[[#This Row],[서울 근무일(기준월)]]&amp;"일 / 구리 "&amp;명단표[[#This Row],[구리 근무일(기준월)]]&amp;"일"&amp;IF(명단표[[#This Row],[구리행]]&lt;&gt;""," (구리 근무자명단 반영)","")&amp;" → 15일 이상 근무 병원 지급","타 병원 포함 → "&amp;IF(명단표[[#This Row],[기준월 대표파견행]]="","소속",INDEX(파견표[파견근거(정규화)],명단표[[#This Row],[기준월 대표파견행]]))&amp;" 규칙"))))</f>
+        <f>IF(OR(명단표[[#This Row],[인턴계획행]]="",인턴위치_이번=""),"",INDEX(인턴계획표[[정규화1]:[정규화6]],명단표[[#This Row],[인턴계획행]],인턴위치_이번)&amp;"")</f>
         <v/>
       </c>
       <c r="AC7" s="8">
-        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(명단표[[#This Row],[기본자료행]]="","기본자료에 없는 사번",IF(COUNTIF(명단표[사번],명단표[[#This Row],[사번]])&gt;1,"중복 사번",IF(명단표[[#This Row],[소속병원]]="","소속(입사장소) 입력",IF(IF(명단표[[#This Row],[키]]="",0,COUNTIFS(파견표[키],명단표[[#This Row],[키]],파견표[입력오류],"?*"))&gt;0,"파견수련계획 입력오류 확인",IF(LEFT(명단표[[#This Row],[급여지급병원(기준월)]],1)="⚠","서울·구리 15일 판정 불가(양쪽 모두 이상/미만)",IF(IF(명단표[[#This Row],[인턴계획행]]="",0,N(INDEX(인턴계획표[입력오류],명단표[[#This Row],[인턴계획행]])))&gt;0,"인턴계획 입력오류 확인",IF(AND(명단표[[#This Row],[구리행]]&lt;&gt;"",명단표[[#This Row],[기준월 근무병원]]&lt;&gt;"구리병원",IF(명단표[[#This Row],[키]]="",0,SUMIFS(파견표[기준월 겹침일수],파견표[키],명단표[[#This Row],[키]],파견표[파견병원(정규화)],"구리병원"))=0),"구리 근무자명단에만 있음(파견수련계획 확인)",IF(AND(명단표[[#This Row],[인턴계획행]]&lt;&gt;"",명단표[[#This Row],[파견상태]]&lt;&gt;"파견중",명단표[[#This Row],[현재 근무병원]]&lt;&gt;명단표[[#This Row],[소속병원]]),"인턴 타지역 근무: 파견 여부 확인","정상")))))))))</f>
+        <f>IF(OR(명단표[[#This Row],[인턴계획행]]="",인턴위치_기준월=""),"",INDEX(인턴계획표[[정규화1]:[정규화6]],명단표[[#This Row],[인턴계획행]],인턴위치_기준월)&amp;"")</f>
         <v/>
       </c>
       <c r="AD7" s="8">
-        <f>IF(명단표[[#This Row],[다기관 기록행]]="","","다기관 "&amp;TEXT(INDEX(파견표[다기관 시작],명단표[[#This Row],[다기관 기록행]]),"yyyy-mm-dd")&amp;"~"&amp;IF(ISNUMBER(INDEX(파견표[다기관 종료],명단표[[#This Row],[다기관 기록행]])),TEXT(INDEX(파견표[다기관 종료],명단표[[#This Row],[다기관 기록행]]),"yyyy-mm-dd"),""))</f>
-        <v/>
-      </c>
-      <c r="AE7" s="6" t="inlineStr">
-        <is>
-          <t>예시(인턴)</t>
-        </is>
+        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(명단표[[#This Row],[입사장소]]&lt;&gt;"",명단표[[#This Row],[입사장소]],IF(명단표[[#This Row],[구리독자]]="구리독자","구리병원",IF(명단표[[#This Row],[근무지]]="","",_xlfn.XLOOKUP(TRIM(명단표[[#This Row],[근무지]]&amp;""),병원약칭표[표기],병원약칭표[정식 병원],명단표[[#This Row],[근무지]]&amp;"")))))</f>
+        <v/>
+      </c>
+      <c r="AE7" s="8">
+        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(AND(명단표[[#This Row],[인턴 기준월]]&lt;&gt;"",LEFT(명단표[[#This Row],[인턴 기준월]],1)&lt;&gt;"⚠"),LEFT(명단표[[#This Row],[인턴 기준월]],FIND(" ",명단표[[#This Row],[인턴 기준월]])-1),명단표[[#This Row],[소속병원]]))</f>
+        <v/>
       </c>
       <c r="AF7" s="8">
-        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IFERROR(_xlfn.XMATCH("S|"&amp;TRIM(명단표[[#This Row],[사번]]&amp;""),기본자료표[사번키]),""))</f>
-        <v/>
-      </c>
-      <c r="AG7" s="8">
-        <f>IF(TRIM(명단표[[#This Row],[전공의등록번호]]&amp;"")="","","R|"&amp;TRIM(명단표[[#This Row],[전공의등록번호]]&amp;""))</f>
+        <f>IF(명단표[[#This Row],[이름]]="","",_xlfn.LET(_xlpm.v_a,_xlfn.XMATCH(명단표[[#This Row],[이름|과]],구리_키),IF(ISNUMBER(_xlpm.v_a),_xlpm.v_a,IF(AND(COUNTIF(구리_이름,명단표[[#This Row],[이름]])=1,COUNTIF(명단표[이름],명단표[[#This Row],[이름]])=1),_xlfn.XMATCH(명단표[[#This Row],[이름]],구리_이름),""))))</f>
+        <v/>
+      </c>
+      <c r="AG7" s="11">
+        <f>IF(명단표[[#This Row],[구리행]]="","",INDEX(구리_근무일,명단표[[#This Row],[구리행]]))</f>
         <v/>
       </c>
       <c r="AH7" s="8">
-        <f>IF(명단표[[#This Row],[이름]]="","",명단표[[#This Row],[이름]]&amp;"|"&amp;명단표[[#This Row],[수련과목]])</f>
-        <v/>
-      </c>
-      <c r="AI7" s="8">
-        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IFERROR(_xlfn.XMATCH("S|"&amp;TRIM(명단표[[#This Row],[사번]]&amp;""),인턴계획표[사번키]),""))</f>
-        <v/>
-      </c>
-      <c r="AJ7" s="8">
-        <f>IF(OR(명단표[[#This Row],[인턴계획행]]="",인턴위치_이번=""),"",INDEX(인턴계획표[[정규화1]:[정규화6]],명단표[[#This Row],[인턴계획행]],인턴위치_이번)&amp;"")</f>
-        <v/>
-      </c>
-      <c r="AK7" s="8">
-        <f>IF(OR(명단표[[#This Row],[인턴계획행]]="",인턴위치_기준월=""),"",INDEX(인턴계획표[[정규화1]:[정규화6]],명단표[[#This Row],[인턴계획행]],인턴위치_기준월)&amp;"")</f>
-        <v/>
-      </c>
-      <c r="AL7" s="8">
-        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(명단표[[#This Row],[입사장소]]&lt;&gt;"",명단표[[#This Row],[입사장소]],IF(IF(명단표[[#This Row],[구리행]]="",FALSE,INDEX(구리_독자,명단표[[#This Row],[구리행]])="구리독자"),"구리병원",IF(명단표[[#This Row],[파견기록행]]&lt;&gt;"",_xlfn.LET(_xlpm.v_m,INDEX(파견표[모병원(정규화)],명단표[[#This Row],[파견기록행]]),IF(AND(_xlpm.v_m&lt;&gt;"",LEFT(_xlpm.v_m,1)&lt;&gt;"⚠"),_xlpm.v_m,IF(명단표[[#This Row],[근무지]]="","",_xlfn.XLOOKUP(TRIM(명단표[[#This Row],[근무지]]&amp;""),병원약칭표[표기],병원약칭표[정식 병원],명단표[[#This Row],[근무지]]&amp;"")))),IF(명단표[[#This Row],[근무지]]="","",_xlfn.XLOOKUP(TRIM(명단표[[#This Row],[근무지]]&amp;""),병원약칭표[표기],병원약칭표[정식 병원],명단표[[#This Row],[근무지]]&amp;""))))))</f>
-        <v/>
-      </c>
-      <c r="AM7" s="8">
-        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(AND(명단표[[#This Row],[인턴 기준월]]&lt;&gt;"",LEFT(명단표[[#This Row],[인턴 기준월]],1)&lt;&gt;"⚠"),LEFT(명단표[[#This Row],[인턴 기준월]],FIND(" ",명단표[[#This Row],[인턴 기준월]])-1),명단표[[#This Row],[소속병원]]))</f>
-        <v/>
-      </c>
-      <c r="AN7" s="8">
-        <f>IF(명단표[[#This Row],[키]]="","",IFERROR(_xlfn.XMATCH(명단표[[#This Row],[키]]&amp;"|파견중",파견표[키|상태]),IFERROR(_xlfn.XMATCH(명단표[[#This Row],[키]]&amp;"|파견예정",파견표[키|상태]),IFERROR(_xlfn.XMATCH(명단표[[#This Row],[키]]&amp;"|파견종료",파견표[키|상태]),""))))</f>
-        <v/>
-      </c>
-      <c r="AO7" s="8">
-        <f>IF(명단표[[#This Row],[키]]="","",IFERROR(_xlfn.XMATCH(명단표[[#This Row],[키]]&amp;"|월",파견표[키|월]),""))</f>
-        <v/>
-      </c>
-      <c r="AP7" s="8">
-        <f>IF(명단표[[#This Row],[키]]="","",IFERROR(_xlfn.XMATCH(명단표[[#This Row],[키]]&amp;"|다기관",파견표[키|다기관]),""))</f>
-        <v/>
-      </c>
-      <c r="AQ7" s="11">
-        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),0,IF(명단표[[#This Row],[키]]="",0,SUMIFS(파견표[다기관 겹침일수],파견표[키],명단표[[#This Row],[키]])))</f>
-        <v/>
-      </c>
-      <c r="AR7" s="8">
-        <f>IF(명단표[[#This Row],[이름]]="","",_xlfn.LET(_xlpm.v_a,_xlfn.XMATCH(명단표[[#This Row],[이름|과]],구리_키),IF(ISNUMBER(_xlpm.v_a),_xlpm.v_a,IF(AND(COUNTIF(구리_이름,명단표[[#This Row],[이름]])=1,COUNTIF(명단표[이름],명단표[[#This Row],[이름]])=1),_xlfn.XMATCH(명단표[[#This Row],[이름]],구리_이름),""))))</f>
-        <v/>
-      </c>
-      <c r="AS7" s="11">
-        <f>IF(명단표[[#This Row],[구리행]]="","",INDEX(구리_근무일,명단표[[#This Row],[구리행]]))</f>
+        <f>IF(명단표[[#This Row],[구리행]]="","",_xlfn.LET(_xlpm.v_s,IFERROR(DATEVALUE(명단표[[#This Row],[구리 근무 시작일(기준월)]]),""),_xlpm.v_e,IFERROR(DATEVALUE(명단표[[#This Row],[구리 근무 종료일(기준월)]]),""),IF(AND(ISNUMBER(_xlpm.v_s),ISNUMBER(_xlpm.v_e)),IF(AND(TODAY()&gt;=_xlpm.v_s,TODAY()&lt;=_xlpm.v_e),"Y",""),"")))</f>
         <v/>
       </c>
     </row>
@@ -7115,132 +5153,88 @@
         </is>
       </c>
       <c r="N8" s="8">
-        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(AND(명단표[[#This Row],[파견상태]]="파견중",명단표[[#This Row],[파견병원]]&lt;&gt;""),명단표[[#This Row],[파견병원]],IF(AND(명단표[[#This Row],[인턴 이번달]]&lt;&gt;"",LEFT(명단표[[#This Row],[인턴 이번달]],1)&lt;&gt;"⚠"),LEFT(명단표[[#This Row],[인턴 이번달]],FIND(" ",명단표[[#This Row],[인턴 이번달]])-1),IF(명단표[[#This Row],[근무지]]="","",_xlfn.XLOOKUP(TRIM(명단표[[#This Row],[근무지]]&amp;""),병원약칭표[표기],병원약칭표[정식 병원],명단표[[#This Row],[근무지]]&amp;"")))))</f>
+        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(AND(명단표[[#This Row],[인턴 이번달]]&lt;&gt;"",LEFT(명단표[[#This Row],[인턴 이번달]],1)&lt;&gt;"⚠"),LEFT(명단표[[#This Row],[인턴 이번달]],FIND(" ",명단표[[#This Row],[인턴 이번달]])-1),IF(명단표[[#This Row],[구리 근무 중]]="Y","구리병원",IF(명단표[[#This Row],[근무지]]="","",_xlfn.XLOOKUP(TRIM(명단표[[#This Row],[근무지]]&amp;""),병원약칭표[표기],병원약칭표[정식 병원],명단표[[#This Row],[근무지]]&amp;"")))))</f>
         <v/>
       </c>
       <c r="O8" s="8">
-        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(AND(명단표[[#This Row],[파견상태]]="파견중",명단표[[#This Row],[파견병원]]&lt;&gt;""),IF(명단표[[#This Row],[파견진료과]]&lt;&gt;"",명단표[[#This Row],[파견진료과]],"파견과 미입력"),IF(AND(명단표[[#This Row],[인턴 이번달]]&lt;&gt;"",LEFT(명단표[[#This Row],[인턴 이번달]],1)&lt;&gt;"⚠"),MID(명단표[[#This Row],[인턴 이번달]],FIND(" ",명단표[[#This Row],[인턴 이번달]])+1,60),IF(명단표[[#This Row],[수련과목]]="","",IF(명단표[[#This Row],[수련과목]]="인턴","수련교육부(인턴)",명단표[[#This Row],[수련과목]])))))</f>
+        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(AND(명단표[[#This Row],[인턴 이번달]]&lt;&gt;"",LEFT(명단표[[#This Row],[인턴 이번달]],1)&lt;&gt;"⚠"),MID(명단표[[#This Row],[인턴 이번달]],FIND(" ",명단표[[#This Row],[인턴 이번달]])+1,60),IF(명단표[[#This Row],[수련과목]]="","",IF(명단표[[#This Row],[수련과목]]="인턴","수련교육부(인턴)",명단표[[#This Row],[수련과목]]))))</f>
         <v/>
       </c>
       <c r="P8" s="8">
-        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(명단표[[#This Row],[다기관 기록행]]&lt;&gt;"",IF(AND(TODAY()&gt;=INDEX(파견표[다기관 시작],명단표[[#This Row],[다기관 기록행]]),OR(NOT(ISNUMBER(INDEX(파견표[다기관 종료],명단표[[#This Row],[다기관 기록행]]))),TODAY()&lt;=INDEX(파견표[다기관 종료],명단표[[#This Row],[다기관 기록행]]))),"다기관",IF(명단표[[#This Row],[파견기록행]]="","",INDEX(파견표[파견근거(정규화)],명단표[[#This Row],[파견기록행]]))),IF(명단표[[#This Row],[파견기록행]]="","",INDEX(파견표[파견근거(정규화)],명단표[[#This Row],[파견기록행]]))))</f>
+        <f>IF(명단표[[#This Row],[구리행]]="","",INDEX(구리_시작,명단표[[#This Row],[구리행]]))</f>
         <v/>
       </c>
       <c r="Q8" s="8">
-        <f>IF(명단표[[#This Row],[파견기록행]]="","",INDEX(파견표[파견병원(정규화)],명단표[[#This Row],[파견기록행]]))</f>
+        <f>IF(명단표[[#This Row],[구리행]]="","",INDEX(구리_종료,명단표[[#This Row],[구리행]]))</f>
         <v/>
       </c>
       <c r="R8" s="8">
-        <f>IF(명단표[[#This Row],[파견기록행]]="","",INDEX(파견표[파견과목(정규화)],명단표[[#This Row],[파견기록행]]))</f>
-        <v/>
-      </c>
-      <c r="S8" s="10">
-        <f>IF(명단표[[#This Row],[파견기록행]]="","",INDEX(파견표[시작일(계산)],명단표[[#This Row],[파견기록행]]))</f>
-        <v/>
-      </c>
-      <c r="T8" s="10">
-        <f>IF(명단표[[#This Row],[파견기록행]]="","",INDEX(파견표[종료일(계산)],명단표[[#This Row],[파견기록행]]))</f>
+        <f>IF(명단표[[#This Row],[구리행]]="","",INDEX(구리_독자,명단표[[#This Row],[구리행]]))</f>
+        <v/>
+      </c>
+      <c r="S8" s="11">
+        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(명단표[[#This Row],[구리행]]&lt;&gt;"",MAX(0,DAY(EOMONTH(급여기준월,0))-N(명단표[[#This Row],[구리명단 근무일]])),IF(명단표[[#This Row],[기준월 근무병원]]="서울병원",DAY(EOMONTH(급여기준월,0)),0)))</f>
+        <v/>
+      </c>
+      <c r="T8" s="11">
+        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(명단표[[#This Row],[구리행]]&lt;&gt;"",N(명단표[[#This Row],[구리명단 근무일]]),IF(명단표[[#This Row],[기준월 근무병원]]="구리병원",DAY(EOMONTH(급여기준월,0)),0)))</f>
         <v/>
       </c>
       <c r="U8" s="8">
-        <f>IF(명단표[[#This Row],[파견기록행]]="","",INDEX(파견표[상태],명단표[[#This Row],[파견기록행]]))</f>
-        <v/>
-      </c>
-      <c r="V8" s="11">
-        <f>IF(명단표[[#This Row],[파견기록행]]="","",INDEX(파견표[파견일수(계산)],명단표[[#This Row],[파견기록행]]))</f>
-        <v/>
-      </c>
-      <c r="W8" s="11">
-        <f>IF(AND(명단표[[#This Row],[파견상태]]="파견중",ISNUMBER(명단표[[#This Row],[파견종료일]])),명단표[[#This Row],[파견종료일]]-TODAY(),"")</f>
-        <v/>
-      </c>
-      <c r="X8" s="11">
-        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(명단표[[#This Row],[키]]="",0,SUMIFS(파견표[기준월 겹침일수],파견표[키],명단표[[#This Row],[키]])))</f>
-        <v/>
-      </c>
-      <c r="Y8" s="11">
-        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(명단표[[#This Row],[구리행]]&lt;&gt;"",MAX(0,DAY(EOMONTH(급여기준월,0))-N(명단표[[#This Row],[구리명단 근무일]])),IF(명단표[[#This Row],[키]]="",0,SUMIFS(파견표[기준월 겹침일수],파견표[키],명단표[[#This Row],[키]],파견표[파견병원(정규화)],"서울병원"))+IF(명단표[[#This Row],[기준월 근무병원]]="서울병원",MAX(0,DAY(EOMONTH(급여기준월,0))-N(명단표[[#This Row],[급여기준월 파견일수]])),0)))</f>
-        <v/>
-      </c>
-      <c r="Z8" s="11">
-        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(명단표[[#This Row],[구리행]]&lt;&gt;"",N(명단표[[#This Row],[구리명단 근무일]]),IF(명단표[[#This Row],[키]]="",0,SUMIFS(파견표[기준월 겹침일수],파견표[키],명단표[[#This Row],[키]],파견표[파견병원(정규화)],"구리병원"))+IF(명단표[[#This Row],[기준월 근무병원]]="구리병원",MAX(0,DAY(EOMONTH(급여기준월,0))-N(명단표[[#This Row],[급여기준월 파견일수]])),0)))</f>
+        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(명단표[[#This Row],[기준월 근무병원]]="","",IF(명단표[[#This Row],[구리행]]="",명단표[[#This Row],[기준월 근무병원]],IF(AND(명단표[[#This Row],[서울 근무일(기준월)]]&gt;=판정기준일,명단표[[#This Row],[구리 근무일(기준월)]]&lt;판정기준일),"서울병원",IF(AND(명단표[[#This Row],[구리 근무일(기준월)]]&gt;=판정기준일,명단표[[#This Row],[서울 근무일(기준월)]]&lt;판정기준일),"구리병원","⚠15일 판정불가(서울 "&amp;명단표[[#This Row],[서울 근무일(기준월)]]&amp;"일/구리 "&amp;명단표[[#This Row],[구리 근무일(기준월)]]&amp;"일)")))))</f>
+        <v/>
+      </c>
+      <c r="V8" s="8">
+        <f>IF(OR(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),명단표[[#This Row],[급여지급병원(기준월)]]=""),"",IF(명단표[[#This Row],[구리행]]&lt;&gt;"","서울 "&amp;명단표[[#This Row],[서울 근무일(기준월)]]&amp;"일 / 구리 "&amp;명단표[[#This Row],[구리 근무일(기준월)]]&amp;"일 (구리 근무자명단) → 15일 이상 근무 병원 지급",IF(AND(명단표[[#This Row],[인턴 기준월]]&lt;&gt;"",LEFT(명단표[[#This Row],[인턴 기준월]],1)&lt;&gt;"⚠"),"인턴 근무계획 → 그 달 근무병원 지급","구리 근무자명단에 없음 → 소속병원 지급")))</f>
+        <v/>
+      </c>
+      <c r="W8" s="8">
+        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(명단표[[#This Row],[기본자료행]]="","기본자료에 없는 사번",IF(COUNTIF(명단표[사번],명단표[[#This Row],[사번]])&gt;1,"중복 사번",IF(명단표[[#This Row],[소속병원]]="","소속(입사장소) 입력",IF(LEFT(명단표[[#This Row],[급여지급병원(기준월)]],1)="⚠","서울·구리 15일 판정 불가(양쪽 모두 이상/미만)",IF(IF(명단표[[#This Row],[인턴계획행]]="",0,N(INDEX(인턴계획표[입력오류],명단표[[#This Row],[인턴계획행]])))&gt;0,"인턴계획 입력오류 확인",IF(AND(명단표[[#This Row],[구리행]]="",COUNTIF(구리_이름,명단표[[#This Row],[이름]])&gt;0),"구리 근무자명단 연결 확인(동명이인·과 불일치)","정상")))))))</f>
+        <v/>
+      </c>
+      <c r="X8" s="6" t="inlineStr">
+        <is>
+          <t>예시(인턴)</t>
+        </is>
+      </c>
+      <c r="Y8" s="8">
+        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IFERROR(_xlfn.XMATCH("S|"&amp;TRIM(명단표[[#This Row],[사번]]&amp;""),기본자료표[사번키]),""))</f>
+        <v/>
+      </c>
+      <c r="Z8" s="8">
+        <f>IF(명단표[[#This Row],[이름]]="","",명단표[[#This Row],[이름]]&amp;"|"&amp;명단표[[#This Row],[수련과목]])</f>
         <v/>
       </c>
       <c r="AA8" s="8">
-        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(명단표[[#This Row],[기준월 근무병원]]="","",IF(명단표[[#This Row],[다기관 겹침일수]]&gt;0,명단표[[#This Row],[소속병원]],IF(AND(N(명단표[[#This Row],[급여기준월 파견일수]])&lt;=0,명단표[[#This Row],[구리행]]=""),명단표[[#This Row],[기준월 근무병원]],IF(명단표[[#This Row],[서울 근무일(기준월)]]+명단표[[#This Row],[구리 근무일(기준월)]]=DAY(EOMONTH(급여기준월,0)),IF(AND(명단표[[#This Row],[서울 근무일(기준월)]]&gt;=판정기준일,명단표[[#This Row],[구리 근무일(기준월)]]&lt;판정기준일),"서울병원",IF(AND(명단표[[#This Row],[구리 근무일(기준월)]]&gt;=판정기준일,명단표[[#This Row],[서울 근무일(기준월)]]&lt;판정기준일),"구리병원","⚠15일 판정불가(서울 "&amp;명단표[[#This Row],[서울 근무일(기준월)]]&amp;"일/구리 "&amp;명단표[[#This Row],[구리 근무일(기준월)]]&amp;"일)")),IF(명단표[[#This Row],[기준월 대표파견행]]="",명단표[[#This Row],[소속병원]],IF(INDEX(파견표[파견근거(정규화)],명단표[[#This Row],[기준월 대표파견행]])="통합수련",INDEX(파견표[파견병원(정규화)],명단표[[#This Row],[기준월 대표파견행]]),명단표[[#This Row],[소속병원]])))))))</f>
+        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IFERROR(_xlfn.XMATCH("S|"&amp;TRIM(명단표[[#This Row],[사번]]&amp;""),인턴계획표[사번키]),""))</f>
         <v/>
       </c>
       <c r="AB8" s="8">
-        <f>IF(OR(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),명단표[[#This Row],[급여지급병원(기준월)]]=""),"",IF(명단표[[#This Row],[다기관 겹침일수]]&gt;0,"다기관 기간 → 소속병원 지급",IF(AND(N(명단표[[#This Row],[급여기준월 파견일수]])&lt;=0,명단표[[#This Row],[구리행]]=""),"파견 없음 → 그 달 근무병원 지급",IF(명단표[[#This Row],[서울 근무일(기준월)]]+명단표[[#This Row],[구리 근무일(기준월)]]=DAY(EOMONTH(급여기준월,0)),"서울 "&amp;명단표[[#This Row],[서울 근무일(기준월)]]&amp;"일 / 구리 "&amp;명단표[[#This Row],[구리 근무일(기준월)]]&amp;"일"&amp;IF(명단표[[#This Row],[구리행]]&lt;&gt;""," (구리 근무자명단 반영)","")&amp;" → 15일 이상 근무 병원 지급","타 병원 포함 → "&amp;IF(명단표[[#This Row],[기준월 대표파견행]]="","소속",INDEX(파견표[파견근거(정규화)],명단표[[#This Row],[기준월 대표파견행]]))&amp;" 규칙"))))</f>
+        <f>IF(OR(명단표[[#This Row],[인턴계획행]]="",인턴위치_이번=""),"",INDEX(인턴계획표[[정규화1]:[정규화6]],명단표[[#This Row],[인턴계획행]],인턴위치_이번)&amp;"")</f>
         <v/>
       </c>
       <c r="AC8" s="8">
-        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(명단표[[#This Row],[기본자료행]]="","기본자료에 없는 사번",IF(COUNTIF(명단표[사번],명단표[[#This Row],[사번]])&gt;1,"중복 사번",IF(명단표[[#This Row],[소속병원]]="","소속(입사장소) 입력",IF(IF(명단표[[#This Row],[키]]="",0,COUNTIFS(파견표[키],명단표[[#This Row],[키]],파견표[입력오류],"?*"))&gt;0,"파견수련계획 입력오류 확인",IF(LEFT(명단표[[#This Row],[급여지급병원(기준월)]],1)="⚠","서울·구리 15일 판정 불가(양쪽 모두 이상/미만)",IF(IF(명단표[[#This Row],[인턴계획행]]="",0,N(INDEX(인턴계획표[입력오류],명단표[[#This Row],[인턴계획행]])))&gt;0,"인턴계획 입력오류 확인",IF(AND(명단표[[#This Row],[구리행]]&lt;&gt;"",명단표[[#This Row],[기준월 근무병원]]&lt;&gt;"구리병원",IF(명단표[[#This Row],[키]]="",0,SUMIFS(파견표[기준월 겹침일수],파견표[키],명단표[[#This Row],[키]],파견표[파견병원(정규화)],"구리병원"))=0),"구리 근무자명단에만 있음(파견수련계획 확인)",IF(AND(명단표[[#This Row],[인턴계획행]]&lt;&gt;"",명단표[[#This Row],[파견상태]]&lt;&gt;"파견중",명단표[[#This Row],[현재 근무병원]]&lt;&gt;명단표[[#This Row],[소속병원]]),"인턴 타지역 근무: 파견 여부 확인","정상")))))))))</f>
+        <f>IF(OR(명단표[[#This Row],[인턴계획행]]="",인턴위치_기준월=""),"",INDEX(인턴계획표[[정규화1]:[정규화6]],명단표[[#This Row],[인턴계획행]],인턴위치_기준월)&amp;"")</f>
         <v/>
       </c>
       <c r="AD8" s="8">
-        <f>IF(명단표[[#This Row],[다기관 기록행]]="","","다기관 "&amp;TEXT(INDEX(파견표[다기관 시작],명단표[[#This Row],[다기관 기록행]]),"yyyy-mm-dd")&amp;"~"&amp;IF(ISNUMBER(INDEX(파견표[다기관 종료],명단표[[#This Row],[다기관 기록행]])),TEXT(INDEX(파견표[다기관 종료],명단표[[#This Row],[다기관 기록행]]),"yyyy-mm-dd"),""))</f>
-        <v/>
-      </c>
-      <c r="AE8" s="6" t="inlineStr">
-        <is>
-          <t>예시(인턴)</t>
-        </is>
+        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(명단표[[#This Row],[입사장소]]&lt;&gt;"",명단표[[#This Row],[입사장소]],IF(명단표[[#This Row],[구리독자]]="구리독자","구리병원",IF(명단표[[#This Row],[근무지]]="","",_xlfn.XLOOKUP(TRIM(명단표[[#This Row],[근무지]]&amp;""),병원약칭표[표기],병원약칭표[정식 병원],명단표[[#This Row],[근무지]]&amp;"")))))</f>
+        <v/>
+      </c>
+      <c r="AE8" s="8">
+        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(AND(명단표[[#This Row],[인턴 기준월]]&lt;&gt;"",LEFT(명단표[[#This Row],[인턴 기준월]],1)&lt;&gt;"⚠"),LEFT(명단표[[#This Row],[인턴 기준월]],FIND(" ",명단표[[#This Row],[인턴 기준월]])-1),명단표[[#This Row],[소속병원]]))</f>
+        <v/>
       </c>
       <c r="AF8" s="8">
-        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IFERROR(_xlfn.XMATCH("S|"&amp;TRIM(명단표[[#This Row],[사번]]&amp;""),기본자료표[사번키]),""))</f>
-        <v/>
-      </c>
-      <c r="AG8" s="8">
-        <f>IF(TRIM(명단표[[#This Row],[전공의등록번호]]&amp;"")="","","R|"&amp;TRIM(명단표[[#This Row],[전공의등록번호]]&amp;""))</f>
+        <f>IF(명단표[[#This Row],[이름]]="","",_xlfn.LET(_xlpm.v_a,_xlfn.XMATCH(명단표[[#This Row],[이름|과]],구리_키),IF(ISNUMBER(_xlpm.v_a),_xlpm.v_a,IF(AND(COUNTIF(구리_이름,명단표[[#This Row],[이름]])=1,COUNTIF(명단표[이름],명단표[[#This Row],[이름]])=1),_xlfn.XMATCH(명단표[[#This Row],[이름]],구리_이름),""))))</f>
+        <v/>
+      </c>
+      <c r="AG8" s="11">
+        <f>IF(명단표[[#This Row],[구리행]]="","",INDEX(구리_근무일,명단표[[#This Row],[구리행]]))</f>
         <v/>
       </c>
       <c r="AH8" s="8">
-        <f>IF(명단표[[#This Row],[이름]]="","",명단표[[#This Row],[이름]]&amp;"|"&amp;명단표[[#This Row],[수련과목]])</f>
-        <v/>
-      </c>
-      <c r="AI8" s="8">
-        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IFERROR(_xlfn.XMATCH("S|"&amp;TRIM(명단표[[#This Row],[사번]]&amp;""),인턴계획표[사번키]),""))</f>
-        <v/>
-      </c>
-      <c r="AJ8" s="8">
-        <f>IF(OR(명단표[[#This Row],[인턴계획행]]="",인턴위치_이번=""),"",INDEX(인턴계획표[[정규화1]:[정규화6]],명단표[[#This Row],[인턴계획행]],인턴위치_이번)&amp;"")</f>
-        <v/>
-      </c>
-      <c r="AK8" s="8">
-        <f>IF(OR(명단표[[#This Row],[인턴계획행]]="",인턴위치_기준월=""),"",INDEX(인턴계획표[[정규화1]:[정규화6]],명단표[[#This Row],[인턴계획행]],인턴위치_기준월)&amp;"")</f>
-        <v/>
-      </c>
-      <c r="AL8" s="8">
-        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(명단표[[#This Row],[입사장소]]&lt;&gt;"",명단표[[#This Row],[입사장소]],IF(IF(명단표[[#This Row],[구리행]]="",FALSE,INDEX(구리_독자,명단표[[#This Row],[구리행]])="구리독자"),"구리병원",IF(명단표[[#This Row],[파견기록행]]&lt;&gt;"",_xlfn.LET(_xlpm.v_m,INDEX(파견표[모병원(정규화)],명단표[[#This Row],[파견기록행]]),IF(AND(_xlpm.v_m&lt;&gt;"",LEFT(_xlpm.v_m,1)&lt;&gt;"⚠"),_xlpm.v_m,IF(명단표[[#This Row],[근무지]]="","",_xlfn.XLOOKUP(TRIM(명단표[[#This Row],[근무지]]&amp;""),병원약칭표[표기],병원약칭표[정식 병원],명단표[[#This Row],[근무지]]&amp;"")))),IF(명단표[[#This Row],[근무지]]="","",_xlfn.XLOOKUP(TRIM(명단표[[#This Row],[근무지]]&amp;""),병원약칭표[표기],병원약칭표[정식 병원],명단표[[#This Row],[근무지]]&amp;""))))))</f>
-        <v/>
-      </c>
-      <c r="AM8" s="8">
-        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(AND(명단표[[#This Row],[인턴 기준월]]&lt;&gt;"",LEFT(명단표[[#This Row],[인턴 기준월]],1)&lt;&gt;"⚠"),LEFT(명단표[[#This Row],[인턴 기준월]],FIND(" ",명단표[[#This Row],[인턴 기준월]])-1),명단표[[#This Row],[소속병원]]))</f>
-        <v/>
-      </c>
-      <c r="AN8" s="8">
-        <f>IF(명단표[[#This Row],[키]]="","",IFERROR(_xlfn.XMATCH(명단표[[#This Row],[키]]&amp;"|파견중",파견표[키|상태]),IFERROR(_xlfn.XMATCH(명단표[[#This Row],[키]]&amp;"|파견예정",파견표[키|상태]),IFERROR(_xlfn.XMATCH(명단표[[#This Row],[키]]&amp;"|파견종료",파견표[키|상태]),""))))</f>
-        <v/>
-      </c>
-      <c r="AO8" s="8">
-        <f>IF(명단표[[#This Row],[키]]="","",IFERROR(_xlfn.XMATCH(명단표[[#This Row],[키]]&amp;"|월",파견표[키|월]),""))</f>
-        <v/>
-      </c>
-      <c r="AP8" s="8">
-        <f>IF(명단표[[#This Row],[키]]="","",IFERROR(_xlfn.XMATCH(명단표[[#This Row],[키]]&amp;"|다기관",파견표[키|다기관]),""))</f>
-        <v/>
-      </c>
-      <c r="AQ8" s="11">
-        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),0,IF(명단표[[#This Row],[키]]="",0,SUMIFS(파견표[다기관 겹침일수],파견표[키],명단표[[#This Row],[키]])))</f>
-        <v/>
-      </c>
-      <c r="AR8" s="8">
-        <f>IF(명단표[[#This Row],[이름]]="","",_xlfn.LET(_xlpm.v_a,_xlfn.XMATCH(명단표[[#This Row],[이름|과]],구리_키),IF(ISNUMBER(_xlpm.v_a),_xlpm.v_a,IF(AND(COUNTIF(구리_이름,명단표[[#This Row],[이름]])=1,COUNTIF(명단표[이름],명단표[[#This Row],[이름]])=1),_xlfn.XMATCH(명단표[[#This Row],[이름]],구리_이름),""))))</f>
-        <v/>
-      </c>
-      <c r="AS8" s="11">
-        <f>IF(명단표[[#This Row],[구리행]]="","",INDEX(구리_근무일,명단표[[#This Row],[구리행]]))</f>
+        <f>IF(명단표[[#This Row],[구리행]]="","",_xlfn.LET(_xlpm.v_s,IFERROR(DATEVALUE(명단표[[#This Row],[구리 근무 시작일(기준월)]]),""),_xlpm.v_e,IFERROR(DATEVALUE(명단표[[#This Row],[구리 근무 종료일(기준월)]]),""),IF(AND(ISNUMBER(_xlpm.v_s),ISNUMBER(_xlpm.v_e)),IF(AND(TODAY()&gt;=_xlpm.v_s,TODAY()&lt;=_xlpm.v_e),"Y",""),"")))</f>
         <v/>
       </c>
     </row>
@@ -7300,169 +5294,112 @@
         </is>
       </c>
       <c r="N9" s="8">
-        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(AND(명단표[[#This Row],[파견상태]]="파견중",명단표[[#This Row],[파견병원]]&lt;&gt;""),명단표[[#This Row],[파견병원]],IF(AND(명단표[[#This Row],[인턴 이번달]]&lt;&gt;"",LEFT(명단표[[#This Row],[인턴 이번달]],1)&lt;&gt;"⚠"),LEFT(명단표[[#This Row],[인턴 이번달]],FIND(" ",명단표[[#This Row],[인턴 이번달]])-1),IF(명단표[[#This Row],[근무지]]="","",_xlfn.XLOOKUP(TRIM(명단표[[#This Row],[근무지]]&amp;""),병원약칭표[표기],병원약칭표[정식 병원],명단표[[#This Row],[근무지]]&amp;"")))))</f>
+        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(AND(명단표[[#This Row],[인턴 이번달]]&lt;&gt;"",LEFT(명단표[[#This Row],[인턴 이번달]],1)&lt;&gt;"⚠"),LEFT(명단표[[#This Row],[인턴 이번달]],FIND(" ",명단표[[#This Row],[인턴 이번달]])-1),IF(명단표[[#This Row],[구리 근무 중]]="Y","구리병원",IF(명단표[[#This Row],[근무지]]="","",_xlfn.XLOOKUP(TRIM(명단표[[#This Row],[근무지]]&amp;""),병원약칭표[표기],병원약칭표[정식 병원],명단표[[#This Row],[근무지]]&amp;"")))))</f>
         <v/>
       </c>
       <c r="O9" s="8">
-        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(AND(명단표[[#This Row],[파견상태]]="파견중",명단표[[#This Row],[파견병원]]&lt;&gt;""),IF(명단표[[#This Row],[파견진료과]]&lt;&gt;"",명단표[[#This Row],[파견진료과]],"파견과 미입력"),IF(AND(명단표[[#This Row],[인턴 이번달]]&lt;&gt;"",LEFT(명단표[[#This Row],[인턴 이번달]],1)&lt;&gt;"⚠"),MID(명단표[[#This Row],[인턴 이번달]],FIND(" ",명단표[[#This Row],[인턴 이번달]])+1,60),IF(명단표[[#This Row],[수련과목]]="","",IF(명단표[[#This Row],[수련과목]]="인턴","수련교육부(인턴)",명단표[[#This Row],[수련과목]])))))</f>
+        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(AND(명단표[[#This Row],[인턴 이번달]]&lt;&gt;"",LEFT(명단표[[#This Row],[인턴 이번달]],1)&lt;&gt;"⚠"),MID(명단표[[#This Row],[인턴 이번달]],FIND(" ",명단표[[#This Row],[인턴 이번달]])+1,60),IF(명단표[[#This Row],[수련과목]]="","",IF(명단표[[#This Row],[수련과목]]="인턴","수련교육부(인턴)",명단표[[#This Row],[수련과목]]))))</f>
         <v/>
       </c>
       <c r="P9" s="8">
-        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(명단표[[#This Row],[다기관 기록행]]&lt;&gt;"",IF(AND(TODAY()&gt;=INDEX(파견표[다기관 시작],명단표[[#This Row],[다기관 기록행]]),OR(NOT(ISNUMBER(INDEX(파견표[다기관 종료],명단표[[#This Row],[다기관 기록행]]))),TODAY()&lt;=INDEX(파견표[다기관 종료],명단표[[#This Row],[다기관 기록행]]))),"다기관",IF(명단표[[#This Row],[파견기록행]]="","",INDEX(파견표[파견근거(정규화)],명단표[[#This Row],[파견기록행]]))),IF(명단표[[#This Row],[파견기록행]]="","",INDEX(파견표[파견근거(정규화)],명단표[[#This Row],[파견기록행]]))))</f>
+        <f>IF(명단표[[#This Row],[구리행]]="","",INDEX(구리_시작,명단표[[#This Row],[구리행]]))</f>
         <v/>
       </c>
       <c r="Q9" s="8">
-        <f>IF(명단표[[#This Row],[파견기록행]]="","",INDEX(파견표[파견병원(정규화)],명단표[[#This Row],[파견기록행]]))</f>
+        <f>IF(명단표[[#This Row],[구리행]]="","",INDEX(구리_종료,명단표[[#This Row],[구리행]]))</f>
         <v/>
       </c>
       <c r="R9" s="8">
-        <f>IF(명단표[[#This Row],[파견기록행]]="","",INDEX(파견표[파견과목(정규화)],명단표[[#This Row],[파견기록행]]))</f>
-        <v/>
-      </c>
-      <c r="S9" s="10">
-        <f>IF(명단표[[#This Row],[파견기록행]]="","",INDEX(파견표[시작일(계산)],명단표[[#This Row],[파견기록행]]))</f>
-        <v/>
-      </c>
-      <c r="T9" s="10">
-        <f>IF(명단표[[#This Row],[파견기록행]]="","",INDEX(파견표[종료일(계산)],명단표[[#This Row],[파견기록행]]))</f>
+        <f>IF(명단표[[#This Row],[구리행]]="","",INDEX(구리_독자,명단표[[#This Row],[구리행]]))</f>
+        <v/>
+      </c>
+      <c r="S9" s="11">
+        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(명단표[[#This Row],[구리행]]&lt;&gt;"",MAX(0,DAY(EOMONTH(급여기준월,0))-N(명단표[[#This Row],[구리명단 근무일]])),IF(명단표[[#This Row],[기준월 근무병원]]="서울병원",DAY(EOMONTH(급여기준월,0)),0)))</f>
+        <v/>
+      </c>
+      <c r="T9" s="11">
+        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(명단표[[#This Row],[구리행]]&lt;&gt;"",N(명단표[[#This Row],[구리명단 근무일]]),IF(명단표[[#This Row],[기준월 근무병원]]="구리병원",DAY(EOMONTH(급여기준월,0)),0)))</f>
         <v/>
       </c>
       <c r="U9" s="8">
-        <f>IF(명단표[[#This Row],[파견기록행]]="","",INDEX(파견표[상태],명단표[[#This Row],[파견기록행]]))</f>
-        <v/>
-      </c>
-      <c r="V9" s="11">
-        <f>IF(명단표[[#This Row],[파견기록행]]="","",INDEX(파견표[파견일수(계산)],명단표[[#This Row],[파견기록행]]))</f>
-        <v/>
-      </c>
-      <c r="W9" s="11">
-        <f>IF(AND(명단표[[#This Row],[파견상태]]="파견중",ISNUMBER(명단표[[#This Row],[파견종료일]])),명단표[[#This Row],[파견종료일]]-TODAY(),"")</f>
-        <v/>
-      </c>
-      <c r="X9" s="11">
-        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(명단표[[#This Row],[키]]="",0,SUMIFS(파견표[기준월 겹침일수],파견표[키],명단표[[#This Row],[키]])))</f>
-        <v/>
-      </c>
-      <c r="Y9" s="11">
-        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(명단표[[#This Row],[구리행]]&lt;&gt;"",MAX(0,DAY(EOMONTH(급여기준월,0))-N(명단표[[#This Row],[구리명단 근무일]])),IF(명단표[[#This Row],[키]]="",0,SUMIFS(파견표[기준월 겹침일수],파견표[키],명단표[[#This Row],[키]],파견표[파견병원(정규화)],"서울병원"))+IF(명단표[[#This Row],[기준월 근무병원]]="서울병원",MAX(0,DAY(EOMONTH(급여기준월,0))-N(명단표[[#This Row],[급여기준월 파견일수]])),0)))</f>
-        <v/>
-      </c>
-      <c r="Z9" s="11">
-        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(명단표[[#This Row],[구리행]]&lt;&gt;"",N(명단표[[#This Row],[구리명단 근무일]]),IF(명단표[[#This Row],[키]]="",0,SUMIFS(파견표[기준월 겹침일수],파견표[키],명단표[[#This Row],[키]],파견표[파견병원(정규화)],"구리병원"))+IF(명단표[[#This Row],[기준월 근무병원]]="구리병원",MAX(0,DAY(EOMONTH(급여기준월,0))-N(명단표[[#This Row],[급여기준월 파견일수]])),0)))</f>
+        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(명단표[[#This Row],[기준월 근무병원]]="","",IF(명단표[[#This Row],[구리행]]="",명단표[[#This Row],[기준월 근무병원]],IF(AND(명단표[[#This Row],[서울 근무일(기준월)]]&gt;=판정기준일,명단표[[#This Row],[구리 근무일(기준월)]]&lt;판정기준일),"서울병원",IF(AND(명단표[[#This Row],[구리 근무일(기준월)]]&gt;=판정기준일,명단표[[#This Row],[서울 근무일(기준월)]]&lt;판정기준일),"구리병원","⚠15일 판정불가(서울 "&amp;명단표[[#This Row],[서울 근무일(기준월)]]&amp;"일/구리 "&amp;명단표[[#This Row],[구리 근무일(기준월)]]&amp;"일)")))))</f>
+        <v/>
+      </c>
+      <c r="V9" s="8">
+        <f>IF(OR(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),명단표[[#This Row],[급여지급병원(기준월)]]=""),"",IF(명단표[[#This Row],[구리행]]&lt;&gt;"","서울 "&amp;명단표[[#This Row],[서울 근무일(기준월)]]&amp;"일 / 구리 "&amp;명단표[[#This Row],[구리 근무일(기준월)]]&amp;"일 (구리 근무자명단) → 15일 이상 근무 병원 지급",IF(AND(명단표[[#This Row],[인턴 기준월]]&lt;&gt;"",LEFT(명단표[[#This Row],[인턴 기준월]],1)&lt;&gt;"⚠"),"인턴 근무계획 → 그 달 근무병원 지급","구리 근무자명단에 없음 → 소속병원 지급")))</f>
+        <v/>
+      </c>
+      <c r="W9" s="8">
+        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(명단표[[#This Row],[기본자료행]]="","기본자료에 없는 사번",IF(COUNTIF(명단표[사번],명단표[[#This Row],[사번]])&gt;1,"중복 사번",IF(명단표[[#This Row],[소속병원]]="","소속(입사장소) 입력",IF(LEFT(명단표[[#This Row],[급여지급병원(기준월)]],1)="⚠","서울·구리 15일 판정 불가(양쪽 모두 이상/미만)",IF(IF(명단표[[#This Row],[인턴계획행]]="",0,N(INDEX(인턴계획표[입력오류],명단표[[#This Row],[인턴계획행]])))&gt;0,"인턴계획 입력오류 확인",IF(AND(명단표[[#This Row],[구리행]]="",COUNTIF(구리_이름,명단표[[#This Row],[이름]])&gt;0),"구리 근무자명단 연결 확인(동명이인·과 불일치)","정상")))))))</f>
+        <v/>
+      </c>
+      <c r="X9" s="6" t="inlineStr">
+        <is>
+          <t>예시(인턴)</t>
+        </is>
+      </c>
+      <c r="Y9" s="8">
+        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IFERROR(_xlfn.XMATCH("S|"&amp;TRIM(명단표[[#This Row],[사번]]&amp;""),기본자료표[사번키]),""))</f>
+        <v/>
+      </c>
+      <c r="Z9" s="8">
+        <f>IF(명단표[[#This Row],[이름]]="","",명단표[[#This Row],[이름]]&amp;"|"&amp;명단표[[#This Row],[수련과목]])</f>
         <v/>
       </c>
       <c r="AA9" s="8">
-        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(명단표[[#This Row],[기준월 근무병원]]="","",IF(명단표[[#This Row],[다기관 겹침일수]]&gt;0,명단표[[#This Row],[소속병원]],IF(AND(N(명단표[[#This Row],[급여기준월 파견일수]])&lt;=0,명단표[[#This Row],[구리행]]=""),명단표[[#This Row],[기준월 근무병원]],IF(명단표[[#This Row],[서울 근무일(기준월)]]+명단표[[#This Row],[구리 근무일(기준월)]]=DAY(EOMONTH(급여기준월,0)),IF(AND(명단표[[#This Row],[서울 근무일(기준월)]]&gt;=판정기준일,명단표[[#This Row],[구리 근무일(기준월)]]&lt;판정기준일),"서울병원",IF(AND(명단표[[#This Row],[구리 근무일(기준월)]]&gt;=판정기준일,명단표[[#This Row],[서울 근무일(기준월)]]&lt;판정기준일),"구리병원","⚠15일 판정불가(서울 "&amp;명단표[[#This Row],[서울 근무일(기준월)]]&amp;"일/구리 "&amp;명단표[[#This Row],[구리 근무일(기준월)]]&amp;"일)")),IF(명단표[[#This Row],[기준월 대표파견행]]="",명단표[[#This Row],[소속병원]],IF(INDEX(파견표[파견근거(정규화)],명단표[[#This Row],[기준월 대표파견행]])="통합수련",INDEX(파견표[파견병원(정규화)],명단표[[#This Row],[기준월 대표파견행]]),명단표[[#This Row],[소속병원]])))))))</f>
+        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IFERROR(_xlfn.XMATCH("S|"&amp;TRIM(명단표[[#This Row],[사번]]&amp;""),인턴계획표[사번키]),""))</f>
         <v/>
       </c>
       <c r="AB9" s="8">
-        <f>IF(OR(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),명단표[[#This Row],[급여지급병원(기준월)]]=""),"",IF(명단표[[#This Row],[다기관 겹침일수]]&gt;0,"다기관 기간 → 소속병원 지급",IF(AND(N(명단표[[#This Row],[급여기준월 파견일수]])&lt;=0,명단표[[#This Row],[구리행]]=""),"파견 없음 → 그 달 근무병원 지급",IF(명단표[[#This Row],[서울 근무일(기준월)]]+명단표[[#This Row],[구리 근무일(기준월)]]=DAY(EOMONTH(급여기준월,0)),"서울 "&amp;명단표[[#This Row],[서울 근무일(기준월)]]&amp;"일 / 구리 "&amp;명단표[[#This Row],[구리 근무일(기준월)]]&amp;"일"&amp;IF(명단표[[#This Row],[구리행]]&lt;&gt;""," (구리 근무자명단 반영)","")&amp;" → 15일 이상 근무 병원 지급","타 병원 포함 → "&amp;IF(명단표[[#This Row],[기준월 대표파견행]]="","소속",INDEX(파견표[파견근거(정규화)],명단표[[#This Row],[기준월 대표파견행]]))&amp;" 규칙"))))</f>
+        <f>IF(OR(명단표[[#This Row],[인턴계획행]]="",인턴위치_이번=""),"",INDEX(인턴계획표[[정규화1]:[정규화6]],명단표[[#This Row],[인턴계획행]],인턴위치_이번)&amp;"")</f>
         <v/>
       </c>
       <c r="AC9" s="8">
-        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(명단표[[#This Row],[기본자료행]]="","기본자료에 없는 사번",IF(COUNTIF(명단표[사번],명단표[[#This Row],[사번]])&gt;1,"중복 사번",IF(명단표[[#This Row],[소속병원]]="","소속(입사장소) 입력",IF(IF(명단표[[#This Row],[키]]="",0,COUNTIFS(파견표[키],명단표[[#This Row],[키]],파견표[입력오류],"?*"))&gt;0,"파견수련계획 입력오류 확인",IF(LEFT(명단표[[#This Row],[급여지급병원(기준월)]],1)="⚠","서울·구리 15일 판정 불가(양쪽 모두 이상/미만)",IF(IF(명단표[[#This Row],[인턴계획행]]="",0,N(INDEX(인턴계획표[입력오류],명단표[[#This Row],[인턴계획행]])))&gt;0,"인턴계획 입력오류 확인",IF(AND(명단표[[#This Row],[구리행]]&lt;&gt;"",명단표[[#This Row],[기준월 근무병원]]&lt;&gt;"구리병원",IF(명단표[[#This Row],[키]]="",0,SUMIFS(파견표[기준월 겹침일수],파견표[키],명단표[[#This Row],[키]],파견표[파견병원(정규화)],"구리병원"))=0),"구리 근무자명단에만 있음(파견수련계획 확인)",IF(AND(명단표[[#This Row],[인턴계획행]]&lt;&gt;"",명단표[[#This Row],[파견상태]]&lt;&gt;"파견중",명단표[[#This Row],[현재 근무병원]]&lt;&gt;명단표[[#This Row],[소속병원]]),"인턴 타지역 근무: 파견 여부 확인","정상")))))))))</f>
+        <f>IF(OR(명단표[[#This Row],[인턴계획행]]="",인턴위치_기준월=""),"",INDEX(인턴계획표[[정규화1]:[정규화6]],명단표[[#This Row],[인턴계획행]],인턴위치_기준월)&amp;"")</f>
         <v/>
       </c>
       <c r="AD9" s="8">
-        <f>IF(명단표[[#This Row],[다기관 기록행]]="","","다기관 "&amp;TEXT(INDEX(파견표[다기관 시작],명단표[[#This Row],[다기관 기록행]]),"yyyy-mm-dd")&amp;"~"&amp;IF(ISNUMBER(INDEX(파견표[다기관 종료],명단표[[#This Row],[다기관 기록행]])),TEXT(INDEX(파견표[다기관 종료],명단표[[#This Row],[다기관 기록행]]),"yyyy-mm-dd"),""))</f>
-        <v/>
-      </c>
-      <c r="AE9" s="6" t="inlineStr">
-        <is>
-          <t>예시(인턴)</t>
-        </is>
+        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(명단표[[#This Row],[입사장소]]&lt;&gt;"",명단표[[#This Row],[입사장소]],IF(명단표[[#This Row],[구리독자]]="구리독자","구리병원",IF(명단표[[#This Row],[근무지]]="","",_xlfn.XLOOKUP(TRIM(명단표[[#This Row],[근무지]]&amp;""),병원약칭표[표기],병원약칭표[정식 병원],명단표[[#This Row],[근무지]]&amp;"")))))</f>
+        <v/>
+      </c>
+      <c r="AE9" s="8">
+        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(AND(명단표[[#This Row],[인턴 기준월]]&lt;&gt;"",LEFT(명단표[[#This Row],[인턴 기준월]],1)&lt;&gt;"⚠"),LEFT(명단표[[#This Row],[인턴 기준월]],FIND(" ",명단표[[#This Row],[인턴 기준월]])-1),명단표[[#This Row],[소속병원]]))</f>
+        <v/>
       </c>
       <c r="AF9" s="8">
-        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IFERROR(_xlfn.XMATCH("S|"&amp;TRIM(명단표[[#This Row],[사번]]&amp;""),기본자료표[사번키]),""))</f>
-        <v/>
-      </c>
-      <c r="AG9" s="8">
-        <f>IF(TRIM(명단표[[#This Row],[전공의등록번호]]&amp;"")="","","R|"&amp;TRIM(명단표[[#This Row],[전공의등록번호]]&amp;""))</f>
+        <f>IF(명단표[[#This Row],[이름]]="","",_xlfn.LET(_xlpm.v_a,_xlfn.XMATCH(명단표[[#This Row],[이름|과]],구리_키),IF(ISNUMBER(_xlpm.v_a),_xlpm.v_a,IF(AND(COUNTIF(구리_이름,명단표[[#This Row],[이름]])=1,COUNTIF(명단표[이름],명단표[[#This Row],[이름]])=1),_xlfn.XMATCH(명단표[[#This Row],[이름]],구리_이름),""))))</f>
+        <v/>
+      </c>
+      <c r="AG9" s="11">
+        <f>IF(명단표[[#This Row],[구리행]]="","",INDEX(구리_근무일,명단표[[#This Row],[구리행]]))</f>
         <v/>
       </c>
       <c r="AH9" s="8">
-        <f>IF(명단표[[#This Row],[이름]]="","",명단표[[#This Row],[이름]]&amp;"|"&amp;명단표[[#This Row],[수련과목]])</f>
-        <v/>
-      </c>
-      <c r="AI9" s="8">
-        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IFERROR(_xlfn.XMATCH("S|"&amp;TRIM(명단표[[#This Row],[사번]]&amp;""),인턴계획표[사번키]),""))</f>
-        <v/>
-      </c>
-      <c r="AJ9" s="8">
-        <f>IF(OR(명단표[[#This Row],[인턴계획행]]="",인턴위치_이번=""),"",INDEX(인턴계획표[[정규화1]:[정규화6]],명단표[[#This Row],[인턴계획행]],인턴위치_이번)&amp;"")</f>
-        <v/>
-      </c>
-      <c r="AK9" s="8">
-        <f>IF(OR(명단표[[#This Row],[인턴계획행]]="",인턴위치_기준월=""),"",INDEX(인턴계획표[[정규화1]:[정규화6]],명단표[[#This Row],[인턴계획행]],인턴위치_기준월)&amp;"")</f>
-        <v/>
-      </c>
-      <c r="AL9" s="8">
-        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(명단표[[#This Row],[입사장소]]&lt;&gt;"",명단표[[#This Row],[입사장소]],IF(IF(명단표[[#This Row],[구리행]]="",FALSE,INDEX(구리_독자,명단표[[#This Row],[구리행]])="구리독자"),"구리병원",IF(명단표[[#This Row],[파견기록행]]&lt;&gt;"",_xlfn.LET(_xlpm.v_m,INDEX(파견표[모병원(정규화)],명단표[[#This Row],[파견기록행]]),IF(AND(_xlpm.v_m&lt;&gt;"",LEFT(_xlpm.v_m,1)&lt;&gt;"⚠"),_xlpm.v_m,IF(명단표[[#This Row],[근무지]]="","",_xlfn.XLOOKUP(TRIM(명단표[[#This Row],[근무지]]&amp;""),병원약칭표[표기],병원약칭표[정식 병원],명단표[[#This Row],[근무지]]&amp;"")))),IF(명단표[[#This Row],[근무지]]="","",_xlfn.XLOOKUP(TRIM(명단표[[#This Row],[근무지]]&amp;""),병원약칭표[표기],병원약칭표[정식 병원],명단표[[#This Row],[근무지]]&amp;""))))))</f>
-        <v/>
-      </c>
-      <c r="AM9" s="8">
-        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),"",IF(AND(명단표[[#This Row],[인턴 기준월]]&lt;&gt;"",LEFT(명단표[[#This Row],[인턴 기준월]],1)&lt;&gt;"⚠"),LEFT(명단표[[#This Row],[인턴 기준월]],FIND(" ",명단표[[#This Row],[인턴 기준월]])-1),명단표[[#This Row],[소속병원]]))</f>
-        <v/>
-      </c>
-      <c r="AN9" s="8">
-        <f>IF(명단표[[#This Row],[키]]="","",IFERROR(_xlfn.XMATCH(명단표[[#This Row],[키]]&amp;"|파견중",파견표[키|상태]),IFERROR(_xlfn.XMATCH(명단표[[#This Row],[키]]&amp;"|파견예정",파견표[키|상태]),IFERROR(_xlfn.XMATCH(명단표[[#This Row],[키]]&amp;"|파견종료",파견표[키|상태]),""))))</f>
-        <v/>
-      </c>
-      <c r="AO9" s="8">
-        <f>IF(명단표[[#This Row],[키]]="","",IFERROR(_xlfn.XMATCH(명단표[[#This Row],[키]]&amp;"|월",파견표[키|월]),""))</f>
-        <v/>
-      </c>
-      <c r="AP9" s="8">
-        <f>IF(명단표[[#This Row],[키]]="","",IFERROR(_xlfn.XMATCH(명단표[[#This Row],[키]]&amp;"|다기관",파견표[키|다기관]),""))</f>
-        <v/>
-      </c>
-      <c r="AQ9" s="11">
-        <f>IF(NOT(TRIM(명단표[[#This Row],[사번]]&amp;"")&lt;&gt;""),0,IF(명단표[[#This Row],[키]]="",0,SUMIFS(파견표[다기관 겹침일수],파견표[키],명단표[[#This Row],[키]])))</f>
-        <v/>
-      </c>
-      <c r="AR9" s="8">
-        <f>IF(명단표[[#This Row],[이름]]="","",_xlfn.LET(_xlpm.v_a,_xlfn.XMATCH(명단표[[#This Row],[이름|과]],구리_키),IF(ISNUMBER(_xlpm.v_a),_xlpm.v_a,IF(AND(COUNTIF(구리_이름,명단표[[#This Row],[이름]])=1,COUNTIF(명단표[이름],명단표[[#This Row],[이름]])=1),_xlfn.XMATCH(명단표[[#This Row],[이름]],구리_이름),""))))</f>
-        <v/>
-      </c>
-      <c r="AS9" s="11">
-        <f>IF(명단표[[#This Row],[구리행]]="","",INDEX(구리_근무일,명단표[[#This Row],[구리행]]))</f>
+        <f>IF(명단표[[#This Row],[구리행]]="","",_xlfn.LET(_xlpm.v_s,IFERROR(DATEVALUE(명단표[[#This Row],[구리 근무 시작일(기준월)]]),""),_xlpm.v_e,IFERROR(DATEVALUE(명단표[[#This Row],[구리 근무 종료일(기준월)]]),""),IF(AND(ISNUMBER(_xlpm.v_s),ISNUMBER(_xlpm.v_e)),IF(AND(TODAY()&gt;=_xlpm.v_s,TODAY()&lt;=_xlpm.v_e),"Y",""),"")))</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:B1048576">
     <cfRule type="expression" priority="1" dxfId="2">
-      <formula>AND($B2&lt;&gt;"",$AF2="")</formula>
+      <formula>AND($B2&lt;&gt;"",$Y2="")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AC2:AC1048576">
+  <conditionalFormatting sqref="W2:W1048576">
     <cfRule type="expression" priority="2" dxfId="3">
-      <formula>AND($AC2&lt;&gt;"",$AC2&lt;&gt;"정상")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA2:AA1048576">
-    <cfRule type="expression" priority="3" dxfId="2">
-      <formula>LEFT($AA2,1)="⚠"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="4" dxfId="4">
-      <formula>AND($AA2&lt;&gt;"",$AL2&lt;&gt;"",$AA2&lt;&gt;$AL2)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A2:T1048576">
-    <cfRule type="expression" priority="5" dxfId="5">
-      <formula>AND($U2="파견중",$W2&lt;&gt;"",$W2&lt;=임박기준일)</formula>
+      <formula>AND($W2&lt;&gt;"",$W2&lt;&gt;"정상")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U2:U1048576">
-    <cfRule type="expression" priority="6" dxfId="6">
-      <formula>$U2="파견중"</formula>
+    <cfRule type="expression" priority="3" dxfId="2">
+      <formula>LEFT($U2,1)="⚠"</formula>
     </cfRule>
-    <cfRule type="expression" priority="7" dxfId="7">
-      <formula>$U2="파견예정"</formula>
+    <cfRule type="expression" priority="4" dxfId="4">
+      <formula>AND($U2&lt;&gt;"",$AD2&lt;&gt;"",$U2&lt;&gt;$AD2)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E1048576">
-    <cfRule type="expression" priority="8" dxfId="8">
+    <cfRule type="expression" priority="5" dxfId="5">
       <formula>ISTEXT($E2)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7478,14 +5415,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00548235"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W6"/>
+  <dimension ref="A1:U6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -7497,20 +5434,18 @@
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
     <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="9" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="11" customWidth="1" min="13" max="13"/>
-    <col width="8" customWidth="1" min="14" max="14"/>
-    <col width="8" customWidth="1" min="15" max="15"/>
-    <col width="40" customWidth="1" min="16" max="16"/>
-    <col width="26" customWidth="1" min="17" max="17"/>
-    <col width="3" customWidth="1" min="18" max="18"/>
-    <col width="9" customWidth="1" min="19" max="19"/>
-    <col width="10" customWidth="1" min="20" max="20"/>
-    <col width="10" customWidth="1" min="21" max="21"/>
-    <col width="8" customWidth="1" min="22" max="22"/>
-    <col width="8" customWidth="1" min="23" max="23"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="40" customWidth="1" min="14" max="14"/>
+    <col width="26" customWidth="1" min="15" max="15"/>
+    <col width="3" customWidth="1" min="16" max="16"/>
+    <col width="9" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
+    <col width="8" customWidth="1" min="20" max="20"/>
+    <col width="8" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7526,47 +5461,47 @@
           <t>급여 기준월</t>
         </is>
       </c>
-      <c r="B2" s="15">
+      <c r="B2" s="13">
         <f>급여기준월</f>
         <v/>
       </c>
-      <c r="D2" s="16" t="inlineStr">
+      <c r="D2" s="14" t="inlineStr">
         <is>
           <t>서울 지급 인원</t>
         </is>
       </c>
-      <c r="E2" s="17">
+      <c r="E2" s="15">
         <f>COUNTIF(명단표[급여지급병원(기준월)],"서울병원")</f>
         <v/>
       </c>
-      <c r="F2" s="16" t="inlineStr">
+      <c r="F2" s="14" t="inlineStr">
         <is>
           <t>그중 타 병원 소속</t>
         </is>
       </c>
-      <c r="G2" s="17">
+      <c r="G2" s="15">
         <f>COUNTIFS(명단표[급여지급병원(기준월)],"서울병원",명단표[소속병원],"&lt;&gt;서울병원")</f>
         <v/>
       </c>
-      <c r="H2" s="16" t="inlineStr">
+      <c r="H2" s="14" t="inlineStr">
         <is>
           <t>⚠ 판정 불가</t>
         </is>
       </c>
-      <c r="I2" s="17">
+      <c r="I2" s="15">
         <f>COUNTIF(명단표[급여지급병원(기준월)],"⚠*")</f>
         <v/>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>※ 자동으로 펼쳐지는 목록입니다(입력 금지). 노란 행 = 소속은 다른 병원인데 이번 달 서울병원이 지급. 급여 기준월은 설정_코드표에서 바꿉니다.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="S4" s="18" t="inlineStr">
+      <c r="Q4" s="17" t="inlineStr">
         <is>
           <t>⚠ 서울·구리 15일 판정 불가 (양쪽 모두 15일 이상/미만) — 담당자 확인 필요</t>
         </is>
@@ -7620,65 +5555,55 @@
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>파견근거</t>
+          <t>구리 근무 시작일</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>파견병원</t>
+          <t>구리 근무 종료일</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t>파견시작일</t>
+          <t>서울 근무일</t>
         </is>
       </c>
       <c r="M5" s="4" t="inlineStr">
         <is>
-          <t>파견종료일</t>
+          <t>구리 근무일</t>
         </is>
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
+          <t>판정 근거</t>
+        </is>
+      </c>
+      <c r="O5" s="4" t="inlineStr">
+        <is>
+          <t>점검</t>
+        </is>
+      </c>
+      <c r="Q5" s="18" t="inlineStr">
+        <is>
+          <t>이름</t>
+        </is>
+      </c>
+      <c r="R5" s="18" t="inlineStr">
+        <is>
+          <t>사번</t>
+        </is>
+      </c>
+      <c r="S5" s="18" t="inlineStr">
+        <is>
+          <t>소속병원</t>
+        </is>
+      </c>
+      <c r="T5" s="18" t="inlineStr">
+        <is>
           <t>서울 근무일</t>
         </is>
       </c>
-      <c r="O5" s="4" t="inlineStr">
-        <is>
-          <t>구리 근무일</t>
-        </is>
-      </c>
-      <c r="P5" s="4" t="inlineStr">
-        <is>
-          <t>판정 근거</t>
-        </is>
-      </c>
-      <c r="Q5" s="4" t="inlineStr">
-        <is>
-          <t>점검</t>
-        </is>
-      </c>
-      <c r="S5" s="19" t="inlineStr">
-        <is>
-          <t>이름</t>
-        </is>
-      </c>
-      <c r="T5" s="19" t="inlineStr">
-        <is>
-          <t>사번</t>
-        </is>
-      </c>
-      <c r="U5" s="19" t="inlineStr">
-        <is>
-          <t>소속병원</t>
-        </is>
-      </c>
-      <c r="V5" s="19" t="inlineStr">
-        <is>
-          <t>서울 근무일</t>
-        </is>
-      </c>
-      <c r="W5" s="19" t="inlineStr">
+      <c r="U5" s="18" t="inlineStr">
         <is>
           <t>구리 근무일</t>
         </is>
@@ -7690,11 +5615,11 @@
         <v/>
       </c>
       <c r="B6" cm="1">
-        <f t="array" ref="B6">IF(COUNTIF(명단표[급여지급병원(기준월)],"서울병원")=0,"대상 없음",_xlfn._xlws.FILTER(CHOOSE({1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16},명단표[이름],명단표[사번]&amp;"",명단표[전공의등록번호]&amp;"",명단표[수련과목]&amp;"",명단표[연차]&amp;"",명단표[소속병원],IF(명단표[소속병원]="서울병원","서울 소속","타 병원 소속("&amp;명단표[소속병원]&amp;") → 서울 지급"),명단표[현재 근무병원],명단표[파견근거],명단표[파견병원],IF(ISNUMBER(명단표[파견시작일]),TEXT(명단표[파견시작일],"yyyy-mm-dd"),""),IF(ISNUMBER(명단표[파견종료일]),TEXT(명단표[파견종료일],"yyyy-mm-dd"),""),명단표[서울 근무일(기준월)],명단표[구리 근무일(기준월)],명단표[급여 판정 근거],명단표[점검]),명단표[급여지급병원(기준월)]="서울병원"))</f>
-        <v/>
-      </c>
-      <c r="S6" cm="1">
-        <f t="array" ref="S6">IF(COUNTIF(명단표[급여지급병원(기준월)],"⚠*")=0,"없음",_xlfn._xlws.FILTER(CHOOSE({1,2,3,4,5},명단표[이름],명단표[사번]&amp;"",명단표[소속병원],명단표[서울 근무일(기준월)],명단표[구리 근무일(기준월)]),LEFT(명단표[급여지급병원(기준월)],1)="⚠"))</f>
+        <f t="array" ref="B6">IF(COUNTIF(명단표[급여지급병원(기준월)],"서울병원")=0,"대상 없음",_xlfn._xlws.FILTER(CHOOSE({1,2,3,4,5,6,7,8,9,10,11,12,13,14},명단표[이름],명단표[사번]&amp;"",명단표[전공의등록번호]&amp;"",명단표[수련과목]&amp;"",명단표[연차]&amp;"",명단표[소속병원],IF(명단표[소속병원]="서울병원","서울 소속","타 병원 소속("&amp;명단표[소속병원]&amp;") → 서울 지급"),명단표[현재 근무병원],명단표[구리 근무 시작일(기준월)]&amp;"",명단표[구리 근무 종료일(기준월)]&amp;"",명단표[서울 근무일(기준월)],명단표[구리 근무일(기준월)],명단표[급여 판정 근거],명단표[점검]),명단표[급여지급병원(기준월)]="서울병원"))</f>
+        <v/>
+      </c>
+      <c r="Q6" cm="1">
+        <f t="array" ref="Q6">IF(COUNTIF(명단표[급여지급병원(기준월)],"⚠*")=0,"없음",_xlfn._xlws.FILTER(CHOOSE({1,2,3,4,5},명단표[이름],명단표[사번]&amp;"",명단표[소속병원],명단표[서울 근무일(기준월)],명단표[구리 근무일(기준월)]),LEFT(명단표[급여지급병원(기준월)],1)="⚠"))</f>
         <v/>
       </c>
     </row>
@@ -7704,21 +5629,21 @@
       <formula>I2&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A6:Q20005">
-    <cfRule type="expression" priority="2" dxfId="9">
+  <conditionalFormatting sqref="A6:O20005">
+    <cfRule type="expression" priority="2" dxfId="6">
       <formula>LEFT($H6,2)="타 "</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q6:Q20005">
+  <conditionalFormatting sqref="O6:O20005">
     <cfRule type="expression" priority="3" dxfId="0">
-      <formula>AND($Q6&lt;&gt;"",$Q6&lt;&gt;"정상")</formula>
+      <formula>AND($O6&lt;&gt;"",$O6&lt;&gt;"정상")</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00548235"/>
@@ -7748,12 +5673,12 @@
           <t>구리병원 근무자 (구리 근무자명단 기준)</t>
         </is>
       </c>
-      <c r="I1" s="20" t="inlineStr">
+      <c r="I1" s="19" t="inlineStr">
         <is>
           <t>명단 연결</t>
         </is>
       </c>
-      <c r="J1" s="21">
+      <c r="J1" s="20">
         <f>COUNTIF($L$6:$L$20005,"명단 일치*")</f>
         <v/>
       </c>
@@ -7764,50 +5689,50 @@
           <t>급여 기준월</t>
         </is>
       </c>
-      <c r="B2" s="15">
+      <c r="B2" s="13">
         <f>급여기준월</f>
         <v/>
       </c>
-      <c r="D2" s="12" t="inlineStr">
+      <c r="D2" s="16" t="inlineStr">
         <is>
           <t>블록 시작 열</t>
         </is>
       </c>
-      <c r="E2" cm="1" s="22">
+      <c r="E2" cm="1" s="21">
         <f t="array" ref="E2">_xlfn.LET(_xlpm.v_h,'입력_구리근무자명단'!$A$3:$ZZ$3&amp;"",_xlpm.v_p1,IFERROR(FIND("월",_xlpm.v_h),999),_xlpm.v_p2,IFERROR(FIND(CHAR(10),_xlpm.v_h),999),_xlpm.v_e,IF(_xlpm.v_p1&lt;_xlpm.v_p2,_xlpm.v_p1,_xlpm.v_p2),_xlpm.v_y,IFERROR(VALUE(LEFT(_xlpm.v_h,4)),0),_xlpm.v_m,IFERROR(VALUE(MID(_xlpm.v_h,6,_xlpm.v_e-6)),0),_xlpm.v_k,IF(ISNUMBER(SEARCH("근무예정자",_xlpm.v_h)),_xlpm.v_y*100+_xlpm.v_m,0),IFERROR(_xlfn.XMATCH(YEAR(급여기준월)*100+MONTH(급여기준월),_xlpm.v_k),""))</f>
         <v/>
       </c>
-      <c r="F2" s="12" t="inlineStr">
+      <c r="F2" s="16" t="inlineStr">
         <is>
           <t>근무자 확정</t>
         </is>
       </c>
-      <c r="G2" s="22">
+      <c r="G2" s="21">
         <f>IF($E$2="","",IF(COUNTIF(INDEX('입력_구리근무자명단'!$A$4:$ZZ$20000,0,$E$2+1),"?*")&gt;0,"확정","예정"))</f>
         <v/>
       </c>
-      <c r="I2" s="20" t="inlineStr">
+      <c r="I2" s="19" t="inlineStr">
         <is>
           <t>명단에 없음/동명이인</t>
         </is>
       </c>
-      <c r="J2" s="21">
+      <c r="J2" s="20">
         <f>COUNTIF($L$6:$L$20005,"명단에 없음*")+COUNTIF($L$6:$L$20005,"동명이인*")</f>
         <v/>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>※ 자동 결과(입력 금지). 그 달 '근무자' 칸이 하나라도 채워져 있으면 근무자, 아니면 근무예정자 기준. 날짜가 없으면 1일~말일. 명단 연결: 이름+진료과(인턴은 이름+인턴), 안 되면 이름만. '블록 시작 열'이 비면 3행 머리글(연·월)을 확인하세요.</t>
         </is>
       </c>
-      <c r="I3" s="20" t="inlineStr">
+      <c r="I3" s="19" t="inlineStr">
         <is>
           <t>날짜 오류</t>
         </is>
       </c>
-      <c r="J3" s="21">
+      <c r="J3" s="20">
         <f>COUNTIF($F$6:$G$20005,"⚠*")</f>
         <v/>
       </c>
@@ -7898,8 +5823,353 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A6:K20005">
-    <cfRule type="expression" priority="4" dxfId="10">
+    <cfRule type="expression" priority="4" dxfId="7">
       <formula>$J6="구리독자"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00548235"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="3" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="3" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="3" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>현황 요약</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>기준일</t>
+        </is>
+      </c>
+      <c r="B2" s="22">
+        <f>TODAY()</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>급여 기준월</t>
+        </is>
+      </c>
+      <c r="B3" s="22">
+        <f>급여기준월</f>
+        <v/>
+      </c>
+      <c r="C3" s="16" t="inlineStr">
+        <is>
+          <t>← 설정값은 설정_코드표에서 변경</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>15일 기준(일)</t>
+        </is>
+      </c>
+      <c r="B4" s="23">
+        <f>판정기준일</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5"/>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>인원 (급여 기준월)</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>인원</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>병원</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>현재 근무</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>급여 지급(기준월)</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>현재 진료과</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>인원</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>인턴 구분</t>
+        </is>
+      </c>
+      <c r="L6" s="4" t="inlineStr">
+        <is>
+          <t>인원</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="24" t="inlineStr">
+        <is>
+          <t>명단 등록 인원</t>
+        </is>
+      </c>
+      <c r="B7" s="25">
+        <f>SUMPRODUCT(--(TRIM(명단표[사번]&amp;"")&lt;&gt;""))</f>
+        <v/>
+      </c>
+      <c r="D7" cm="1">
+        <f t="array" ref="D7">병원표[병원]</f>
+        <v/>
+      </c>
+      <c r="E7" cm="1">
+        <f t="array" ref="E7">COUNTIF(명단표[현재 근무병원],병원표[병원])</f>
+        <v/>
+      </c>
+      <c r="F7" cm="1">
+        <f t="array" ref="F7">COUNTIF(명단표[급여지급병원(기준월)],병원표[병원])</f>
+        <v/>
+      </c>
+      <c r="H7" cm="1">
+        <f t="array" ref="H7">진료과표[근무과]</f>
+        <v/>
+      </c>
+      <c r="I7" cm="1">
+        <f t="array" ref="I7">COUNTIF(명단표[현재 진료과],진료과표[근무과])</f>
+        <v/>
+      </c>
+      <c r="K7" cm="1">
+        <f t="array" ref="K7">인턴구분표[인턴 구분]</f>
+        <v/>
+      </c>
+      <c r="L7" cm="1">
+        <f t="array" ref="L7">COUNTIF(명단표[현재 진료과],인턴구분표[인턴 구분])</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="24" t="inlineStr">
+        <is>
+          <t>서울병원 지급</t>
+        </is>
+      </c>
+      <c r="B8" s="25">
+        <f>COUNTIF(명단표[급여지급병원(기준월)],"서울병원")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="24" t="inlineStr">
+        <is>
+          <t>구리병원 지급</t>
+        </is>
+      </c>
+      <c r="B9" s="25">
+        <f>COUNTIF(명단표[급여지급병원(기준월)],"구리병원")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="24" t="inlineStr">
+        <is>
+          <t>그 외 병원 지급</t>
+        </is>
+      </c>
+      <c r="B10" s="25">
+        <f>SUMPRODUCT((명단표[급여지급병원(기준월)]&lt;&gt;"")*(명단표[급여지급병원(기준월)]&lt;&gt;"서울병원")*(명단표[급여지급병원(기준월)]&lt;&gt;"구리병원")*(LEFT(명단표[급여지급병원(기준월)],1)&lt;&gt;"⚠"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="24" t="inlineStr">
+        <is>
+          <t>⚠ 판정 불가</t>
+        </is>
+      </c>
+      <c r="B11" s="25">
+        <f>COUNTIF(명단표[급여지급병원(기준월)],"⚠*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="24" t="inlineStr">
+        <is>
+          <t>구리 근무자명단 연결 인원</t>
+        </is>
+      </c>
+      <c r="B12" s="25">
+        <f>COUNT(명단표[구리행])</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>데이터 점검</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>건수</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="24" t="inlineStr">
+        <is>
+          <t>기본자료 인원</t>
+        </is>
+      </c>
+      <c r="B16" s="25">
+        <f>SUMPRODUCT(--(TRIM(기본자료표[사번]&amp;"")&lt;&gt;""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="24" t="inlineStr">
+        <is>
+          <t>기본자료 재직 인원</t>
+        </is>
+      </c>
+      <c r="B17" s="25">
+        <f>COUNTIF(기본자료표[현재근무 여부],"재직")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="24" t="inlineStr">
+        <is>
+          <t>기본자료에 없는 사번</t>
+        </is>
+      </c>
+      <c r="B18" s="25">
+        <f>SUMPRODUCT((TRIM(명단표[사번]&amp;"")&lt;&gt;"")*(명단표[기본자료행]=""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="24" t="inlineStr">
+        <is>
+          <t>명단 중복 사번</t>
+        </is>
+      </c>
+      <c r="B19" s="25">
+        <f>SUMPRODUCT((TRIM(명단표[사번]&amp;"")&lt;&gt;"")*(COUNTIF(명단표[사번],명단표[사번])&gt;1))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="24" t="inlineStr">
+        <is>
+          <t>날짜 형식 오류(생년월일/수련개시일)</t>
+        </is>
+      </c>
+      <c r="B20" s="25">
+        <f>SUMPRODUCT(--ISTEXT(명단표[생년월일]))+SUMPRODUCT(--ISTEXT(명단표[수련개시일]))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="24" t="inlineStr">
+        <is>
+          <t>인턴계획 입력 오류(병원/진료과)</t>
+        </is>
+      </c>
+      <c r="B21" s="25">
+        <f>SUM(인턴계획표[입력오류])</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="24" t="inlineStr">
+        <is>
+          <t>서울·구리 15일 판정 불가</t>
+        </is>
+      </c>
+      <c r="B22" s="25">
+        <f>COUNTIF(명단표[급여지급병원(기준월)],"⚠*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="24" t="inlineStr">
+        <is>
+          <t>구리 근무자명단: 명단에 없음/동명이인</t>
+        </is>
+      </c>
+      <c r="B23" s="25">
+        <f>'출력_구리근무자'!$J$2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="24" t="inlineStr">
+        <is>
+          <t>구리 근무자명단: 날짜 오류</t>
+        </is>
+      </c>
+      <c r="B24" s="25">
+        <f>'출력_구리근무자'!$J$3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="24" t="inlineStr">
+        <is>
+          <t>점검 필요 행(전공의명단 '점검' 열)</t>
+        </is>
+      </c>
+      <c r="B25" s="25">
+        <f>SUMPRODUCT((TRIM(명단표[사번]&amp;"")&lt;&gt;"")*(명단표[점검]&lt;&gt;"정상"))</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="B18:B25">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>B18&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7913,31 +6183,39 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P26"/>
+  <dimension ref="A1:X6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="3" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="3" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="3" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="3" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
-    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="10" max="10"/>
+    <col width="17" customWidth="1" min="11" max="11"/>
+    <col width="17" customWidth="1" min="12" max="12"/>
+    <col width="17" customWidth="1" min="13" max="13"/>
+    <col width="17" customWidth="1" min="14" max="14"/>
+    <col width="17" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="3" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
+    <col width="10" customWidth="1" min="20" max="20"/>
+    <col width="10" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="22" max="22"/>
+    <col width="10" customWidth="1" min="23" max="23"/>
+    <col width="10" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>파견 현황 요약</t>
+          <t>인턴 근무 현황</t>
         </is>
       </c>
     </row>
@@ -7947,356 +6225,280 @@
           <t>기준일</t>
         </is>
       </c>
-      <c r="B2" s="23">
+      <c r="B2" s="26">
         <f>TODAY()</f>
         <v/>
       </c>
+      <c r="J2" s="16" t="inlineStr">
+        <is>
+          <t>급여 기준월 위치→</t>
+        </is>
+      </c>
+      <c r="K2" s="27">
+        <f>IFERROR(MATCH(MONTH(급여기준월),$J$3:$O$3,0),"")</f>
+        <v/>
+      </c>
+      <c r="R2" s="3" t="inlineStr">
+        <is>
+          <t>월별 병원별 인턴 인원</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>급여 기준월</t>
-        </is>
-      </c>
-      <c r="B3" s="23">
-        <f>급여기준월</f>
-        <v/>
-      </c>
-      <c r="C3" s="12" t="inlineStr">
-        <is>
-          <t>← 설정값은 설정_코드표에서 변경</t>
-        </is>
+      <c r="A3" s="16" t="inlineStr">
+        <is>
+          <t>계획 월 번호(자동)</t>
+        </is>
+      </c>
+      <c r="F3" s="16" t="inlineStr">
+        <is>
+          <t>이번/다음 달 위치→</t>
+        </is>
+      </c>
+      <c r="G3" s="27">
+        <f>IFERROR(MATCH(MONTH(TODAY()),$J$3:$O$3,0),"")</f>
+        <v/>
+      </c>
+      <c r="I3" s="27">
+        <f>IFERROR(MATCH(MONTH(EDATE(TODAY(),1)),$J$3:$O$3,0),"")</f>
+        <v/>
+      </c>
+      <c r="J3" s="27">
+        <f>IFERROR(VALUE(SUBSTITUTE(TRIM(J5),"월","")),"")</f>
+        <v/>
+      </c>
+      <c r="K3" s="27">
+        <f>IFERROR(VALUE(SUBSTITUTE(TRIM(K5),"월","")),"")</f>
+        <v/>
+      </c>
+      <c r="L3" s="27">
+        <f>IFERROR(VALUE(SUBSTITUTE(TRIM(L5),"월","")),"")</f>
+        <v/>
+      </c>
+      <c r="M3" s="27">
+        <f>IFERROR(VALUE(SUBSTITUTE(TRIM(M5),"월","")),"")</f>
+        <v/>
+      </c>
+      <c r="N3" s="27">
+        <f>IFERROR(VALUE(SUBSTITUTE(TRIM(N5),"월","")),"")</f>
+        <v/>
+      </c>
+      <c r="O3" s="27">
+        <f>IFERROR(VALUE(SUBSTITUTE(TRIM(O5),"월","")),"")</f>
+        <v/>
+      </c>
+      <c r="R3" s="4" t="inlineStr">
+        <is>
+          <t>병원</t>
+        </is>
+      </c>
+      <c r="S3" s="4">
+        <f>J5</f>
+        <v/>
+      </c>
+      <c r="T3" s="4">
+        <f>K5</f>
+        <v/>
+      </c>
+      <c r="U3" s="4">
+        <f>L5</f>
+        <v/>
+      </c>
+      <c r="V3" s="4">
+        <f>M5</f>
+        <v/>
+      </c>
+      <c r="W3" s="4">
+        <f>N5</f>
+        <v/>
+      </c>
+      <c r="X3" s="4">
+        <f>O5</f>
+        <v/>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>15일 기준(일)</t>
-        </is>
-      </c>
-      <c r="B4" s="24">
-        <f>판정기준일</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>종료 임박 기준(일)</t>
-        </is>
-      </c>
-      <c r="B5" s="24">
-        <f>임박기준일</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6"/>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>파견상태</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>인원</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>병원</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>현재 근무</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>급여 지급(기준월)</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>파견 수용(파견중)</t>
-        </is>
-      </c>
-      <c r="I7" s="4" t="inlineStr">
-        <is>
-          <t>현재 진료과</t>
-        </is>
-      </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>인원</t>
-        </is>
-      </c>
-      <c r="L7" s="4" t="inlineStr">
-        <is>
-          <t>인턴 구분</t>
-        </is>
-      </c>
-      <c r="M7" s="4" t="inlineStr">
-        <is>
-          <t>인원</t>
-        </is>
-      </c>
-      <c r="O7" s="4" t="inlineStr">
-        <is>
-          <t>파견근거</t>
-        </is>
-      </c>
-      <c r="P7" s="4" t="inlineStr">
-        <is>
-          <t>인원</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="25" t="inlineStr">
-        <is>
-          <t>파견중</t>
-        </is>
-      </c>
-      <c r="B8" s="25">
-        <f>COUNTIF(명단표[파견상태],A8)</f>
-        <v/>
-      </c>
-      <c r="D8" cm="1">
-        <f t="array" ref="D8">병원표[병원]</f>
-        <v/>
-      </c>
-      <c r="E8" cm="1">
-        <f t="array" ref="E8">COUNTIF(명단표[현재 근무병원],병원표[병원])</f>
-        <v/>
-      </c>
-      <c r="F8" cm="1">
-        <f t="array" ref="F8">COUNTIF(명단표[급여지급병원(기준월)],병원표[병원])</f>
-        <v/>
-      </c>
-      <c r="G8" cm="1">
-        <f t="array" ref="G8">COUNTIFS(명단표[파견병원],병원표[병원],명단표[파견상태],"파견중")</f>
-        <v/>
-      </c>
-      <c r="I8" cm="1">
-        <f t="array" ref="I8">진료과표[근무과]</f>
-        <v/>
-      </c>
-      <c r="J8" cm="1">
-        <f t="array" ref="J8">COUNTIF(명단표[현재 진료과],진료과표[근무과])</f>
-        <v/>
-      </c>
-      <c r="L8" cm="1">
-        <f t="array" ref="L8">인턴구분표[인턴 구분]</f>
-        <v/>
-      </c>
-      <c r="M8" cm="1">
-        <f t="array" ref="M8">COUNTIF(명단표[현재 진료과],인턴구분표[인턴 구분])</f>
-        <v/>
-      </c>
-      <c r="O8" cm="1">
-        <f t="array" ref="O8">근거표[파견근거]</f>
-        <v/>
-      </c>
-      <c r="P8" cm="1">
-        <f t="array" ref="P8">COUNTIF(명단표[파견근거],근거표[파견근거])</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="25" t="inlineStr">
-        <is>
-          <t>파견예정</t>
-        </is>
-      </c>
-      <c r="B9" s="25">
-        <f>COUNTIF(명단표[파견상태],A9)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="25" t="inlineStr">
-        <is>
-          <t>파견종료</t>
-        </is>
-      </c>
-      <c r="B10" s="25">
-        <f>COUNTIF(명단표[파견상태],A10)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="25" t="inlineStr">
-        <is>
-          <t>명단 등록 인원</t>
-        </is>
-      </c>
-      <c r="B11" s="25">
-        <f>SUMPRODUCT(--(TRIM(명단표[사번]&amp;"")&lt;&gt;""))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="25" t="inlineStr">
-        <is>
-          <t>종료 임박(파견중)</t>
-        </is>
-      </c>
-      <c r="B12" s="25">
-        <f>COUNTIFS(명단표[파견상태],"파견중",명단표[종료까지(일)],"&lt;="&amp;임박기준일)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>데이터 점검</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>건수</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="25" t="inlineStr">
-        <is>
-          <t>기본자료 인원</t>
-        </is>
-      </c>
-      <c r="B15" s="26">
-        <f>SUMPRODUCT(--(TRIM(기본자료표[사번]&amp;"")&lt;&gt;""))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="25" t="inlineStr">
-        <is>
-          <t>기본자료 재직 인원</t>
-        </is>
-      </c>
-      <c r="B16" s="26">
-        <f>COUNTIF(기본자료표[현재근무 여부],"재직")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="25" t="inlineStr">
-        <is>
-          <t>기본자료에 없는 사번</t>
-        </is>
-      </c>
-      <c r="B17" s="26">
-        <f>SUMPRODUCT((TRIM(명단표[사번]&amp;"")&lt;&gt;"")*(명단표[기본자료행]=""))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="25" t="inlineStr">
-        <is>
-          <t>명단 중복 사번</t>
-        </is>
-      </c>
-      <c r="B18" s="26">
-        <f>SUMPRODUCT((TRIM(명단표[사번]&amp;"")&lt;&gt;"")*(COUNTIF(명단표[사번],명단표[사번])&gt;1))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="25" t="inlineStr">
-        <is>
-          <t>날짜 형식 오류(생년월일/수련개시일)</t>
-        </is>
-      </c>
-      <c r="B19" s="26">
-        <f>SUMPRODUCT(--ISTEXT(명단표[생년월일]))+SUMPRODUCT(--ISTEXT(명단표[수련개시일]))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="25" t="inlineStr">
-        <is>
-          <t>인턴계획 입력 오류(병원/진료과)</t>
-        </is>
-      </c>
-      <c r="B20" s="26">
-        <f>SUM(인턴계획표[입력오류])</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="25" t="inlineStr">
-        <is>
-          <t>파견수련계획 입력 오류</t>
-        </is>
-      </c>
-      <c r="B21" s="26">
-        <f>SUMPRODUCT(--(LEN(파견표[입력오류])&gt;0))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="25" t="inlineStr">
-        <is>
-          <t>명단에 없는 파견 기록(등록번호)</t>
-        </is>
-      </c>
-      <c r="B22" s="26">
-        <f>SUMPRODUCT((파견표[키]&lt;&gt;"")*ISNA(_xlfn.XMATCH(파견표[키],명단표[키])))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="25" t="inlineStr">
-        <is>
-          <t>서울·구리 15일 판정 불가</t>
-        </is>
-      </c>
-      <c r="B23" s="26">
-        <f>COUNTIF(명단표[급여지급병원(기준월)],"⚠*")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="25" t="inlineStr">
-        <is>
-          <t>구리 근무자명단: 명단에 없음/동명이인</t>
-        </is>
-      </c>
-      <c r="B24" s="26">
-        <f>'출력_구리근무자'!$J$2</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="25" t="inlineStr">
-        <is>
-          <t>구리 근무자명단: 날짜 오류</t>
-        </is>
-      </c>
-      <c r="B25" s="26">
-        <f>'출력_구리근무자'!$J$3</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="25" t="inlineStr">
-        <is>
-          <t>점검 필요 행(전공의명단 '점검' 열)</t>
-        </is>
-      </c>
-      <c r="B26" s="26">
-        <f>SUMPRODUCT((TRIM(명단표[사번]&amp;"")&lt;&gt;"")*(명단표[점검]&lt;&gt;"정상"))</f>
+      <c r="R4" s="28" t="inlineStr">
+        <is>
+          <t>합계(배정)</t>
+        </is>
+      </c>
+      <c r="S4" s="20">
+        <f>COUNTIF(인턴계획표[정규화1],"?*")</f>
+        <v/>
+      </c>
+      <c r="T4" s="20">
+        <f>COUNTIF(인턴계획표[정규화2],"?*")</f>
+        <v/>
+      </c>
+      <c r="U4" s="20">
+        <f>COUNTIF(인턴계획표[정규화3],"?*")</f>
+        <v/>
+      </c>
+      <c r="V4" s="20">
+        <f>COUNTIF(인턴계획표[정규화4],"?*")</f>
+        <v/>
+      </c>
+      <c r="W4" s="20">
+        <f>COUNTIF(인턴계획표[정규화5],"?*")</f>
+        <v/>
+      </c>
+      <c r="X4" s="20">
+        <f>COUNTIF(인턴계획표[정규화6],"?*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>순번</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>이름</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>사번</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>기본자료 확인</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>입사일</t>
+        </is>
+      </c>
+      <c r="F5" s="4">
+        <f>"이번 달("&amp;IF($G$3="","계획 외",MONTH(TODAY())&amp;"월")&amp;") 병원"</f>
+        <v/>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>이번 달 진료과</t>
+        </is>
+      </c>
+      <c r="H5" s="4">
+        <f>"다음 달("&amp;IF($I$3="","계획 외",MONTH(EDATE(TODAY(),1))&amp;"월")&amp;") 병원"</f>
+        <v/>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>다음 달 진료과</t>
+        </is>
+      </c>
+      <c r="J5" s="4">
+        <f>TRIM(INDEX(인턴계획표[#Headers],1,4)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="K5" s="4">
+        <f>TRIM(INDEX(인턴계획표[#Headers],1,5)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="L5" s="4">
+        <f>TRIM(INDEX(인턴계획표[#Headers],1,6)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="M5" s="4">
+        <f>TRIM(INDEX(인턴계획표[#Headers],1,7)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="N5" s="4">
+        <f>TRIM(INDEX(인턴계획표[#Headers],1,8)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="O5" s="4">
+        <f>TRIM(INDEX(인턴계획표[#Headers],1,9)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="P5" s="4" t="inlineStr">
+        <is>
+          <t>입력오류</t>
+        </is>
+      </c>
+      <c r="R5" s="28" t="inlineStr">
+        <is>
+          <t>⚠ 오류</t>
+        </is>
+      </c>
+      <c r="S5" s="20">
+        <f>COUNTIF(인턴계획표[정규화1],"⚠*")</f>
+        <v/>
+      </c>
+      <c r="T5" s="20">
+        <f>COUNTIF(인턴계획표[정규화2],"⚠*")</f>
+        <v/>
+      </c>
+      <c r="U5" s="20">
+        <f>COUNTIF(인턴계획표[정규화3],"⚠*")</f>
+        <v/>
+      </c>
+      <c r="V5" s="20">
+        <f>COUNTIF(인턴계획표[정규화4],"⚠*")</f>
+        <v/>
+      </c>
+      <c r="W5" s="20">
+        <f>COUNTIF(인턴계획표[정규화5],"⚠*")</f>
+        <v/>
+      </c>
+      <c r="X5" s="20">
+        <f>COUNTIF(인턴계획표[정규화6],"⚠*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" cm="1">
+        <f t="array" ref="A6">_xlfn.LET(_xlpm.v_n,TRIM(인턴계획표[이름]&amp;""),_xlpm.v_x,_xlpm.v_n&lt;&gt;"",_xlpm.v_c,IF($G$3="","",INDEX(인턴계획표[[정규화1]:[정규화6]],0,$G$3)&amp;""),_xlpm.v_t,IF($I$3="","",INDEX(인턴계획표[[정규화1]:[정규화6]],0,$I$3)&amp;""),_xlpm.v_ok,IF(ISNUMBER(_xlfn.XMATCH(인턴계획표[사번키],기본자료표[사번키])),"확인","미등록"),_xlpm.v_in,IF(ISNUMBER(인턴계획표[입사일(비고)]),TEXT(인턴계획표[입사일(비고)],"yyyy-mm-dd"),인턴계획표[입사일(비고)]&amp;""),IF(SUM(--_xlpm.v_x)=0,"인턴 계획 없음",_xlfn._xlws.FILTER(CHOOSE({1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16},인턴계획표[순번]&amp;"",_xlpm.v_n,인턴계획표[사번]&amp;"",_xlpm.v_ok,_xlpm.v_in,IF(_xlpm.v_c="","",IF(LEFT(_xlpm.v_c,1)="⚠",_xlpm.v_c,IFERROR(LEFT(_xlpm.v_c,FIND(" ",_xlpm.v_c)-1),_xlpm.v_c))),IF(_xlpm.v_c="","",IF(LEFT(_xlpm.v_c,1)="⚠","",IFERROR(MID(_xlpm.v_c,FIND(" ",_xlpm.v_c)+1,60),""))),IF(_xlpm.v_t="","",IF(LEFT(_xlpm.v_t,1)="⚠",_xlpm.v_t,IFERROR(LEFT(_xlpm.v_t,FIND(" ",_xlpm.v_t)-1),_xlpm.v_t))),IF(_xlpm.v_t="","",IF(LEFT(_xlpm.v_t,1)="⚠","",IFERROR(MID(_xlpm.v_t,FIND(" ",_xlpm.v_t)+1,60),""))),인턴계획표[정규화1],인턴계획표[정규화2],인턴계획표[정규화3],인턴계획표[정규화4],인턴계획표[정규화5],인턴계획표[정규화6],인턴계획표[입력오류]),_xlpm.v_x)))</f>
+        <v/>
+      </c>
+      <c r="R6" cm="1">
+        <f t="array" ref="R6">병원표[병원]</f>
+        <v/>
+      </c>
+      <c r="S6" cm="1">
+        <f t="array" ref="S6">COUNTIF(인턴계획표[정규화1],병원표[병원]&amp;" *")</f>
+        <v/>
+      </c>
+      <c r="T6" cm="1">
+        <f t="array" ref="T6">COUNTIF(인턴계획표[정규화2],병원표[병원]&amp;" *")</f>
+        <v/>
+      </c>
+      <c r="U6" cm="1">
+        <f t="array" ref="U6">COUNTIF(인턴계획표[정규화3],병원표[병원]&amp;" *")</f>
+        <v/>
+      </c>
+      <c r="V6" cm="1">
+        <f t="array" ref="V6">COUNTIF(인턴계획표[정규화4],병원표[병원]&amp;" *")</f>
+        <v/>
+      </c>
+      <c r="W6" cm="1">
+        <f t="array" ref="W6">COUNTIF(인턴계획표[정규화5],병원표[병원]&amp;" *")</f>
+        <v/>
+      </c>
+      <c r="X6" cm="1">
+        <f t="array" ref="X6">COUNTIF(인턴계획표[정규화6],병원표[병원]&amp;" *")</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B17:B26">
+  <conditionalFormatting sqref="D6:D20005">
     <cfRule type="expression" priority="1" dxfId="0">
-      <formula>B17&gt;0</formula>
+      <formula>$D6="미등록"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J6:O20005">
+    <cfRule type="expression" priority="2" dxfId="8">
+      <formula>LEFT(J6,1)="⚠"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J5:O20005">
+    <cfRule type="expression" priority="3" dxfId="6">
+      <formula>J$3=MONTH(TODAY())</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/전공의_파견_모니터링.xlsx
+++ b/전공의_파견_모니터링.xlsx
@@ -16,7 +16,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="출력_구리근무자" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="출력_요약" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="출력_인턴현황" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="설정_코드표" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="출력_기관명단" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="설정_코드표" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="급여기준월">'설정_코드표'!$P$9</definedName>
@@ -904,7 +905,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A30"/>
+  <dimension ref="A1:A31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="175" customWidth="1" min="1" max="1"/>
@@ -956,145 +957,152 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr"/>
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>• 출력_기관명단: 급여 기준월의 전원 기관(근무병원·급여지급병원) — 시간외근무 판정 파일의 입력_기관명단에 값으로 붙여넣는 용도</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>[붙여넣는 방법]</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>• 기본자료: A2부터 (머리글 순서: 현재근무 여부·사번·이름·수련과목·연차·근무지·수련개시일·전공의등록번호·의사면허번호·성별·생년월일·비고). 날짜는 20260301 형식도 됩니다.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>• 인턴근무계획: B3부터 자료 행(순번·이름·사번·월 6칸·비고). 학기가 바뀌면 2행의 월 머리글(9월~2월 등)도 바꿔 적으세요. 비고 2026.03 = 2026-03-01 입사.</t>
+          <t>• 기본자료: A2부터 (머리글 순서: 현재근무 여부·사번·이름·수련과목·연차·근무지·수련개시일·전공의등록번호·의사면허번호·성별·생년월일·비고). 날짜는 20260301 형식도 됩니다.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>• 구리 근무자명단: 구리병원 파일의 시트를 A1에 양식 그대로(1~2행 제목, 3행 머리글, 4행부터 자료). 날짜는 'YYYY.MM.DD' 글자도 됩니다.</t>
+          <t>• 인턴근무계획: B3부터 자료 행(순번·이름·사번·월 6칸·비고). 학기가 바뀌면 2행의 월 머리글(9월~2월 등)도 바꿔 적으세요. 비고 2026.03 = 2026-03-01 입사.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>• 전공의명단: 사번·입사장소·비고만 입력. 나머지는 자동.</t>
+          <t>• 구리 근무자명단: 구리병원 파일의 시트를 A1에 양식 그대로(1~2행 제목, 3행 머리글, 4행부터 자료). 날짜는 'YYYY.MM.DD' 글자도 됩니다.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>• 전공의명단: 사번·입사장소·비고만 입력. 나머지는 자동.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
           <t>• 예시 데이터(ㅇㅇ)는 모두 지우고 실제 자료를 넣으세요. 표의 행을 지울 때는 행 전체 삭제(표 행 삭제)를 쓰세요.</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr"/>
-    </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>[표기 해석]</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>• 인턴 월 칸은 '지역 진료과'(예: 서울 산부 → 서울병원 산부인과, 제주 에스중앙 내과 → 제주병원 내과). 첫 단어=지역(병원약칭표), 마지막 단어=진료과(과약칭표).</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>• 통합(과 미지정), 핵/방, 직/피, 정/영 등은 인턴 전용 구분입니다(과약칭표에서 직피·정영 등 약칭도 인정).</t>
+          <t>• 인턴 월 칸은 '지역 진료과'(예: 서울 산부 → 서울병원 산부인과, 제주 에스중앙 내과 → 제주병원 내과). 첫 단어=지역(병원약칭표), 마지막 단어=진료과(과약칭표).</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>• 통합(과 미지정), 핵/방, 직/피, 정/영 등은 인턴 전용 구분입니다(과약칭표에서 직피·정영 등 약칭도 인정).</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
           <t>• 코드표에 없는 값을 직접 입력하면 오류 팝업이 뜹니다. 붙여넣기는 팝업이 뜨지 않으므로 해당 칸이 빨갛게 표시되고 요약에 집계됩니다.</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr"/>
-    </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>[급여지급병원(기준월) 규칙]</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>• 서울병원·구리병원 사이: 소속과 무관하게 급여 기준월에 15일 이상 근무한 병원이 그 달 전체를 지급(예: 구리 10일·서울 20일 → 서울 지급).</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>• 근무일: 구리 근무자명단에 있으면 그 날짜가 구리 근무일, 그 달의 나머지 날은 모두 서울 근무일입니다.</t>
+          <t>• 서울병원·구리병원 사이: 소속과 무관하게 급여 기준월에 15일 이상 근무한 병원이 그 달 전체를 지급(예: 구리 10일·서울 20일 → 서울 지급).</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>• 양쪽 모두 15일 이상이거나 모두 미만이면 ⚠ 판정 불가로 표시합니다.</t>
+          <t>• 근무일: 구리 근무자명단에 있으면 그 날짜가 구리 근무일, 그 달의 나머지 날은 모두 서울 근무일입니다.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>• 구리 근무자명단에 없는 사람은 그 달 근무병원(인턴은 인턴근무계획의 병원, 그 외는 소속병원)이 지급합니다.</t>
+          <t>• 양쪽 모두 15일 이상이거나 모두 미만이면 ⚠ 판정 불가로 표시합니다.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>• 구리 근무자명단에 없는 사람은 그 달 근무병원(인턴은 인턴근무계획의 병원, 그 외는 소속병원)이 지급합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
           <t>• 소속병원 = 입사장소 → (비어 있으면) 구리 근무자명단 비고 '구리독자'면 구리병원 → 기본자료 근무지 순서로 정합니다.</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr"/>
-    </row>
     <row r="28">
-      <c r="A28" s="3" t="inlineStr">
+      <c r="A28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>[참고]</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>• Microsoft 365(또는 Excel 2021 이상)에서만 정상 동작합니다. 구버전에서는 출력 시트가 오류로 보입니다.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>• Microsoft 365(또는 Excel 2021 이상)에서만 정상 동작합니다. 구버전에서는 출력 시트가 오류로 보입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>• 개인정보(생년월일·면허번호 등)가 포함되므로 파일 암호 설정과 접근 권한 관리를 권장합니다.</t>
         </is>
@@ -1106,6 +1114,100 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00548235"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>기관명단 (급여 기준월 기준) — 시간외근무 판정 파일의 입력_기관명단에 값으로 붙여넣기</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="16" t="inlineStr">
+        <is>
+          <t>※ A5부터 아래로 펼쳐진 전체를 복사 → 시간외 판정 파일 입력_기관명단의 표 아래에 '값 붙여넣기'. 전월·대상월·익월이 필요하면 설정_코드표의 급여 기준월을 바꿔 가며 반복하세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>기준월</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>사번</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>이름</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>수련과목</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>연차</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>소속병원</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>기준월 근무병원</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>급여지급병원(기준월)</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>급여 판정 근거</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" cm="1">
+        <f t="array" ref="A5">_xlfn.LET(_xlpm.v_k,TRIM(명단표[사번]&amp;"")&lt;&gt;"",IF(SUM(--_xlpm.v_k)=0,"명단 없음",_xlfn._xlws.FILTER(CHOOSE({1,2,3,4,5,6,7,8,9},TEXT(급여기준월,"yyyy-mm")&amp;LEFT(명단표[사번],0),명단표[사번]&amp;"",명단표[이름],명단표[수련과목],명단표[연차]&amp;"",명단표[소속병원],명단표[기준월 근무병원],명단표[급여지급병원(기준월)],명단표[급여 판정 근거]),_xlpm.v_k)))</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="007F7F7F"/>
